--- a/Maldivler_Potansiyel_Musteri_Listesi.xlsx
+++ b/Maldivler_Potansiyel_Musteri_Listesi.xlsx
@@ -204,9 +204,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Resortlar" displayName="Resortlar" ref="A1:M91" headerRowCount="1">
-  <autoFilter ref="A1:M91"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Resortlar" displayName="Resortlar" ref="A1:P91" headerRowCount="1">
+  <autoFilter ref="A1:P91"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="#"/>
     <tableColumn id="2" name="Resort"/>
     <tableColumn id="3" name="Atoll"/>
@@ -215,20 +215,23 @@
     <tableColumn id="6" name="Enerji durumu"/>
     <tableColumn id="7" name="Bilinen enerji altyapısı (not)"/>
     <tableColumn id="8" name="Web sitesi"/>
-    <tableColumn id="9" name="Kurumsal iletişim kanalı"/>
-    <tableColumn id="10" name="Hedef rol"/>
-    <tableColumn id="11" name="Puan (0–7)"/>
-    <tableColumn id="12" name="Öncelik"/>
-    <tableColumn id="13" name="Öncelik gerekçesi"/>
+    <tableColumn id="9" name="Genel e-posta (kurumsal)"/>
+    <tableColumn id="10" name="Telefon"/>
+    <tableColumn id="11" name="İletişim kaynağı / güven"/>
+    <tableColumn id="12" name="Kaynak bağlantısı"/>
+    <tableColumn id="13" name="Hedef rol"/>
+    <tableColumn id="14" name="Puan (0–7)"/>
+    <tableColumn id="15" name="Öncelik"/>
+    <tableColumn id="16" name="Öncelik gerekçesi"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Gruplar" displayName="Gruplar" ref="A1:G15" headerRowCount="1">
-  <autoFilter ref="A1:G15"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Gruplar" displayName="Gruplar" ref="A1:K18" headerRowCount="1">
+  <autoFilter ref="A1:K18"/>
+  <tableColumns count="11">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Merkez"/>
     <tableColumn id="3" name="Maldivler'deki resort sayısı (yakl.)"/>
@@ -236,6 +239,10 @@
     <tableColumn id="5" name="Enerji durumu / not"/>
     <tableColumn id="6" name="Web sitesi"/>
     <tableColumn id="7" name="Öncelik"/>
+    <tableColumn id="8" name="Merkez ofis e-posta (kurumsal)"/>
+    <tableColumn id="9" name="Merkez ofis telefon"/>
+    <tableColumn id="10" name="Adres"/>
+    <tableColumn id="11" name="Kaynak bağlantısı"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
@@ -257,8 +264,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Ortaklar" displayName="Ortaklar" ref="A1:E10" headerRowCount="1">
-  <autoFilter ref="A1:E10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Ortaklar" displayName="Ortaklar" ref="A1:E13" headerRowCount="1">
+  <autoFilter ref="A1:E13"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Firma"/>
     <tableColumn id="2" name="Tür"/>
@@ -583,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -696,50 +703,85 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>Özel durum: Türk sahipli resort (Ayada) +3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>Öncelik: A = 6–7 puan, B = 4–5 puan, C = 0–3 puan</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>ÖNEMLİ NOTLAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>• Oda sayıları yaklaşıktır (kamuya açık kaynaklardan/genel bilgiden); görüşme öncesi resort web sitesinden teyit edin.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>• 'Dizel ağırlıklı' = internette GES bilgisine rastlanmadı demektir; resortun hiç GES'i olmadığı anlamına gelmeyebilir.</t>
+          <t>• Oda sayıları yaklaşıktır (kamuya açık kaynaklardan/genel bilgiden); görüşme öncesi resort web sitesinden teyit edin.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>• Kişisel veri toplanmadı. İletişim için resortların kurumsal web sitelerindeki genel iletişim kanalları kullanılmalı;</t>
+          <t>• 'Dizel ağırlıklı' = internette GES bilgisine rastlanmadı demektir; resortun hiç GES'i olmadığı anlamına gelmeyebilir.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  hedef rol (Chief Engineer vb.) LinkedIn'de unvan ile aranabilir.</t>
+          <t>• İletişim sütunları yalnızca KURUMSAL genel adresleri içerir (info@, reservations@, sales@ vb.). Kişisel adres eklenmedi.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>• 'İletişim kaynağı / güven' sütunu adresin nereden alındığını gösterir: 'Otelin kendi sitesi' en güvenilir olanıdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>• Rezervasyon adresine yazarken konu satırına 'Attn: Director of Engineering / Chief Engineer' ekleyin; mail ilgili kişiye yönlendirilir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>• E-postası '—' olan resortlarda adres sitede gizlenmiş; web sitesindeki iletişim formunu veya telefonu kullanın.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>• Resmi tam liste: Turizm Bakanlığı sitesindeki 'Registered Facilities' listesi (tourism.gov.mv) tüm resortların e-posta/telefonunu içerir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>• Bazı resortların adı 2025–2026'da değişti (Niva, Villa Park, Villa Nautica, Machchafushi, NH Reethi, Emerald Faarufushi) – notlarda belirtildi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>• 'Doğrulanmalı' yazan alanlar masa başı araştırmada kesinleştirilemedi.</t>
         </is>
@@ -756,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:P91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -766,12 +808,15 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -817,25 +862,40 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>Kurumsal iletişim kanalı</t>
+          <t>Genel e-posta (kurumsal)</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
+          <t>Telefon</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>İletişim kaynağı / güven</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Kaynak bağlantısı</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
           <t>Hedef rol</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Puan (0–7)</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Öncelik</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Öncelik gerekçesi</t>
         </is>
@@ -857,7 +917,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Universal Resorts</t>
+          <t>VERSA Hospitality (Niva)</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -875,28 +935,43 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>kuramathi.com</t>
+          <t>nivakuramathi.com</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>info@kuramathi.com</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
+          <t>+960 666 0527</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Arama sonucu (otel bilgisi); 'Niva Kuramathi' adıyla yeni marka/site görünüyor (nivakuramathi.com) – doğrulanmalı</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nivakuramathi.com/contact/</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="N2" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>büyük resort (yüksek dizel tüketimi); GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -908,58 +983,73 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Anantara Dhigu / Veli / Naladhu</t>
+          <t>Sun Island Resort &amp; Spa</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Güney Malé)</t>
+          <t>Alif Dhaal (Güney Ari)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Minor Hotels</t>
+          <t>Villa Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>3 resort komşu adalarda</t>
+          <t>Yeni adı Villa Park; 2.400+ güneş paneli var</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>anantara.com</t>
+          <t>villaresorts.com</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>park@villaresorts.com; hello@villaresorts.com (Villa Resorts genel)</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
+          <t>+960 668 0088</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi. NOT: Yeni adı 'Villa Park' (eski Sun Island)</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>https://villaresorts.com/villa-park/contact/</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K3" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="N3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>büyük resort (yüksek dizel tüketimi); GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -969,58 +1059,73 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Atmosphere Kanifushi</t>
+          <t>Anantara Dhigu / Veli / Naladhu</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Lhaviyani</t>
+          <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Atmosphere Core</t>
+          <t>Minor Hotels</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Kısmi GES, ESS yok/bilinmiyor</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Grup genelinde ~8.900 panel (çatı GES)</t>
+          <t>3 resort komşu adalarda</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>atmosphere-kanifushi.com</t>
+          <t>anantara.com</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>dhigumaldives@anantara.com</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
+          <t>+960 664 4100</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi (iletişim sayfası)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.anantara.com/en/dhigu-maldives/contact</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="N4" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -1030,21 +1135,21 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Canareef Resort Maldives</t>
+          <t>Atmosphere Kanifushi</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Addu</t>
+          <t>Lhaviyani</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Bağımsız</t>
+          <t>Atmosphere Core</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>280</v>
+        <v>150</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -1053,35 +1158,50 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Büyük çatı GES kurulumu duyuruldu</t>
+          <t>Grup genelinde ~8.900 panel (çatı GES)</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>canareef.com</t>
+          <t>atmosphere-kanifushi.com</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reservations@atmosphere-kanifushi.com</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
+          <t>+960 662 0066</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi; genel adres sayfada gizlenmiş</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>https://atmosphere-kanifushi.com/en/contact-us</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="N5" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>büyük resort (yüksek dizel tüketimi); GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi</t>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -1091,21 +1211,21 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Club Med Kani</t>
+          <t>Ayada Maldives</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Gaafu Dhaalu</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Club Med</t>
+          <t>Aydeniz Grubu (Ankara, TÜRK)</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>250</v>
+        <v>110</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -1114,35 +1234,50 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Türk sahipli (Aydeniz Grubu) – Türkçe, doğrudan sahibe ulaşılabilir</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>clubmed.com</t>
+          <t>ayadamaldives.com</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>info@ayadamaldives.com</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
+          <t>+960 684 4444; Türkiye: 444 6 200</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi. TÜRK SAHİPLİ: Aydeniz Grubu (Ankara) – teyit edildi</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ayadamaldives.com/contact</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="N6" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; Türk sahipli (Aydeniz Grubu, Ankara) – doğrudan sahiple Türkçe görüşme, ilk referans için ideal</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1287,21 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Holiday Inn Resort Kandooma</t>
+          <t>Canareef Resort Maldives</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Güney Malé)</t>
+          <t>Addu</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>IHG markası</t>
+          <t>Bağımsız</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>160</v>
+        <v>280</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -1175,35 +1310,50 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Sitede GES programı anlatılıyor</t>
+          <t>Büyük çatı GES kurulumu duyuruldu</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>maldives.holidayinnresorts.com</t>
+          <t>canareef.com</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>info@canareef.com</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
+          <t>+960 689 6677</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>https://canareef.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="N7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>büyük resort (yüksek dizel tüketimi); GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi</t>
         </is>
       </c>
     </row>
@@ -1213,21 +1363,21 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Kandima Maldives</t>
+          <t>Club Med Kani</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Dhaalu</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Pulse Hotels &amp; Resorts</t>
+          <t>Club Med</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -1241,28 +1391,43 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>kandima.com</t>
+          <t>clubmed.com</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
+          <t>+960 664 3152</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>E-posta sayfada gizlenmiş; Club Med merkezi üzerinden</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hotelcontact.net/club-med-kani-maldives-north-male-en.html</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="N8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="L8" s="6" t="inlineStr">
+      <c r="O8" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="P8" s="5" t="inlineStr">
         <is>
           <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -1274,58 +1439,73 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Kuredu Island Resort</t>
+          <t>Holiday Inn Resort Kandooma</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Lhaviyani</t>
+          <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Kuredu (bağımsız grup)</t>
+          <t>IHG markası</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>380</v>
+        <v>160</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Ülkenin en büyük resortlarından</t>
+          <t>Sitede GES programı anlatılıyor</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>kuredu.com</t>
+          <t>maldives.holidayinnresorts.com</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reservations.hikandooma@ihg.com</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
+          <t>+960 664 0511</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>https://maldives.holidayinnresorts.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="N9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="L9" s="6" t="inlineStr">
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -1335,58 +1515,73 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>LUX* South Ari Atoll</t>
+          <t>Kandima Maldives</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Alif Dhaal (Güney Ari)</t>
+          <t>Dhaalu</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>LUX* / The Lux Collective</t>
+          <t>Pulse Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Kısmi GES, ESS yok/bilinmiyor</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Swimsol SolarSea yüzer GES</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>luxresorts.com</t>
+          <t>kandima.com</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>mykindofplace@kandima.com; reservations@kandima.com</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
+          <t>+960 676 0077</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Otel rehberi / arama sonucu</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.maldivesyp.com/company/638/Kandima_Maldives</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="N10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="L10" s="6" t="inlineStr">
+      <c r="O10" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -1396,58 +1591,73 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Mandarin Oriental Bolidhuffaru Reef</t>
+          <t>Kuredu Island Resort</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Güney Malé)</t>
+          <t>Lhaviyani</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Mandarin Oriental</t>
+          <t>Crown &amp; Champa (Kuredu Holdings)</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>120</v>
+        <v>380</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>~2026 açılış hedefi</t>
+          <t>Ülkenin en büyük resortlarından</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>mandarinoriental.com</t>
+          <t>kuredu.com</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
+          <t>+960 662 0337</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi; e-posta sayfada gizlenmiş. NOT: Crown &amp; Champa sitesinde listeleniyor</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kuredu.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="N11" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -1457,21 +1667,21 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>One&amp;Only Reethi Rah</t>
+          <t>LUX* South Ari Atoll</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Alif Dhaal (Güney Ari)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Kerzner</t>
+          <t>LUX* / The Lux Collective</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -1480,33 +1690,48 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Swimsol müşterisi</t>
+          <t>Swimsol SolarSea yüzer GES</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>oneandonlyresorts.com</t>
+          <t>luxresorts.com</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>stay@luxmaldivesresort.com</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
+          <t>+960 668 0901</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.luxresorts.com/en/maldives/resort/luxsouthariatoll/contact-us</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="N12" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="L12" s="6" t="inlineStr">
+      <c r="O12" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="P12" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -1518,58 +1743,73 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Paradise Island Resort</t>
+          <t>Mandarin Oriental Bolidhuffaru Reef</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Villa Hotels &amp; Resorts</t>
+          <t>Mandarin Oriental</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>~2026 açılış hedefi</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>villaresorts.com</t>
+          <t>mandarinoriental.com</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="N13" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -1579,58 +1819,73 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Sun Island Resort &amp; Spa</t>
+          <t>One&amp;Only Reethi Rah</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Alif Dhaal (Güney Ari)</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Villa Hotels &amp; Resorts</t>
+          <t>Kerzner</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>350</v>
+        <v>128</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Swimsol müşterisi</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>villaresorts.com</t>
+          <t>oneandonlyresorts.com</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reservations@oneandonlyreethirah.com (düşük güven)</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
+          <t>+960 664 8800</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Üçüncü taraf site – doğrulanmalı</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.travelweekly.com/Hotels/Male-Maldives/OneOnly-Reethi-Rah-p58629322</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K14" s="5" t="n">
+      <c r="N14" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="inlineStr">
+      <c r="O14" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -1640,58 +1895,73 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Waldorf Astoria Ithaafushi</t>
+          <t>Paradise Island Resort</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Güney Malé)</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Hilton markası</t>
+          <t>Villa Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>120</v>
+        <v>280</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Kısmi GES, ESS yok/bilinmiyor</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Swimsol müşterisi</t>
+          <t>Yeni adı Villa Nautica</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>hilton.com</t>
+          <t>villaresorts.com</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>nautica@villaresorts.com; hello@villaresorts.com</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
+          <t>+960 664 0011</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi. NOT: Yeni adı 'Villa Nautica' (Villa Resorts)</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>https://villaresorts.com/villa-nautica/contact/</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="N15" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="L15" s="6" t="inlineStr">
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1971,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Adaaran Club Rannalhi</t>
+          <t>Waldorf Astoria Ithaafushi</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1711,48 +1981,63 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Aitken Spence (Adaaran)</t>
+          <t>Hilton markası</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Swimsol müşterisi</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>adaaran.com</t>
+          <t>hilton.com</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>MLEON.hotel@waldorfastoria.com</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
+          <t>+960 400 0300</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.waldorfastoriamaldives.com/contact/</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K16" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="N16" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -1762,12 +2047,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Adaaran Select Hudhuranfushi</t>
+          <t>Adaaran Club Rannalhi</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1776,7 +2061,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -1795,23 +2080,38 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>res.acr@adaaran.com.mv</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
+          <t>+960 664 2688</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi (iletişim sayfası)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.adaaran.com/clubrannalhi/contact-us/</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K17" s="5" t="n">
+      <c r="N17" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="P17" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -1823,60 +2123,73 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Aman Maldives</t>
+          <t>Adaaran Select Hudhuranfushi</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Vaavu</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Aman</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Doğrulanmalı</t>
-        </is>
+          <t>Aitken Spence (Adaaran)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>210</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>2027 hedef, tarih belirsiz</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>aman.com</t>
+          <t>adaaran.com</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>res.hrf@adaaran.com.mv</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
+          <t>+960 664 0375</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi (iletişim sayfası)</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.adaaran.com/selecthudhuranfushi/contact-us/</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K18" s="5" t="n">
+      <c r="N18" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -1886,24 +2199,24 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Amaraa Faru (yeni)</t>
+          <t>Aman Maldives</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
+          <t>Vaavu</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Aman</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Atmosphere Core</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Doğrulanmalı</t>
-        </is>
-      </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
@@ -1911,33 +2224,48 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>2027 açılış; GES planlandığı açıklandı</t>
+          <t>2027 hedef, tarih belirsiz</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>atmospherecore.com</t>
+          <t>aman.com</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K19" s="5" t="n">
+      <c r="N19" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr">
         <is>
           <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -1949,58 +2277,75 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Bandos Maldives</t>
+          <t>Amaraa Faru (yeni)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Doğrulanmalı</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Bağımsız (Maldivli)</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>250</v>
+          <t>Atmosphere Core</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Doğrulanmalı</t>
+        </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2027 açılış; GES planlandığı açıklandı</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>bandosmaldives.com</t>
+          <t>atmospherecore.com</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="N20" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi</t>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -2010,58 +2355,73 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Bvlgari Resort Ranfushi</t>
+          <t>Bandos Maldives</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Raa</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Bvlgari (Marriott)</t>
+          <t>Bağımsız (Maldivli)</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>54</v>
+        <v>250</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>~2027 açılış</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>bulgarihotels.com</t>
+          <t>bandosmaldives.com</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
+          <t>+960 664 0088</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi; e-posta sayfada gizlenmiş</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>https://bandosmaldives.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K21" s="5" t="n">
+      <c r="N21" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi</t>
         </is>
       </c>
     </row>
@@ -2071,23 +2431,21 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Capella Maldives (Fari Islands)</t>
+          <t>Bvlgari Resort Ranfushi</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Raa</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Pontiac Land</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Doğrulanmalı</t>
-        </is>
+          <t>Bvlgari (Marriott)</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>54</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
@@ -2096,35 +2454,50 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>2027 hedef; Fari mikro şebekesine bağlanabilir</t>
+          <t>~2027 açılış</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>capellahotels.com</t>
+          <t>bulgarihotels.com</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K22" s="5" t="n">
+      <c r="N22" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P22" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -2134,58 +2507,75 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Centara Grand Island Resort</t>
+          <t>Capella Maldives (Fari Islands)</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Alif Dhaal (Güney Ari)</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Centara Hotels</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>112</v>
+          <t>Pontiac Land</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Doğrulanmalı</t>
+        </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Kısmi GES, ESS yok/bilinmiyor</t>
+          <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Tüm çatılarda GES; 2,3 GWh üretim / 645 bin L dizel tasarrufu</t>
+          <t>2027 hedef; Fari mikro şebekesine bağlanabilir</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>centarahotelsresorts.com</t>
+          <t>capellahotels.com</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K23" s="5" t="n">
+      <c r="N23" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2585,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Centara Ras Fushi</t>
+          <t>Centara Grand Island Resort</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Alif Dhaal (Güney Ari)</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -2209,16 +2599,16 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Yeni adı Machchafushi Island Resort (Centara Collection); tüm çatılarda GES</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -2228,25 +2618,40 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
+          <t>+960 668 8000</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>NOT: Yeni adı 'Machchafushi Island Resort &amp; Spa, The Centara Collection'; e-posta sayfada gizlenmiş</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>https://www.centarahotelsresorts.com/centaragrand/cirm/contact/</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K24" s="5" t="n">
+      <c r="N24" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L24" s="7" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2661,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Cinnamon Dhonveli</t>
+          <t>Centara Ras Fushi</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2266,11 +2671,11 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Cinnamon Hotels (John Keells)</t>
+          <t>Centara Hotels</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -2284,28 +2689,43 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>cinnamonhotels.com</t>
+          <t>centarahotelsresorts.com</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>crf@chr.co.th</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
+          <t>+960 664 3880</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.centarahotelsresorts.com/centara/CRF/contact</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K25" s="5" t="n">
+      <c r="N25" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="P25" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -2317,17 +2737,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Conrad Maldives Rangali Island</t>
+          <t>Cinnamon Dhonveli</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Alif Dhaal (Güney Ari)</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Hilton markası</t>
+          <t>Cinnamon Hotels (John Keells)</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
@@ -2345,28 +2765,43 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>hilton.com</t>
+          <t>cinnamonhotels.com</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>dhonveli@cinnamonhotels.com; sales.mv@cinnamonhotels.com</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
+          <t>+960 664 0055</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Otel rehberi / otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>https://www.maldivesyp.com/company/547/Cinnamon_Dhonveli_Maldives</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K26" s="5" t="n">
+      <c r="N26" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="P26" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -2378,21 +2813,21 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Dhigali Maldives</t>
+          <t>Conrad Maldives Rangali Island</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Raa</t>
+          <t>Alif Dhaal (Güney Ari)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Universal Resorts</t>
+          <t>Hilton markası</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -2406,28 +2841,43 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>dhigali.com</t>
+          <t>hilton.com</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>mlehi.maldives@conradhotels.com</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
+          <t>+960 668 0629</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.conradmaldives.com/contact/</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K27" s="5" t="n">
+      <c r="N27" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="P27" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -2439,58 +2889,73 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Four Seasons Kuda Huraa</t>
+          <t>Dhigali Maldives</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Raa</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Four Seasons</t>
+          <t>VERSA Hospitality (Niva)</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Kısmi GES, ESS yok/bilinmiyor</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Swimsol GES</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>fourseasons.com/maldiveskh</t>
+          <t>nivadhigali.com</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
+          <t>+960 658 6060</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>NOT: 'Niva Dhigali' adıyla yeni marka/site; e-posta sayfada gizlenmiş</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nivadhigali.com/contact/</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K28" s="5" t="n">
+      <c r="N28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P28" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -2500,12 +2965,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Four Seasons Landaa Giraavaru</t>
+          <t>Four Seasons Kuda Huraa</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Baa</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2514,7 +2979,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
@@ -2523,33 +2988,48 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Swimsol çatı GES (3.105 panel)</t>
+          <t>Swimsol GES</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>fourseasons.com/maldiveslg</t>
+          <t>fourseasons.com/maldiveskh</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
+          <t>+960 664 4888</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>E-posta bulunamadı (Four Seasons merkezi formu)</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>https://www.forbestravelguide.com/hotels/maldives-maldives/four-seasons-resort-maldives-at-kuda-huraa</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K29" s="5" t="n">
+      <c r="N29" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="P29" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -2561,58 +3041,73 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Hard Rock Hotel Maldives</t>
+          <t>Four Seasons Landaa Giraavaru</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Güney Malé)</t>
+          <t>Baa</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>CROSSROADS / Singha Estate</t>
+          <t>Four Seasons</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Entegre ada kompleksi (marina + 2 otel)</t>
+          <t>Swimsol çatı GES (3.105 panel)</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>hardrockhotels.com/maldives</t>
+          <t>fourseasons.com/maldiveslg</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reservations.maldives@fourseasons.com</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
+          <t>+960 660 0888</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Arama sonucu (Four Seasons Maldivler ortak adresi)</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fourseasons.com/maldiveslg/</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K30" s="5" t="n">
+      <c r="N30" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P30" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -2622,21 +3117,21 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Heritance Aarah</t>
+          <t>Hard Rock Hotel Maldives</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Raa</t>
+          <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Aitken Spence (Heritance)</t>
+          <t>CROSSROADS / Singha Estate</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -2645,33 +3140,48 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Entegre ada kompleksi (marina + 2 otel)</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>heritancehotels.com</t>
+          <t>hardrockhotels.com/maldives</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>info@hrhmaldives.com</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
+          <t>+960 665 1400</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>https://hotel.hardrock.com/maldives/contact.aspx</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K31" s="5" t="n">
+      <c r="N31" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="P31" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -2683,21 +3193,21 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Holiday Island Resort</t>
+          <t>Heritance Aarah</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Alif Dhaal (Güney Ari)</t>
+          <t>Raa</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Villa Hotels &amp; Resorts</t>
+          <t>Aitken Spence (Heritance)</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -2711,28 +3221,43 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>villaresorts.com</t>
+          <t>heritancehotels.com</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>res.aarah@heritancehotels.com</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
+          <t>+960 664 1908</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>https://www.heritancehotels.com/aarah/contact-us/</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K32" s="5" t="n">
+      <c r="N32" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr">
+      <c r="P32" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -2744,58 +3269,73 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Hurawalhi Island Resort</t>
+          <t>Holiday Island Resort</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Lhaviyani</t>
+          <t>Alif Dhaal (Güney Ari)</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Crown &amp; Champa Resorts</t>
+          <t>Villa Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Kısmi GES, ESS yok/bilinmiyor</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Mimariye entegre GES</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>hurawalhi.com</t>
+          <t>villaresorts.com</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>hello@villaresorts.com (Villa Resorts genel)</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendine ait adresi bulunamadı; Villa Resorts merkezi</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>https://villaresorts.com/contact/</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K33" s="5" t="n">
+      <c r="N33" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="O33" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P33" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -2805,58 +3345,73 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Kurumba Maldives</t>
+          <t>Hurawalhi Island Resort</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Lhaviyani</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Universal Resorts</t>
+          <t>Crown &amp; Champa Resorts</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mimariye entegre GES</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>kurumba.com</t>
+          <t>hurawalhi.com</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reservations@hurawalhi.com</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
+          <t>+960 662 2000</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hurawalhi.com/contact/</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K34" s="5" t="n">
+      <c r="N34" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P34" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -2866,7 +3421,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Meeru Maldives Resort Island</t>
+          <t>Kurumba Maldives</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -2876,11 +3431,11 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Bağımsız (Maldivli)</t>
+          <t>VERSA Hospitality (Niva)</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>286</v>
+        <v>180</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -2894,30 +3449,45 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>meeru.com</t>
+          <t>kurumba.com</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
+          <t>+960 664 2324</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi; e-postalar sayfada gizlenmiş</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kurumba.com/contact</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K35" s="5" t="n">
+      <c r="N35" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi</t>
+      <c r="P35" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -2927,58 +3497,73 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>OZEN LIFE Maadhoo</t>
+          <t>Meeru Maldives Resort Island</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Güney Malé)</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Atmosphere Core</t>
+          <t>Bağımsız (Maldivli)</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>90</v>
+        <v>286</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Kısmi GES, ESS yok/bilinmiyor</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Swimsol SolarSea yüzer GES</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>ozen-life-maadhoo.com</t>
+          <t>meeru.com</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reservations@meeru.com</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
+          <t>+960 664 3157</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>https://www.meeru.com/one-island-one-resort-contact-us/</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K36" s="5" t="n">
+      <c r="N36" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P36" s="5" t="inlineStr">
+        <is>
+          <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi</t>
         </is>
       </c>
     </row>
@@ -2988,7 +3573,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>OZEN Reserve Bolifushi</t>
+          <t>OZEN LIFE Maadhoo</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -3011,33 +3596,48 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Grup çatı GES programı</t>
+          <t>Swimsol SolarSea yüzer GES</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>ozen-reserve-bolifushi.com</t>
+          <t>ozen-life-maadhoo.com</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
+          <t>+960 400 2222</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi; e-posta sayfada gizlenmiş</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>https://www.theozencollection.com/ozenlife-maadhoo/contact-us/</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K37" s="5" t="n">
+      <c r="N37" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="P37" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -3049,58 +3649,73 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Robinson Maldives</t>
+          <t>OZEN Reserve Bolifushi</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Gaafu Alifu</t>
+          <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>TUI / Robinson</t>
+          <t>Atmosphere Core</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Grup çatı GES programı</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>robinson.com</t>
+          <t>ozen-reserve-bolifushi.com</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
+          <t>+960 664 2020</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi; e-posta sayfada gizlenmiş</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>https://theozencollection.com/bolifushi/en/contact-us</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K38" s="5" t="n">
+      <c r="N38" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="O38" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P38" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -3110,60 +3725,73 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Rosewood Ranfaru</t>
+          <t>Robinson Maldives</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Haa Alifu</t>
+          <t>Gaafu Alifu</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Rosewood</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>Doğrulanmalı</t>
-        </is>
+          <t>TUI / Robinson</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>125</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>GES sahası planı açıklandı</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>rosewoodhotels.com</t>
+          <t>robinson.com</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>maldives@robinson.com</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
+          <t>+960 682 0000</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi / arama sonucu</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>https://www.robinson.com/en/en/resort-holiday/maldives/maldives/club-details/</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K39" s="5" t="n">
+      <c r="N39" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P39" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -3173,58 +3801,75 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Royal Island Resort</t>
+          <t>Rosewood Ranfaru</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Baa</t>
+          <t>Haa Alifu</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Villa Hotels &amp; Resorts</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>150</v>
+          <t>Rosewood</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Doğrulanmalı</t>
+        </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GES sahası planı açıklandı</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>villaresorts.com</t>
+          <t>rosewoodhotels.com</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K40" s="5" t="n">
+      <c r="N40" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L40" s="7" t="inlineStr">
+      <c r="O40" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P40" s="5" t="inlineStr">
+        <is>
+          <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -3234,21 +3879,21 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>SAii Lagoon Maldives</t>
+          <t>Royal Island Resort</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Güney Malé)</t>
+          <t>Baa</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>CROSSROADS / Singha Estate</t>
+          <t>Villa Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
@@ -3257,33 +3902,48 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Hard Rock ile aynı ada kompleksi</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>saiihotels.com</t>
+          <t>villaresorts.com</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>hello@villaresorts.com; sales@villaresorts.com</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
+          <t>+960 660 0088</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi (Villa Resorts)</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>https://villaresorts.com/royal-island/contact/</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K41" s="5" t="n">
+      <c r="N41" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L41" s="7" t="inlineStr">
+      <c r="O41" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="P41" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -3295,21 +3955,21 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Shangri-La Villingili</t>
+          <t>SAii Lagoon Maldives</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Addu</t>
+          <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Shangri-La</t>
+          <t>CROSSROADS / Singha Estate</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
@@ -3318,33 +3978,48 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hard Rock ile aynı ada kompleksi</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>shangri-la.com</t>
+          <t>saiihotels.com</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>rsvn.lagoon@saiihotels.com</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
+          <t>+960 665 1300</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>https://www.saiihotels.com/lagoon-maldives/contact-us/</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K42" s="5" t="n">
+      <c r="N42" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L42" s="7" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M42" s="5" t="inlineStr">
+      <c r="P42" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -3356,21 +4031,21 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Sheraton Maldives Full Moon</t>
+          <t>Shangri-La Villingili</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Addu</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Marriott markası</t>
+          <t>Shangri-La</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
@@ -3384,28 +4059,43 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>marriott.com</t>
+          <t>shangri-la.com</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
+          <t>+960 689 7888</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi; e-posta sayfada gizlenmiş</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.shangri-la.com/male/villingiliresort/about/local-guide/explore-male/quick-facts/</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K43" s="5" t="n">
+      <c r="N43" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L43" s="7" t="inlineStr">
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M43" s="5" t="inlineStr">
+      <c r="P43" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -3417,58 +4107,73 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Six Senses Laamu</t>
+          <t>Sheraton Maldives Full Moon</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Laamu</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Six Senses (IHG)</t>
+          <t>Marriott markası</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>97</v>
+        <v>176</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Kısmi GES, ESS yok/bilinmiyor</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Sürdürülebilirlik odaklı; GES bilgisi var, kapsamı doğrulanmalı</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>sixsenses.com</t>
+          <t>marriott.com</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>sheraton.maldives@sheraton.com</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
+          <t>+960 664 2010</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>Otel rehberi / arama sonucu</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hotelcontact.net/sheraton-maldives-full-moon-resort-spa-vihamanaafushi-en.html</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K44" s="5" t="n">
+      <c r="N44" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L44" s="7" t="inlineStr">
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P44" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -3478,58 +4183,73 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Sun Siyam Iru Fushi</t>
+          <t>Six Senses Laamu</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Noonu</t>
+          <t>Laamu</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Sun Siyam Resorts</t>
+          <t>Six Senses (IHG)</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>220</v>
+        <v>97</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Grup modeli diğer adalara yayacağını açıkladı (2. faz adayı)</t>
+          <t>Sürdürülebilirlik odaklı; GES bilgisi var, kapsamı doğrulanmalı</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>sunsiyam.com</t>
+          <t>sixsenses.com</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reservations-laamu@sixsenses.com</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
+          <t>+960 680 0800</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>Arama sonucu</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>https://wetu.com/iBrochure/en/Information/63679/six_senses_laamu/Contact</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K45" s="5" t="n">
+      <c r="N45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="O45" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P45" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -3539,12 +4259,12 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Sun Siyam Iru Veli</t>
+          <t>Sun Siyam Iru Fushi</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Dhaalu</t>
+          <t>Noonu</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -3553,7 +4273,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
@@ -3562,7 +4282,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Grup 2. faz adayı</t>
+          <t>Grup modeli diğer adalara yayacağını açıkladı (2. faz adayı)</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -3572,23 +4292,38 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>info.irufushi@sunsiyam.com; book@sunsiyam.com (merkez)</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
+          <t>+960 656 0591</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sunsiyam.com/sun-siyam-iru-fushi/contact-us/</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K46" s="5" t="n">
+      <c r="N46" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="O46" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M46" s="5" t="inlineStr">
+      <c r="P46" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -3600,58 +4335,73 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Taj Coral Reef</t>
+          <t>Sun Siyam Iru Veli</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Dhaalu</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>IHCL (Taj)</t>
+          <t>Sun Siyam Resorts</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Kısmi GES, ESS yok/bilinmiyor</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Swimsol SolarSea yüzer GES</t>
+          <t>Grup 2. faz adayı</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>tajhotels.com</t>
+          <t>sunsiyam.com</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>book@sunsiyam.com (merkez)</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
+          <t>+960 676 0100</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi; otele özel e-posta gizlenmiş</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sunsiyam.com/sun-siyam-iru-veli/contact-us/</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K47" s="5" t="n">
+      <c r="N47" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="O47" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P47" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -3661,12 +4411,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Taj Exotica Resort &amp; Spa</t>
+          <t>Taj Coral Reef</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Güney Malé)</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -3675,7 +4425,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
@@ -3694,23 +4444,38 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>tajcoralreef@tajhotels.com</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
+          <t>+960 664 1948</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>Arama sonucu</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>https://www.maldivestourism.net/resorts/taj-coral-reef-resort/</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K48" s="5" t="n">
+      <c r="N48" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L48" s="7" t="inlineStr">
+      <c r="O48" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M48" s="5" t="inlineStr">
+      <c r="P48" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -3722,21 +4487,21 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>VARU by Atmosphere</t>
+          <t>Taj Exotica Resort &amp; Spa</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Atmosphere Core</t>
+          <t>IHCL (Taj)</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
@@ -3745,33 +4510,48 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Grup çatı GES programı</t>
+          <t>Swimsol SolarSea yüzer GES</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>varu-by-atmosphere.com</t>
+          <t>tajhotels.com</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>exotica.maldives@tajhotels.com</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
+          <t>+960 400 6000</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>Arama sonucu</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>https://visitmaldives.com/en/resorts/taj-exotica-resort-and-spa-maldives</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K49" s="5" t="n">
+      <c r="N49" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="O49" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="P49" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -3783,58 +4563,73 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Velassaru Maldives</t>
+          <t>VARU by Atmosphere</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Güney Malé)</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Universal Resorts</t>
+          <t>Atmosphere Core</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Grup çatı GES programı</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>velassaru.com</t>
+          <t>varu-by-atmosphere.com</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
+          <t>+960 400 0800</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi; e-posta sayfada gizlenmiş</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>https://varu-atmosphere.com/en/contact-us</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K50" s="5" t="n">
+      <c r="N50" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L50" s="7" t="inlineStr">
+      <c r="O50" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M50" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P50" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -3844,7 +4639,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Zamani Islands (3 resort + marina)</t>
+          <t>Velassaru Maldives</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -3854,50 +4649,63 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Zamani</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>Doğrulanmalı</t>
-        </is>
+          <t>VERSA Hospitality (Niva)</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>129</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>8 adalı karma proje – büyük enerji ihtiyacı</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>nivavelassaru.com</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Doğrulanmalı</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
+          <t>+960 665 6100</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>NOT: 'Niva Velassaru' adıyla yeni marka/site; e-posta gizlenmiş</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nivavelassaru.com/contact/</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K51" s="5" t="n">
+      <c r="N51" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L51" s="7" t="inlineStr">
+      <c r="O51" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M51" s="5" t="inlineStr">
-        <is>
-          <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P51" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -3907,7 +4715,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Adaaran Prestige Vadoo</t>
+          <t>Zamani Islands (3 resort + marina)</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -3917,48 +4725,65 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Aitken Spence (Adaaran)</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>50</v>
+          <t>Zamani</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Doğrulanmalı</t>
+        </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8 adalı karma proje – büyük enerji ihtiyacı</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>adaaran.com</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>Bulunamadı (yeni proje / doğrulanmalı)</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K52" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L52" s="7" t="inlineStr">
+      <c r="N52" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O52" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M52" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P52" s="5" t="inlineStr">
+        <is>
+          <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -3968,21 +4793,21 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Anantara Kihavah</t>
+          <t>Adaaran Prestige Vadoo</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Baa</t>
+          <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Minor Hotels</t>
+          <t>Aitken Spence (Adaaran)</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
@@ -3996,28 +4821,43 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>anantara.com</t>
+          <t>adaaran.com</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>res.vadoo@adaaran.com.mv</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
+          <t>+960 664 3976</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.adaaran.com/prestigevadoo/contact-us/</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K53" s="5" t="n">
+      <c r="N53" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L53" s="7" t="inlineStr">
+      <c r="O53" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M53" s="5" t="inlineStr">
+      <c r="P53" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -4029,21 +4869,21 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Angsana Velavaru</t>
+          <t>Anantara Kihavah</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Dhaalu</t>
+          <t>Baa</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Banyan Group</t>
+          <t>Minor Hotels</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
@@ -4057,28 +4897,43 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>angsana.com</t>
+          <t>anantara.com</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>kihavahmaldives@anantara.com</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
+          <t>+960 660 1020</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>https://www.anantara.com/en/kihavah-maldives/contact</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K54" s="5" t="n">
+      <c r="N54" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L54" s="7" t="inlineStr">
+      <c r="O54" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M54" s="5" t="inlineStr">
+      <c r="P54" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -4090,60 +4945,73 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Aura Maldives</t>
+          <t>Angsana Velavaru</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Baa</t>
+          <t>Dhaalu</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Doğrulanmalı</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>Doğrulanmalı</t>
-        </is>
+          <t>Banyan Group</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>113</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>2026 sonu açılış bekleniyor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>angsana.com</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Doğrulanmalı</t>
+          <t>reservations-velavaru@angsana.com</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
+          <t>+960 676 0028</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>Arama sonucu</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>https://www.angsana.com/maldives/velavaru/travel-information</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K55" s="5" t="n">
+      <c r="N55" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L55" s="7" t="inlineStr">
+      <c r="O55" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M55" s="5" t="inlineStr">
-        <is>
-          <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir</t>
+      <c r="P55" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -4153,58 +5021,75 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Baros Maldives</t>
+          <t>Aura Maldives</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Baa</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Universal Resorts</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>75</v>
+          <t>Doğrulanmalı</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Doğrulanmalı</t>
+        </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026 sonu açılış bekleniyor</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>baros.com</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>Bulunamadı (yeni proje / doğrulanmalı)</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K56" s="5" t="n">
+      <c r="N56" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L56" s="7" t="inlineStr">
+      <c r="O56" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M56" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P56" s="5" t="inlineStr">
+        <is>
+          <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir</t>
         </is>
       </c>
     </row>
@@ -4214,21 +5099,21 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Cinnamon Hakuraa Huraa</t>
+          <t>Baros Maldives</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Meemu</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Cinnamon Hotels (John Keells)</t>
+          <t>VERSA Hospitality</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
@@ -4242,28 +5127,43 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>cinnamonhotels.com</t>
+          <t>baros.com</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reservations@baros.com</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
+          <t>+960 664 2672</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>Arama sonucu (otel sitesi)</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>https://barosthn.emarketingeye.net/contact-us</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K57" s="5" t="n">
+      <c r="N57" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L57" s="7" t="inlineStr">
+      <c r="O57" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M57" s="5" t="inlineStr">
+      <c r="P57" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -4275,12 +5175,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Cinnamon Velifushi</t>
+          <t>Cinnamon Hakuraa Huraa</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Vaavu</t>
+          <t>Meemu</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -4289,7 +5189,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
@@ -4308,23 +5208,38 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>info@cinnamonhotels.com (merkez); sales.mv@cinnamonhotels.com</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
+          <t>+960 672 6000</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>Arama sonucu</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cinnamonhotels.com/cinnamon-hakuraa-huraa-maldives</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K58" s="5" t="n">
+      <c r="N58" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L58" s="7" t="inlineStr">
+      <c r="O58" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M58" s="5" t="inlineStr">
+      <c r="P58" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -4336,21 +5251,21 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Club Med Finolhu Villas</t>
+          <t>Cinnamon Velifushi</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Vaavu</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Club Med</t>
+          <t>Cinnamon Hotels (John Keells)</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
@@ -4359,33 +5274,48 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Kani ile aynı lagün</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>clubmed.com</t>
+          <t>cinnamonhotels.com</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>info@cinnamonhotels.com (merkez); sales.mv@cinnamonhotels.com</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
+          <t>+94 112 161 161 (merkez)</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>Otele özel bilgi bulunamadı</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cinnamonhotels.com/hotel-contact-information</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K59" s="5" t="n">
+      <c r="N59" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L59" s="7" t="inlineStr">
+      <c r="O59" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M59" s="5" t="inlineStr">
+      <c r="P59" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -4397,23 +5327,21 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Diğer Crown &amp; Champa resortları</t>
+          <t>Club Med Finolhu Villas</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Çeşitli</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Crown &amp; Champa Resorts</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>Doğrulanmalı</t>
-        </is>
+          <t>Club Med</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>50</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
@@ -4422,35 +5350,50 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Grup düzeyinde tek görüşme ile 7+ ada</t>
+          <t>Kani ile aynı lagün</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>crownandchamparesorts.com</t>
+          <t>clubmed.com</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>contactus.asia@clubmed.com (bölge merkezi)</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
+          <t>+960 664 4040</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>Club Med sitesi</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>https://www.clubmed.us/r/the-finolhu-villas/y</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K60" s="5" t="n">
+      <c r="N60" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L60" s="7" t="inlineStr">
+      <c r="O60" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M60" s="5" t="inlineStr">
-        <is>
-          <t>oda sayısı doğrulanmalı; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P60" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -4460,21 +5403,23 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Dusit Thani Maldives</t>
+          <t>Diğer Crown &amp; Champa resortları</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Baa</t>
+          <t>Çeşitli</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Dusit</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>100</v>
+          <t>Crown &amp; Champa Resorts</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Doğrulanmalı</t>
+        </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
@@ -4483,35 +5428,50 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Grup düzeyinde tek görüşme ile 7+ ada</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>dusit.com</t>
+          <t>crownandchamparesorts.com</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="J61" s="5" t="inlineStr">
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K61" s="5" t="n">
+      <c r="N61" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L61" s="7" t="inlineStr">
+      <c r="O61" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M61" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P61" s="5" t="inlineStr">
+        <is>
+          <t>oda sayısı doğrulanmalı; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -4521,21 +5481,21 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Ellaidhoo Maldives by Cinnamon</t>
+          <t>Dusit Thani Maldives</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Alif Alif (Kuzey Ari)</t>
+          <t>Baa</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Cinnamon Hotels (John Keells)</t>
+          <t>Dusit</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
@@ -4549,28 +5509,43 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>cinnamonhotels.com</t>
+          <t>dusit.com</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>resmaldives@dusit.com</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
+          <t>+960 660 8888</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dusit.com/dusitthani-maldives/contact-us/</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K62" s="5" t="n">
+      <c r="N62" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L62" s="7" t="inlineStr">
+      <c r="O62" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M62" s="5" t="inlineStr">
+      <c r="P62" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -4582,21 +5557,21 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Embudu Village</t>
+          <t>Ellaidhoo Maldives by Cinnamon</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Güney Malé)</t>
+          <t>Alif Alif (Kuzey Ari)</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Bağımsız</t>
+          <t>Cinnamon Hotels (John Keells)</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
@@ -4610,30 +5585,45 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>embudu.com</t>
+          <t>cinnamonhotels.com</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>info@cinnamonhotels.com (merkez); sales.mv@cinnamonhotels.com</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
+          <t>+94 112 161 161 (merkez)</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>Otele özel bilgi bulunamadı</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cinnamonhotels.com/hotel-contact-information</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K63" s="5" t="n">
+      <c r="N63" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L63" s="7" t="inlineStr">
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M63" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi</t>
+      <c r="P63" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -4643,17 +5633,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Emerald Maldives Resort</t>
+          <t>Embudu Village</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Raa</t>
+          <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Emerald Collection</t>
+          <t>Bağımsız</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
@@ -4671,28 +5661,43 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>emeraldmaldives.com</t>
+          <t>embudu.com</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>sales@embuduvillage.com</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
+          <t>+960 664 4776</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>https://www.embuduvillage.com/contact-us</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K64" s="5" t="n">
+      <c r="N64" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L64" s="7" t="inlineStr">
+      <c r="O64" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M64" s="5" t="inlineStr">
+      <c r="P64" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi</t>
         </is>
@@ -4704,7 +5709,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Faarufushi Maldives</t>
+          <t>Emerald Maldives Resort</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -4714,11 +5719,11 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Universal Resorts</t>
+          <t>Emerald Collection</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
@@ -4732,30 +5737,45 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>faarufushimaldives.com</t>
+          <t>emeraldmaldives.com</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reservations@emerald-maldives.com</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
+          <t>+960 658 2100</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>https://www.emerald-maldives.com/</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K65" s="5" t="n">
+      <c r="N65" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L65" s="7" t="inlineStr">
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M65" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P65" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi</t>
         </is>
       </c>
     </row>
@@ -4765,21 +5785,21 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Fun Island Resort</t>
+          <t>Faarufushi Maldives</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Güney Malé)</t>
+          <t>Raa</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Villa Hotels &amp; Resorts</t>
+          <t>Emerald Collection</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
@@ -4788,33 +5808,48 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Yeni adı Emerald Faarufushi</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>villaresorts.com</t>
+          <t>emerald-faarufushi.com</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reservations@emerald-faarufushi.com</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
+          <t>+960 658 8000</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>NOT: Yeni adı 'Emerald Faarufushi Resort &amp; Spa' (Emerald grubu) – işletmeci değişmiş</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>https://www.emerald-faarufushi.com/</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K66" s="5" t="n">
+      <c r="N66" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L66" s="7" t="inlineStr">
+      <c r="O66" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M66" s="5" t="inlineStr">
+      <c r="P66" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -4826,58 +5861,73 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Gili Lankanfushi</t>
+          <t>Fun Island Resort</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Bağımsız</t>
+          <t>Villa Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Kısmi GES, ESS yok/bilinmiyor</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>GES bilgisi var, kapsamı doğrulanmalı</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>gili-lankanfushi.com</t>
+          <t>villaresorts.com</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>hello@villaresorts.com (Villa Resorts genel)</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>Otele özel bilgi bulunamadı</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>https://villaresorts.com/contact/</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K67" s="5" t="n">
+      <c r="N67" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L67" s="7" t="inlineStr">
+      <c r="O67" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M67" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi</t>
+      <c r="P67" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -4887,7 +5937,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Grand Park Kodhipparu</t>
+          <t>Gili Lankanfushi</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -4897,48 +5947,63 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Park Hotel Group</t>
+          <t>Bağımsız</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GES bilgisi var, kapsamı doğrulanmalı</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>grandparkkodhipparu.com</t>
+          <t>gili-lankanfushi.com</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>mr.friday@gili-lankanfushi.com</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
+          <t>+960 664 0304</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi (genel misafir hattı)</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>https://gili-lankanfushi.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K68" s="5" t="n">
+      <c r="N68" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L68" s="7" t="inlineStr">
+      <c r="O68" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M68" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi</t>
+      <c r="P68" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi</t>
         </is>
       </c>
     </row>
@@ -4948,21 +6013,21 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>InterContinental Maamunagau</t>
+          <t>Grand Park Kodhipparu</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Raa</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>IHG markası</t>
+          <t>Park Hotel Group</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
@@ -4976,30 +6041,45 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>ihg.com</t>
+          <t>grandparkkodhipparu.com</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>info@grandparkkodhipparu.com; rsvn.gpkd@parkhotelgroup.com</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
+          <t>+960 665 1111</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>Arama sonucu</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>https://wetu.com/iBrochure/en/Information/141358/grand_park_kodhipparu/Contact</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K69" s="5" t="n">
+      <c r="N69" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L69" s="7" t="inlineStr">
+      <c r="O69" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M69" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P69" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi</t>
         </is>
       </c>
     </row>
@@ -5009,21 +6089,21 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Kandolhu Maldives</t>
+          <t>InterContinental Maamunagau</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Alif Alif (Kuzey Ari)</t>
+          <t>Raa</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Universal Resorts</t>
+          <t>IHG markası</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
@@ -5037,28 +6117,43 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>kandolhu.com</t>
+          <t>ihg.com</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>Intercontinental.Maldives@ihg.com</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
+          <t>+960 658 0500</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>https://maldives.intercontinental.com/contact-form/</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K70" s="5" t="n">
+      <c r="N70" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L70" s="7" t="inlineStr">
+      <c r="O70" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M70" s="5" t="inlineStr">
+      <c r="P70" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -5070,21 +6165,21 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Komandoo Island Resort</t>
+          <t>Kandolhu Maldives</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Lhaviyani</t>
+          <t>Alif Alif (Kuzey Ari)</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Kuredu (bağımsız grup)</t>
+          <t>VERSA Hospitality</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
@@ -5098,28 +6193,43 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>komandoo.com</t>
+          <t>kandolhu.com</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>info@kandolhu.com</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
+          <t>+960 668 0790</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kandolhu.com/contact.html</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K71" s="5" t="n">
+      <c r="N71" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L71" s="7" t="inlineStr">
+      <c r="O71" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M71" s="5" t="inlineStr">
+      <c r="P71" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -5131,21 +6241,21 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Milaidhoo Maldives</t>
+          <t>Komandoo Island Resort</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Baa</t>
+          <t>Lhaviyani</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Universal Resorts</t>
+          <t>Crown &amp; Champa (Kuredu Holdings)</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
@@ -5159,28 +6269,43 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>milaidhoo.com</t>
+          <t>komandoo.com</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reservations@komandoo.com</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
+          <t>+960 662 1010</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>https://www.komandoo.com/contact/</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K72" s="5" t="n">
+      <c r="N72" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L72" s="7" t="inlineStr">
+      <c r="O72" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M72" s="5" t="inlineStr">
+      <c r="P72" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -5192,60 +6317,73 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>RAH GILI MALDIVES</t>
+          <t>Milaidhoo Maldives</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Doğrulanmalı</t>
+          <t>Baa</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Bağımsız</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>Doğrulanmalı</t>
-        </is>
+          <t>VERSA Hospitality</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>50</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Kısmi GES, ESS yok/bilinmiyor</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Günlük ~17.000 kWh tüketim, ~8.000 kWh GES; yılda ~540.000 L dizel tasarrufu</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>rahgili.com</t>
+          <t>milaidhoo.com</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>welcome@milaidhoo.com</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
+          <t>+960 660 7788</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi (Universal Enterprises / VERSA)</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>https://www.milaidhoo.com/contact-us.html</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K73" s="5" t="n">
+      <c r="N73" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L73" s="7" t="inlineStr">
+      <c r="O73" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M73" s="5" t="inlineStr">
-        <is>
-          <t>oda sayısı doğrulanmalı; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi</t>
+      <c r="P73" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -5255,58 +6393,73 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Siyam World Maldives</t>
+          <t>Reethi Beach Resort</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Noonu</t>
+          <t>Baa</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Sun Siyam Resorts</t>
+          <t>NH Collection (Minor Hotels)</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>500</v>
+        <v>115</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>GES + ESS mevcut / sözleşmeli</t>
+          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>2025: GES (2,7 MW hedef) + 1.720 kWh ESS – Hayleys Fentons</t>
+          <t>Yeni adı NH Collection Maldives Reethi</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>siyamworld.com</t>
+          <t>nh-collection.com</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reethi@nhcollection.com</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
+          <t>+960 660 2626</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>NOT: Yeni adı 'NH Collection Maldives Reethi Resort' (Minor/NH)</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hotelcontact.net/reethi-beach-resort-maldives-baa-en.html</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K74" s="5" t="n">
+      <c r="N74" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L74" s="7" t="inlineStr">
+      <c r="O74" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M74" s="5" t="inlineStr">
-        <is>
-          <t>büyük resort (yüksek dizel tüketimi); rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P74" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -5316,12 +6469,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Sun Siyam Vilu Reef</t>
+          <t>Siyam World Maldives</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Dhaalu</t>
+          <t>Noonu</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -5330,44 +6483,59 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>GES + ESS mevcut / sözleşmeli</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Grup 2. faz adayı</t>
+          <t>2025: GES (2,7 MW hedef) + 1.720 kWh ESS – Hayleys Fentons</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>sunsiyam.com</t>
+          <t>siyamworld.com</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>book@sunsiyam.com (merkez)</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
+          <t>+960 656 7777</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi; otele özel e-posta gizlenmiş</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sunsiyam.com/siyam-world/contact-us/</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K75" s="5" t="n">
+      <c r="N75" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L75" s="7" t="inlineStr">
+      <c r="O75" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M75" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P75" s="5" t="inlineStr">
+        <is>
+          <t>büyük resort (yüksek dizel tüketimi); rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -5377,21 +6545,21 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Vilamendhoo Island Resort</t>
+          <t>Sun Siyam Vilu Reef</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Alif Dhaal (Güney Ari)</t>
+          <t>Dhaalu</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Bağımsız</t>
+          <t>Sun Siyam Resorts</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
@@ -5400,35 +6568,50 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Grup 2. faz adayı</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>vilamendhoo.com</t>
+          <t>sunsiyam.com</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>info.vilureef@sunsiyam.com</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
+          <t>+960 676 0011</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sunsiyam.com/sun-siyam-vilu-reef/contact-us/</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K76" s="5" t="n">
+      <c r="N76" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L76" s="7" t="inlineStr">
+      <c r="O76" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M76" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi</t>
+      <c r="P76" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -5438,21 +6621,21 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Ayada Maldives</t>
+          <t>Vilamendhoo Island Resort</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Gaafu Dhaalu</t>
+          <t>Alif Dhaal (Güney Ari)</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Bağımsız (Türk sermayeli)</t>
+          <t>Bağımsız</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
@@ -5461,35 +6644,50 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Türk bağlantısı – sıcak giriş fırsatı (doğrulanmalı)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>ayadamaldives.com</t>
+          <t>vilamendhoo.com</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reservations@vilamendhoo.com</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
+          <t>+960 668 0637</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vilamendhoo.com/contact-us.html</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K77" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L77" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M77" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi</t>
+      <c r="N77" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O77" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P77" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi</t>
         </is>
       </c>
     </row>
@@ -5532,23 +6730,38 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>biyadhoo@sunland.com.mv</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
+          <t>+960 664 7171</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>Arama sonucu (Sunland grubu)</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/ShowTopic-g298335-i9918-k6983585-How_to_contact_Biyadhoo_Island_Resort_in_Maldives-South_Male_Atoll.html</t>
+        </is>
+      </c>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K78" s="5" t="n">
+      <c r="N78" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="L78" s="8" t="inlineStr">
+      <c r="O78" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M78" s="5" t="inlineStr">
+      <c r="P78" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi</t>
         </is>
@@ -5593,23 +6806,38 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reservations@malahini.mv</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
+          <t>+960 664 4556</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi (malahini.mv)</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>https://malahini.mv/</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K79" s="5" t="n">
+      <c r="N79" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="L79" s="8" t="inlineStr">
+      <c r="O79" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M79" s="5" t="inlineStr">
+      <c r="P79" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi</t>
         </is>
@@ -5621,12 +6849,12 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Reethi Beach Resort</t>
+          <t>Summer Island Maldives</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Baa</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -5635,7 +6863,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
@@ -5649,28 +6877,43 @@
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>reethibeach.com</t>
+          <t>summerislandmaldives.com</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reservations@summerislandmaldives.com</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
+          <t>+960 664 1949</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>https://www.summerislandmaldives.com/contact-us</t>
+        </is>
+      </c>
+      <c r="M80" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K80" s="5" t="n">
+      <c r="N80" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="L80" s="8" t="inlineStr">
+      <c r="O80" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M80" s="5" t="inlineStr">
+      <c r="P80" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi</t>
         </is>
@@ -5682,58 +6925,73 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Summer Island Maldives</t>
+          <t>Sun Siyam Olhuveli</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Bağımsız</t>
+          <t>Sun Siyam Resorts</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
+          <t>GES + ESS mevcut / sözleşmeli</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2025: GES + 537,5 kWh ESS – Hayleys Fentons</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>summerislandmaldives.com</t>
+          <t>sunsiyam.com</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>ecommerce.olhuveli@sunsiyam.com</t>
         </is>
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
+          <t>+960 664 2788</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sunsiyam.com/sun-siyam-olhuveli/contact-us/</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K81" s="5" t="n">
+      <c r="N81" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="L81" s="8" t="inlineStr">
+      <c r="O81" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M81" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi</t>
+      <c r="P81" s="5" t="inlineStr">
+        <is>
+          <t>orta-büyük resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -5743,21 +7001,21 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Sun Siyam Olhuveli</t>
+          <t>Cheval Blanc Randheli</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Güney Malé)</t>
+          <t>Noonu</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Sun Siyam Resorts</t>
+          <t>LVMH</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>200</v>
+        <v>46</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
@@ -5766,35 +7024,50 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>2025: GES + 537,5 kWh ESS – Hayleys Fentons</t>
+          <t>Swimsol 2.421 kWp yüzer GES + 1.953 kWh ESS</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>sunsiyam.com</t>
+          <t>chevalblanc.com</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="J82" s="5" t="inlineStr">
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K82" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L82" s="8" t="inlineStr">
+      <c r="N82" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O82" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M82" s="5" t="inlineStr">
-        <is>
-          <t>orta-büyük resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P82" s="5" t="inlineStr">
+        <is>
+          <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
@@ -5804,21 +7077,21 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Cheval Blanc Randheli</t>
+          <t>Kudadoo Maldives Private Island</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Noonu</t>
+          <t>Lhaviyani</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>LVMH</t>
+          <t>Crown &amp; Champa Resorts</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
@@ -5827,33 +7100,48 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Swimsol 2.421 kWp yüzer GES + 1.953 kWh ESS</t>
+          <t>Tamamen güneş enerjili olarak tasarlandı</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>chevalblanc.com</t>
+          <t>kudadoo.com</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="J83" s="5" t="inlineStr">
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K83" s="5" t="n">
+      <c r="N83" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="L83" s="8" t="inlineStr">
+      <c r="O83" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M83" s="5" t="inlineStr">
+      <c r="P83" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -5865,21 +7153,21 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Kudadoo Maldives Private Island</t>
+          <t>Patina Maldives (Fari Islands)</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Lhaviyani</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Crown &amp; Champa Resorts</t>
+          <t>Pontiac Land</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
@@ -5888,33 +7176,48 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Tamamen güneş enerjili olarak tasarlandı</t>
+          <t>~3 MWp GES + 2 MWh ESS; Fari toplam 6,4 MW</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>kudadoo.com</t>
+          <t>patinahotels.com</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="J84" s="5" t="inlineStr">
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K84" s="5" t="n">
+      <c r="N84" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="L84" s="8" t="inlineStr">
+      <c r="O84" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M84" s="5" t="inlineStr">
+      <c r="P84" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -5926,21 +7229,21 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Patina Maldives (Fari Islands)</t>
+          <t>Soneva Fushi</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Baa</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Pontiac Land</t>
+          <t>Soneva</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
@@ -5949,33 +7252,48 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>~3 MWp GES + 2 MWh ESS; Fari toplam 6,4 MW</t>
+          <t>Canopy Power GES + ESS (~%60 yenilenebilir)</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>patinahotels.com</t>
+          <t>soneva.com</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="J85" s="5" t="inlineStr">
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M85" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K85" s="5" t="n">
+      <c r="N85" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="L85" s="8" t="inlineStr">
+      <c r="O85" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M85" s="5" t="inlineStr">
+      <c r="P85" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -5987,12 +7305,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Soneva Fushi</t>
+          <t>Soneva Jani</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Baa</t>
+          <t>Noonu</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -6001,7 +7319,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
@@ -6010,7 +7328,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Canopy Power GES + ESS (~%60 yenilenebilir)</t>
+          <t>Canopy Power GES + ESS</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
@@ -6020,23 +7338,38 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="J86" s="5" t="inlineStr">
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M86" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K86" s="5" t="n">
+      <c r="N86" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="L86" s="8" t="inlineStr">
+      <c r="O86" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M86" s="5" t="inlineStr">
+      <c r="P86" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -6048,12 +7381,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Soneva Jani</t>
+          <t>Soneva Secret</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Noonu</t>
+          <t>Haa Dhaalu</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -6062,7 +7395,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
@@ -6071,7 +7404,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Canopy Power GES + ESS</t>
+          <t>Canopy Power 2 MWp yüzer GES + 3 MWh Huawei ESS</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
@@ -6081,23 +7414,38 @@
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="J87" s="5" t="inlineStr">
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M87" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K87" s="5" t="n">
+      <c r="N87" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="L87" s="8" t="inlineStr">
+      <c r="O87" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M87" s="5" t="inlineStr">
+      <c r="P87" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -6109,21 +7457,21 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Soneva Secret</t>
+          <t>The Ritz-Carlton Maldives (Fari Islands)</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Haa Dhaalu</t>
+          <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Soneva</t>
+          <t>Pontiac Land / Marriott</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
@@ -6132,33 +7480,48 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Canopy Power 2 MWp yüzer GES + 3 MWh Huawei ESS</t>
+          <t>983 kW çatı GES; Fari ortak mikro şebeke</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>soneva.com</t>
+          <t>ritzcarlton.com</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="J88" s="5" t="inlineStr">
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K88" s="5" t="n">
+      <c r="N88" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="L88" s="8" t="inlineStr">
+      <c r="O88" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M88" s="5" t="inlineStr">
+      <c r="P88" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -6170,17 +7533,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>The Ritz-Carlton Maldives (Fari Islands)</t>
+          <t>Veligandu Maldives</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Kaafu (Kuzey Malé)</t>
+          <t>Alif Alif (Rasdhoo)</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Pontiac Land / Marriott</t>
+          <t>Crown &amp; Champa Resorts</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
@@ -6193,33 +7556,48 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>983 kW çatı GES; Fari ortak mikro şebeke</t>
+          <t>1.441 kW GES + 1.668 kWh ESS (Eyl. 2025)</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>ritzcarlton.com</t>
+          <t>veligandu.com</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
+          <t>+960 666 0519</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi; e-posta gizlenmiş</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>https://veligandu.com/contact/</t>
+        </is>
+      </c>
+      <c r="M89" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K89" s="5" t="n">
+      <c r="N89" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="L89" s="8" t="inlineStr">
+      <c r="O89" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M89" s="5" t="inlineStr">
+      <c r="P89" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -6231,21 +7609,23 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Veligandu Maldives</t>
+          <t>RAH GILI MALDIVES</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Alif Alif (Rasdhoo)</t>
+          <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Crown &amp; Champa Resorts</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="n">
-        <v>100</v>
+          <t>Bağımsız</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Doğrulanmalı</t>
+        </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
@@ -6254,35 +7634,50 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>1.441 kW GES + 1.668 kWh ESS (Eyl. 2025)</t>
+          <t>2 MW GES + 2.500 kWh ESS; günlük ~17.000 kWh tüketim</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>veligandu.com</t>
+          <t>rahgili.com</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
+          <t>reservations@rahgili.com</t>
         </is>
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
+          <t>+960 401 4001</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>Otelin kendi sitesi</t>
+        </is>
+      </c>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>https://rahgili.com/contact-us</t>
+        </is>
+      </c>
+      <c r="M90" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K90" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L90" s="8" t="inlineStr">
+      <c r="N90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M90" s="5" t="inlineStr">
-        <is>
-          <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
+      <c r="P90" s="5" t="inlineStr">
+        <is>
+          <t>oda sayısı doğrulanmalı; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis</t>
         </is>
       </c>
     </row>
@@ -6327,23 +7722,38 @@
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>Doğrulanmalı</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>Bulunamadı (yeni proje / doğrulanmalı)</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="K91" s="5" t="n">
+      <c r="N91" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L91" s="8" t="inlineStr">
+      <c r="O91" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M91" s="5" t="inlineStr">
+      <c r="P91" s="5" t="inlineStr">
         <is>
           <t>oda sayısı doğrulanmalı; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis</t>
         </is>
@@ -6363,7 +7773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6373,6 +7783,10 @@
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -6411,11 +7825,31 @@
           <t>Öncelik</t>
         </is>
       </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Merkez ofis e-posta (kurumsal)</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Merkez ofis telefon</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Adres</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Kaynak bağlantısı</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Universal Resorts</t>
+          <t>VERSA Hospitality (eski Universal Resorts)</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -6430,22 +7864,42 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Kuramathi, Kurumba, Velassaru, Baros, Dhigali</t>
+          <t>Niva Kuramathi, Niva Kurumba, Niva Velassaru, Niva Dhigali, Baros, Milaidhoo, Kandolhu</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Kuramathi'de kısmi GES; diğerlerinde kamuya açık GES bilgisi yok</t>
+          <t>Ekim 2025'te VERSA adını aldı, Niva markasını kurdu. Kuramathi'de kısmi GES; diğerlerinde kamuya açık GES bilgisi yok</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>universalresorts.com</t>
+          <t>versahospitality.com</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>— (web sitesindeki form)</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>39 Orchid Magu, Malé</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.versahospitality.com/</t>
         </is>
       </c>
     </row>
@@ -6467,12 +7921,12 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Sun Island, Paradise Island, Royal Island</t>
+          <t>Villa Park (eski Sun Island), Villa Nautica (eski Paradise Island), Royal Island</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Büyük, orta segment, dizel ağırlıklı; Villa Group'un kendi enerji/yakıt işi de var</t>
+          <t>Büyük, orta segment; Villa Park'ta 2.400+ panel var, batarya bilgisi yok</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -6483,6 +7937,26 @@
       <c r="G3" s="6" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>hello@villaresorts.com; sales@villaresorts.com</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>+960 334 4777</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Villa House, Kandi Dhonmanik Goalhi, Malé 20181</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>https://villaresorts.com/contact/</t>
         </is>
       </c>
     </row>
@@ -6522,6 +7996,26 @@
           <t>A</t>
         </is>
       </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>sales@sunsiyam.com; book@sunsiyam.com</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>+960 332 5977</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Sun Siyam Building, Boduthakurufaanu Magu, Malé 20066</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>https://prelive.sunsiyam.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -6541,12 +8035,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Veligandu, Hurawalhi, Kudadoo</t>
+          <t>Kuredu, Komandoo, Veligandu, Hurawalhi, Kudadoo, Vilamendhoo, Meeru (doğrulanmalı)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Veligandu tamamlandı; grubun diğer adaları sırada olabilir</t>
+          <t>Veligandu tamamlandı; Kuredu (380 oda) en büyük fırsat</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -6557,139 +8051,219 @@
       <c r="G5" s="6" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>info@crownandchamparesorts.com</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>+960 664 0219</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Champa Building 3. kat, Kandi Dhon Manik Goalhi, Malé 20187</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.crownandchamparesorts.com/inquire-now.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Atmosphere Core</t>
+          <t>Kuredu Holdings (Crown &amp; Champa ortağı)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Malé / Hindistan</t>
+          <t>Malé (Maldivli)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>9-10</t>
+          <t>2+</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Kanifushi, OZEN Reserve, OZEN LIFE, VARU, Amaraa Faru (2027)</t>
+          <t>Kuredu, Komandoo</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Çatı GES yaygın; ESS ilavesi ve yeni açılışlar fırsat</t>
+          <t>Kuredu ve Komandoo'nun sahibi; yeni resortlar geliştiriyor</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>atmospherecore.com</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>— (Crown &amp; Champa üzerinden)</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>M. Champa Building 4. kat, Kandi Dhon Manik Goalhi, Malé 20187</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>https://business.egov.mv/BusinessRegistry/ViewDetails/39070?key=-577025120</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Aitken Spence (Adaaran / Heritance)</t>
+          <t>Atmosphere Core</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Malé / Hindistan</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9-10</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Adaaran Hudhuranfushi, Rannalhi, Vadoo, Heritance Aarah</t>
+          <t>Kanifushi, OZEN Reserve, OZEN LIFE, VARU, Amaraa Faru (2027)</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Kamuya açık GES bilgisi sınırlı</t>
+          <t>Çatı GES yaygın; ESS ilavesi ve yeni açılışlar fırsat</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>aitkenspence.com</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>atmospherecore.com</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>info@atmospherecore.com</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>+960 330 0668</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Boduthakurufaanu Magu, Malé 20094</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.atmospherecore.com/contact-us</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Cinnamon Hotels (John Keells)</t>
+          <t>Aydeniz Grubu (TÜRK – Ayada Maldives sahibi)</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Ankara, Türkiye</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Dhonveli, Velifushi, Ellaidhoo, Hakuraa</t>
+          <t>Ayada Maldives</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Kamuya açık GES bilgisi sınırlı</t>
+          <t>Kamuya açık GES bilgisi yok. Türk sahipli: Türkçe ve doğrudan sahiple görüşme imkânı – İLK REFERANS İÇİN EN SICAK ADAY</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>cinnamonhotels.com</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>aydeniz.com</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>info@aydeniz.com</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>+90 312 212 6612</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Ayten Sok. No:9 Tandoğan 06580 Ankara</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>http://www.aydeniz.com/contact.htm</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Minor Hotels (Anantara)</t>
+          <t>Aitken Spence (Adaaran / Heritance)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bangkok, Tayland</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Anantara Dhigu/Veli/Naladhu, Kihavah</t>
+          <t>Adaaran Hudhuranfushi, Rannalhi, Vadoo, Heritance Aarah</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -6699,56 +8273,96 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>minorhotels.com</t>
+          <t>aitkenspencehotels.com</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
           <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>inquiries.mv@adaaran.com.mv</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>+960 664 0375</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>H. Thuniya 6. kat, Boduthakurufaanu Magu, Malé 20026</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.aitkenspencehotels.com/contact-us.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Pulse Hotels &amp; Resorts (Kandima)</t>
+          <t>Cinnamon Hotels (John Keells)</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Malé</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Kandima</t>
+          <t>Dhonveli, Velifushi, Ellaidhoo, Hakuraa</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Kamuya açık GES bilgisi yok</t>
+          <t>Kamuya açık GES bilgisi sınırlı</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>kandima.com</t>
+          <t>cinnamonhotels.com</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
           <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>sales.mv@cinnamonhotels.com</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>+960 333 6000</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>H. Maizan Building 2. kat, Sosun Magu, Malé 20252</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.maldivesyp.com/company/547/Cinnamon_Dhonveli_Maldives</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>CROSSROADS / Singha Estate</t>
+          <t>Minor Hotels (Anantara, NH Collection)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -6758,175 +8372,446 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>2 + marina</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Hard Rock, SAii Lagoon</t>
+          <t>Anantara Dhigu/Veli/Naladhu, Kihavah, NH Reethi</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Entegre ada kompleksi, tek enerji santrali</t>
+          <t>Kamuya açık GES bilgisi sınırlı. Malé adresi VERSA ile aynı – adaların sahibi VERSA olabilir (doğrulanmalı)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>crossroadsmaldives.com</t>
+          <t>minorhotels.com</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
           <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>reservations.maldives@anantara.com</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>+960 664 4123</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>39 Orchid Magu, Malé (VERSA ile aynı adres – mülk sahipliği bağlantısı doğrulanmalı)</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.minorhotels.com/en/reservations-offices</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Centara Hotels &amp; Resorts</t>
+          <t>Pulse Hotels &amp; Resorts (Kandima)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Bangkok, Tayland</t>
+          <t>Malé / Singapur</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>3+</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Centara Grand, Ras Fushi, Mirage</t>
+          <t>Kandima</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Centara Grand'da çatı GES -&gt; ESS ilavesi</t>
+          <t>Kamuya açık GES bilgisi yok. Mayıs 2026'da Director of Engineering ilanı açtı (yeni kişi göreve başlamış olabilir)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>centarahotelsresorts.com</t>
+          <t>kandima.com</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
           <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>KeepinTouch@pulseresorts.com</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>+65 6838 9123 (Singapur)</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Kaneeru Villa 4. kat, Orchid Magu, Malé 20212</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>https://kandima.com/en/explore/contact</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Pontiac Land (Fari Islands)</t>
+          <t>CROSSROADS / Singha Estate</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Singapur</t>
+          <t>Bangkok, Tayland</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>3 (Capella 2027)</t>
+          <t>2 + marina</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Patina, Ritz-Carlton, Capella</t>
+          <t>Hard Rock, SAii Lagoon</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Swimsol ile büyük GES+ESS – rakip tarafından alınmış</t>
+          <t>Entegre ada kompleksi, tek enerji santrali</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>fari-islands.com</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>crossroadsmaldives.com</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>sales@crossroadsmaldives.com</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>+960 665 1200</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>South Malé Atoll, P.O. Box 2097</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>https://crossroadsmaldives.com/contact-us/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Soneva</t>
+          <t>Centara Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Maldivler / Tayland</t>
+          <t>Bangkok, Tayland</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3+</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Soneva Fushi, Jani, Secret</t>
+          <t>Machchafushi (eski Centara Grand), Ras Fushi, Mirage Lagoon</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Canopy Power + Huawei ESS – rakip tarafından alınmış (referans vaka)</t>
+          <t>Machchafushi'de çatı GES -&gt; ESS ilavesi</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>soneva.com</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>centarahotelsresorts.com</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>Emerald Collection</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Doğrulanmalı</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Emerald Maldives, Emerald Faarufushi</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Kamuya açık GES bilgisi yok</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>emerald-maldives.com</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Pontiac Land (Fari Islands)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Singapur</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>3 (Capella 2027)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Patina, Ritz-Carlton, Capella</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Swimsol ile büyük GES+ESS – rakip tarafından alınmış</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>fari-islands.com</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Soneva</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Maldivler / Dubai</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Soneva Fushi, Jani, Secret</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Canopy Power + Huawei ESS – rakip tarafından alınmış (referans vaka)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>soneva.com</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
           <t>Marriott / Hilton / IHG / Four Seasons vb. küresel markalar</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Çeşitli</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Çok sayıda</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Waldorf, Conrad, Sheraton, Holiday Inn, Four Seasons</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Karar çoğunlukla mülk sahibi (owner) şirkette; marka sadece işletmeci. Owner şirket tespit edilmeli</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>B</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7385,7 +9270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -7641,25 +9526,106 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t>SunCore Energy</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Yerel GES firması (Maldivler)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Maldivli GES şirketi; 16+ yıllık proje yöneticisi var</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>suncore.mv</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Yerel ortak adayı</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Atoll Solar</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Yerel GES / yüzer GES</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Hotelier Maldives GM Forum 2026'da Ocean Sun ile lagün yüzer GES sunumu yaptı – resort yöneticilerine erişimi var</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Doğrulanmalı</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Yerel ortak adayı</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>DEIF</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Hibrit kontrol sistemi (Danimarka)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Maldivler'de bir lüks resortta dizel+GES+batarya hibrit kontrolünü yaptı; ESS entegrasyonunda teknik ortak</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>deif.com</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Teknik ortak</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
           <t>Elemental Water Makers</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Güneş enerjili su arıtma</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Resortlarda tuzdan arındırma en büyük elektrik yüklerinden biri</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>elementalwatermakers.com</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Tamamlayıcı ortak</t>
         </is>
@@ -7811,7 +9777,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Resort listeleri, yeni ada kiralamaları, istatistik</t>
+          <t>Resort listeleri, yeni ada kiralamaları, istatistik. Sitedeki 'Registered Facilities' listesi tüm resortların resmi telefon/e-posta bilgilerini içerir (PDF/CSV indirilebilir). Bakanlık: info@tourism.gov.mv, +960 332 3224</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">

--- a/Maldivler_Potansiyel_Musteri_Listesi.xlsx
+++ b/Maldivler_Potansiyel_Musteri_Listesi.xlsx
@@ -264,14 +264,15 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Ortaklar" displayName="Ortaklar" ref="A1:E13" headerRowCount="1">
-  <autoFilter ref="A1:E13"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Ortaklar" displayName="Ortaklar" ref="A1:F14" headerRowCount="1">
+  <autoFilter ref="A1:F14"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="Firma"/>
     <tableColumn id="2" name="Tür"/>
-    <tableColumn id="3" name="Neden uygun"/>
-    <tableColumn id="4" name="Web sitesi"/>
-    <tableColumn id="5" name="Not"/>
+    <tableColumn id="3" name="Bilinen marka tercihi (inverter/batarya)"/>
+    <tableColumn id="4" name="Karea / HYXI için değerlendirme"/>
+    <tableColumn id="5" name="Web sitesi"/>
+    <tableColumn id="6" name="Not"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
@@ -9270,14 +9271,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -9293,15 +9295,20 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Neden uygun</t>
+          <t>Bilinen marka tercihi (inverter/batarya)</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
+          <t>Karea / HYXI için değerlendirme</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
           <t>Web sitesi</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Not</t>
         </is>
@@ -9315,20 +9322,25 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>GES lideri / EPC</t>
+          <t>GES lideri / EPC (Avusturya, Malé'de yerleşik)</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>50+ resort müşterisi var; ESS ilavesi gereken GES'lerin çoğu onların. ESS tedarikçisi olarak yaklaşılabilir</t>
+          <t>Panel: kendi SolarSea sistemi. Batarya markası kamuya açık değil</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
+          <t>50+ resortta GES; Veligandu (1,7 MWh) ve RAH GILI (2,5 MWh) bataryalarını da kurdu. Batarya tedarikçisi olarak HYXI için en büyük potansiyel</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
           <t>swimsol.com</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Hem rakip hem müşteri olabilir</t>
         </is>
@@ -9337,268 +9349,318 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Ecogreen Maldives</t>
+          <t>Avi Technologies</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Yerel kurulumcu</t>
+          <t>Yerel EPC (2015)</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Tüm atollerde turnkey GES; yerel lisans ve saha ekibi</t>
+          <t>Kamuya açık marka bilgisi yok</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>ecogreenmaldives.com</t>
+          <t>GES + ESS + dizel entegrasyonu yapıyor (Haa Alif'te 14 adada 3,78 MWh ESS). 15+ MW kurulum. HYXI C&amp;I ESS için en uygun yerel ortak adayı</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Yerel ortak adayı</t>
+          <t>avitech.com.mv</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Yerel ortak – 1. öncelik</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Renewable Energy Maldives (REM)</t>
+          <t>Atoll Solar (Octopus Systems)</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Yerel kurulumcu</t>
+          <t>Yerel EPC, resort odaklı</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>2012'den beri yerel GES deneyimi</t>
+          <t>BYD ile çalışıyor</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Doğrulanmalı</t>
+          <t>Ana şirket Octopus Systems resortların sistem entegratörü, yani tüm resortlara zaten erişimi var. BYD'ye alternatif ikinci marka olarak HYXI sunulabilir</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Yerel ortak adayı</t>
+          <t>atollsolar.com</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Yerel ortak – 1. öncelik</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Avi Technologies</t>
+          <t>Ecogreen Maldives</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Kurulumcu</t>
+          <t>Yerel kurulumcu (2014)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Batarya entegrasyonu odaklı</t>
+          <t>Kamuya açık marka bilgisi yok</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Doğrulanmalı</t>
+          <t>Resort, misafirhane, konut ve tekne GES. Ağırlıklı olarak küçük/orta ölçek</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Ortak adayı</t>
+          <t>ecogreenmaldives.com</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Yerel ortak adayı</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Solar Atolls / Atoll Solar / AOI Utopia</t>
+          <t>Renewable Energy Maldives (REM)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Yerel kurulumcular</t>
+          <t>Yerel kurulumcu (2006)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>ENF Solar dizininde Maldivler kurulumcuları</t>
+          <t>Sri Lanka kolu (REM Lanka) SolaX kullanıyor</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>enfsolar.com/directory/installer/Maldives</t>
+          <t>~25 ada ve resortlarla çalışmış eski oyuncu</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Ön eleme yapılmalı</t>
+          <t>LinkedIn: REM Solar</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Yerel ortak adayı</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Hayleys Fentons</t>
+          <t>SunCore Energy</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Bölgesel EPC (Sri Lanka)</t>
+          <t>Yerel GES firması</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Maldivler resort referansı (Sun Siyam) var; ürün tedarikçisi arıyor olabilir</t>
+          <t>Kamuya açık marka bilgisi yok</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>fentons.lk (doğrulanmalı)</t>
+          <t>16+ yıllık proje direktörü; kamu ve kurumsal projeler</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Ortak veya rakip</t>
+          <t>suncore.mv</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Yerel ortak adayı</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Canopy Power</t>
+          <t>Hayleys Fentons / Hayleys Solar</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Mikro şebeke EPC (Singapur)</t>
+          <t>Bölgesel EPC (Sri Lanka, 500+ MW)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Resort mikro şebeke uzmanı; Huawei ile çalışıyor</t>
+          <t>HUAWEI kullanıyor (inverter tedarikçileri arasında; Hayleys Electronics Huawei ile ortak forum yaptı); BYD batarya ortağı</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>canopypower.com</t>
+          <t>Sun Siyam projesinin yüklenicisi. Huawei kanalında oldukları için HYXI'ye geçmeleri zor; Huawei tarafında ise bölgesel rakip/kanal</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Huawei kanalı ile çakışma kontrol edilmeli</t>
+          <t>hayleysfentons.com</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Huawei kullanıcısı</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Resort jeneratör bakım/servis firmaları</t>
+          <t>Canopy Power</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>O&amp;M</t>
+          <t>Mikro şebeke EPC (Singapur)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Her resortun enerji santraline zaten erişimleri var; hibrit kontrol entegrasyonu için kritik</t>
+          <t>HUAWEI ESS (Soneva Secret 3 MWh)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Saha ziyaretinde tespit edilecek</t>
+          <t>Huawei kanalında</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Cummins, MTU, Caterpillar yerel bayileri</t>
+          <t>canopypower.com</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Huawei kullanıcısı</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SunCore Energy</t>
+          <t>Solmacher Solar Energy</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Yerel GES firması (Maldivler)</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Maldivli GES şirketi; 16+ yıllık proje yöneticisi var</t>
+          <t>HUAWEI (Royal Rosewood 40 MWh ESS + inverter, Ağu. 2026)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>suncore.mv</t>
+          <t>Huawei'nin Maldivler'deki en büyük projesi bu firmada</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Yerel ortak adayı</t>
+          <t>Doğrulanmalı</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Huawei kullanıcısı</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Atoll Solar</t>
+          <t>SINOSOAR</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Yerel GES / yüzer GES</t>
+          <t>Çin EPC – kamu hibrit projeleri</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Hotelier Maldives GM Forum 2026'da Ocean Sun ile lagün yüzer GES sunumu yaptı – resort yöneticilerine erişimi var</t>
+          <t>Kendi PCS/EMS'i; Sungrow ile bağlantılı</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Doğrulanmalı</t>
+          <t>134 adada kamu mikro şebeke projesi (ADB/ASSURE 40 MWh dahil). Kamu ihaleleri tarafında güçlü rakip</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Yerel ortak adayı</t>
+          <t>sinosoarhybrid.com</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Rakip (kamu)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>DEIF</t>
+          <t>Resort jeneratör bakım/servis firmaları</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Hibrit kontrol sistemi (Danimarka)</t>
+          <t>O&amp;M</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Maldivler'de bir lüks resortta dizel+GES+batarya hibrit kontrolünü yaptı; ESS entegrasyonunda teknik ortak</t>
+          <t>Cummins, MTU, Caterpillar yerel bayileri</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>deif.com</t>
+          <t>Her resortun enerji santraline zaten erişimleri var; hibrit kontrol entegrasyonu için kritik</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Saha ziyaretinde tespit edilecek</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Teknik ortak</t>
         </is>
@@ -9607,25 +9669,62 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>DEIF</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Hibrit kontrol sistemi (Danimarka)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Maldivler'de bir lüks resortta dizel+GES+batarya kontrolünü yaptı; ESS entegrasyonunda teknik ortak</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>deif.com</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Teknik ortak</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
           <t>Elemental Water Makers</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Güneş enerjili su arıtma</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Resortlarda tuzdan arındırma en büyük elektrik yüklerinden biri</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>elementalwatermakers.com</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Tamamlayıcı ortak</t>
         </is>

--- a/Maldivler_Potansiyel_Musteri_Listesi.xlsx
+++ b/Maldivler_Potansiyel_Musteri_Listesi.xlsx
@@ -831,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1362,36 +1362,506 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2. tur</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Villa Hotels &amp; Resorts (Villa Group)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – grup merkezi</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>sales@villaresorts.com</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – battery storage for Villa Park's existing solar</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2. tur</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Crown &amp; Champa Resorts</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – grup merkezi</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>info@crownandchamparesorts.com</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for your next resorts after Veligandu</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2. tur</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Atmosphere Core</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – grup merkezi</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>info@atmospherecore.com</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Technical Services – battery storage for your resorts and Amaraa Faru</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2. tur</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Sun Siyam Resorts</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – grup merkezi</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>sales@sunsiyam.com</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – next phase of your 2030 renewable target</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2. tur</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Adaaran / Aitken Spence (Malé ofisi)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – grup merkezi</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>inquiries.mv@adaaran.com.mv</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – reducing diesel costs at your Maldives resorts</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2. tur</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Cinnamon Hotels – John Keells Maldivian Resorts</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – grup merkezi</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>sales.mv@cinnamonhotels.com</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for your Maldives resorts</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2. tur</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>CROSSROADS Maldives (Singha Estate)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – grup merkezi</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>sales@crossroadsmaldives.com</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for the CROSSROADS islands</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2. tur</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Kandima / Pulse Hotels &amp; Resorts</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – grup merkezi</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>KeepinTouch@pulseresorts.com</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Kandima Maldives</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2. tur</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Meeru Maldives Resort Island</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>reservations@meeru.com</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Chief Engineer – solar and storage for Meeru</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2. tur</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Canareef Resort Maldives</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>info@canareef.com</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – battery storage for your rooftop solar</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Renkler:</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Mail gönderildi</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Yanıt geldi</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Görüşme planlandı</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>İlgilenmiyor</t>
         </is>
@@ -1903,68 +2373,68 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Canareef Resort Maldives</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Addu</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Bağımsız</t>
         </is>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="5" t="n">
         <v>280</v>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Büyük çatı GES kurulumu duyuruldu</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>canareef.com</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>info@canareef.com</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>+960 689 6677</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>https://canareef.com/contact-us/</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N7" s="11" t="n">
+      <c r="N7" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O7" s="12" t="inlineStr">
@@ -1972,9 +2442,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>büyük resort (yüksek dizel tüketimi); GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -2131,68 +2606,68 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Kandima Maldives</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Dhaalu</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Pulse Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="5" t="n">
         <v>266</v>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>kandima.com</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>mykindofplace@kandima.com; reservations@kandima.com</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>+960 676 0077</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>Otel rehberi / arama sonucu</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>https://www.maldivesyp.com/company/638/Kandima_Maldives</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N10" s="11" t="n">
+      <c r="N10" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O10" s="12" t="inlineStr">
@@ -2200,9 +2675,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="P10" s="11" t="inlineStr">
+      <c r="P10" s="5" t="inlineStr">
         <is>
           <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -4113,68 +4593,68 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n">
+      <c r="A36" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Meeru Maldives Resort Island</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Bağımsız (Maldivli)</t>
         </is>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="5" t="n">
         <v>286</v>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>meeru.com</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>reservations@meeru.com</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>+960 664 3157</t>
         </is>
       </c>
-      <c r="K36" s="11" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L36" s="11" t="inlineStr">
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>https://www.meeru.com/one-island-one-resort-contact-us/</t>
         </is>
       </c>
-      <c r="M36" s="11" t="inlineStr">
+      <c r="M36" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N36" s="11" t="n">
+      <c r="N36" s="5" t="n">
         <v>5</v>
       </c>
       <c r="O36" s="13" t="inlineStr">
@@ -4182,9 +4662,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P36" s="11" t="inlineStr">
+      <c r="P36" s="5" t="inlineStr">
         <is>
           <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi</t>
+        </is>
+      </c>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -8531,32 +9016,32 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Villa Hotels &amp; Resorts (Villa Group)</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Malé (Maldivli)</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>5+</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Villa Park (eski Sun Island), Villa Nautica (eski Paradise Island), Royal Island</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Büyük, orta segment; Villa Park'ta 2.400+ panel var, batarya bilgisi yok</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>villaresorts.com</t>
         </is>
@@ -8566,54 +9051,59 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>hello@villaresorts.com; sales@villaresorts.com</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>+960 334 4777</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Villa House, Kandi Dhonmanik Goalhi, Malé 20181</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://villaresorts.com/contact/</t>
         </is>
       </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Sun Siyam Resorts</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Malé (Maldivli)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Siyam World, Olhuveli, Iru Fushi, Iru Veli, Vilu Reef</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2 resortta GES+ESS (Hayleys Fentons); %50 yenilenebilir @2030 hedefi -&gt; kalan 3 resort için 2. faz</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>sunsiyam.com</t>
         </is>
@@ -8623,54 +9113,59 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>sales@sunsiyam.com; book@sunsiyam.com</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>+960 332 5977</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Sun Siyam Building, Boduthakurufaanu Magu, Malé 20066</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://prelive.sunsiyam.com/contact/</t>
         </is>
       </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Crown &amp; Champa Resorts</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Malé (Maldivli)</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Kuredu, Komandoo, Veligandu, Hurawalhi, Kudadoo, Vilamendhoo, Meeru (doğrulanmalı)</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Veligandu tamamlandı; Kuredu (380 oda) en büyük fırsat</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>crownandchamparesorts.com</t>
         </is>
@@ -8680,24 +9175,29 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>info@crownandchamparesorts.com</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>+960 664 0219</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Champa Building 3. kat, Kandi Dhon Manik Goalhi, Malé 20187</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://www.crownandchamparesorts.com/inquire-now.html</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -8759,32 +9259,32 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Atmosphere Core</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Malé / Hindistan</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>9-10</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Kanifushi, OZEN Reserve, OZEN LIFE, VARU, Amaraa Faru (2027)</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Çatı GES yaygın; ESS ilavesi ve yeni açılışlar fırsat</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>atmospherecore.com</t>
         </is>
@@ -8794,24 +9294,29 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>info@atmospherecore.com</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>+960 330 0668</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Boduthakurufaanu Magu, Malé 20094</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://www.atmospherecore.com/contact-us</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -8878,32 +9383,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Aitken Spence (Adaaran / Heritance)</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Colombo, Sri Lanka</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Adaaran Hudhuranfushi, Rannalhi, Vadoo, Heritance Aarah</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Kamuya açık GES bilgisi sınırlı</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>aitkenspencehotels.com</t>
         </is>
@@ -8913,54 +9418,59 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>inquiries.mv@adaaran.com.mv</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>+960 664 0375</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>H. Thuniya 6. kat, Boduthakurufaanu Magu, Malé 20026</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://www.aitkenspencehotels.com/contact-us.html</t>
         </is>
       </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Cinnamon Hotels (John Keells)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Colombo, Sri Lanka</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Dhonveli, Velifushi, Ellaidhoo, Hakuraa</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Kamuya açık GES bilgisi sınırlı</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>cinnamonhotels.com</t>
         </is>
@@ -8970,24 +9480,29 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>sales.mv@cinnamonhotels.com</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>+960 333 6000</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>H. Maizan Building 2. kat, Sosun Magu, Malé 20252</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://www.maldivesyp.com/company/547/Cinnamon_Dhonveli_Maldives</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -9049,32 +9564,32 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Pulse Hotels &amp; Resorts (Kandima)</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Malé / Singapur</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Kandima</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Kamuya açık GES bilgisi yok. Mayıs 2026'da Director of Engineering ilanı açtı (yeni kişi göreve başlamış olabilir)</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>kandima.com</t>
         </is>
@@ -9084,54 +9599,59 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>KeepinTouch@pulseresorts.com</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>+65 6838 9123 (Singapur)</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Kaneeru Villa 4. kat, Orchid Magu, Malé 20212</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>https://kandima.com/en/explore/contact</t>
         </is>
       </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>CROSSROADS / Singha Estate</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Bangkok, Tayland</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>2 + marina</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Hard Rock, SAii Lagoon</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Entegre ada kompleksi, tek enerji santrali</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>crossroadsmaldives.com</t>
         </is>
@@ -9141,24 +9661,29 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>sales@crossroadsmaldives.com</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>+960 665 1200</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>South Malé Atoll, P.O. Box 2097</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>https://crossroadsmaldives.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>

--- a/Maldivler_Potansiyel_Musteri_Listesi.xlsx
+++ b/Maldivler_Potansiyel_Musteri_Listesi.xlsx
@@ -831,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2302,36 +2302,1399 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Anantara Kihavah Maldives Villas</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>kihavahmaldives@anantara.com</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Anantara Kihavah</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Sheraton Maldives Full Moon</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>sheraton.maldives@sheraton.com</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Sheraton Maldives Full Moon</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Six Senses Laamu</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>reservations-laamu@sixsenses.com</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Six Senses Laamu</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Six Senses Kanuhura</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>reservations-maldives@sixsenses.com</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Six Senses Kanuhura</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Dusit Thani Maldives</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>resmaldives@dusit.com</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Dusit Thani Maldives</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Grand Park Kodhipparu</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>info@grandparkkodhipparu.com</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Grand Park Kodhipparu</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>InterContinental Maldives Maamunagau</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Intercontinental.Maldives@ihg.com</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for InterContinental Maldives Maamunagau</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Summer Island Maldives</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>reservations@summerislandmaldives.com</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Summer Island Maldives</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Embudu Village</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>sales@embuduvillage.com</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Embudu Village</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Biyadhoo Island Resort</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>biyadhoo@sunland.com.mv</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Biyadhoo Island Resort</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Malahini Kuda Bandos</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>reservations@malahini.mv</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Malahini Kuda Bandos</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>NH Collection Maldives Reethi</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>reethi@nhcollection.com</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for NH Collection Maldives Reethi</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Gili Lankanfushi</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>mr.friday@gili-lankanfushi.com</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Gili Lankanfushi</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Baros Maldives (VERSA)</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>reservations@baros.com</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Baros Maldives</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Milaidhoo Maldives (VERSA)</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>welcome@milaidhoo.com</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Milaidhoo Maldives</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Kandolhu Maldives (VERSA)</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>info@kandolhu.com</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Kandolhu Maldives</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Angsana Velavaru</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>reservations-velavaru@angsana.com</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Angsana Velavaru</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Club Med Kani &amp; Finolhu Villas</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>contactus.asia@clubmed.com</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Club Med Kani and Finolhu Villas</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Centara Maldives (Ras Fushi, Machchafushi, Mirage Lagoon)</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>crf@chr.co.th</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Centara Maldives</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Fairmont Maldives Sirru Fen Fushi</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>reservations@sirrufenfushi.com</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Sirru Fen Fushi</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Lily Beach Resort &amp; Spa</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>reservations@lilybeachmaldives.com</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Lily Beach Resort</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Radisson Blu Resort Maldives</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>info.maldives@radisson.com</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Radisson Blu Resort Maldives</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Pullman Maldives Maamutaa</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>H9924-re@accor.com</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Pullman Maldives Maamutaa</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Mercure Maldives Kooddoo</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>H9923@accor.com</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Mercure Maldives Kooddoo</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>OUTRIGGER Maldives Maafushivaru</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>maldives.maafushivaru@outrigger.com</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for OUTRIGGER Maldives Maafushivaru</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Hideaway Beach Resort &amp; Spa</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>reservations@hideawaybeachmaldives.com</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Hideaway Beach Resort</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>The Westin Maldives Miriandhoo</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>mlewi.reservation@westinhotels.com</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for The Westin Maldives Miriandhoo</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>JW Marriott Maldives Resort &amp; Spa</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>jwmaldivesreservations@marriott.com</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for JW Marriott Maldives</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>4. tur</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Jumeirah Maldives Olhahali Island</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Son kullanıcı – resort</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>reservations@jumeirah.com</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Attn: Engineering – solar and storage for Jumeirah Maldives Olhahali Island</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>Yanıt yoksa nazik hatırlatma maili</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>Renkler:</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>Mail gönderildi</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>Yanıt geldi</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>Görüşme planlandı</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>İlgilenmiyor</t>
         </is>
@@ -2934,68 +4297,68 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Club Med Kani</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Club Med</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>clubmed.com</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>+960 664 3152</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>E-posta sayfada gizlenmiş; Club Med merkezi üzerinden</t>
         </is>
       </c>
-      <c r="L8" s="12" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>https://www.hotelcontact.net/club-med-kani-maldives-north-male-en.html</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N8" s="12" t="n">
+      <c r="N8" s="5" t="n">
         <v>6</v>
       </c>
       <c r="O8" s="11" t="inlineStr">
@@ -3003,9 +4366,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="P8" s="12" t="inlineStr">
+      <c r="P8" s="5" t="inlineStr">
         <is>
           <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -4176,68 +5544,68 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Centara Grand Island Resort</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Alif Dhaal (Güney Ari)</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Centara Hotels</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="5" t="n">
         <v>112</v>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Yeni adı Machchafushi Island Resort (Centara Collection); tüm çatılarda GES</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>centarahotelsresorts.com</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J24" s="12" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>+960 668 8000</t>
         </is>
       </c>
-      <c r="K24" s="12" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>NOT: Yeni adı 'Machchafushi Island Resort &amp; Spa, The Centara Collection'; e-posta sayfada gizlenmiş</t>
         </is>
       </c>
-      <c r="L24" s="12" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>https://www.centarahotelsresorts.com/centaragrand/cirm/contact/</t>
         </is>
       </c>
-      <c r="M24" s="12" t="inlineStr">
+      <c r="M24" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N24" s="12" t="n">
+      <c r="N24" s="5" t="n">
         <v>5</v>
       </c>
       <c r="O24" s="13" t="inlineStr">
@@ -4245,75 +5613,80 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P24" s="12" t="inlineStr">
+      <c r="P24" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Centara Ras Fushi</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Centara Hotels</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>centarahotelsresorts.com</t>
         </is>
       </c>
-      <c r="I25" s="12" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>crf@chr.co.th</t>
         </is>
       </c>
-      <c r="J25" s="12" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>+960 664 3880</t>
         </is>
       </c>
-      <c r="K25" s="12" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L25" s="12" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>https://www.centarahotelsresorts.com/centara/CRF/contact</t>
         </is>
       </c>
-      <c r="M25" s="12" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N25" s="12" t="n">
+      <c r="N25" s="5" t="n">
         <v>5</v>
       </c>
       <c r="O25" s="13" t="inlineStr">
@@ -4321,9 +5694,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P25" s="12" t="inlineStr">
+      <c r="P25" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+        </is>
+      </c>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -5723,68 +7101,68 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="n">
+      <c r="A44" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Sheraton Maldives Full Moon</t>
         </is>
       </c>
-      <c r="C44" s="12" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Marriott markası</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="5" t="n">
         <v>176</v>
       </c>
-      <c r="F44" s="12" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>marriott.com</t>
         </is>
       </c>
-      <c r="I44" s="12" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>sheraton.maldives@sheraton.com</t>
         </is>
       </c>
-      <c r="J44" s="12" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>+960 664 2010</t>
         </is>
       </c>
-      <c r="K44" s="12" t="inlineStr">
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>Otel rehberi / arama sonucu</t>
         </is>
       </c>
-      <c r="L44" s="12" t="inlineStr">
+      <c r="L44" s="5" t="inlineStr">
         <is>
           <t>https://www.hotelcontact.net/sheraton-maldives-full-moon-resort-spa-vihamanaafushi-en.html</t>
         </is>
       </c>
-      <c r="M44" s="12" t="inlineStr">
+      <c r="M44" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N44" s="12" t="n">
+      <c r="N44" s="5" t="n">
         <v>5</v>
       </c>
       <c r="O44" s="13" t="inlineStr">
@@ -5792,75 +7170,80 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P44" s="12" t="inlineStr">
+      <c r="P44" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="n">
+      <c r="A45" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Six Senses Laamu</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>Laamu</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Six Senses (IHG)</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Sürdürülebilirlik odaklı; GES bilgisi var, kapsamı doğrulanmalı</t>
         </is>
       </c>
-      <c r="H45" s="12" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>sixsenses.com</t>
         </is>
       </c>
-      <c r="I45" s="12" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>reservations-laamu@sixsenses.com</t>
         </is>
       </c>
-      <c r="J45" s="12" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>+960 680 0800</t>
         </is>
       </c>
-      <c r="K45" s="12" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>Arama sonucu</t>
         </is>
       </c>
-      <c r="L45" s="12" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>https://wetu.com/iBrochure/en/Information/63679/six_senses_laamu/Contact</t>
         </is>
       </c>
-      <c r="M45" s="12" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N45" s="12" t="n">
+      <c r="N45" s="5" t="n">
         <v>5</v>
       </c>
       <c r="O45" s="13" t="inlineStr">
@@ -5868,9 +7251,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P45" s="12" t="inlineStr">
+      <c r="P45" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+        </is>
+      </c>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -6495,68 +7883,68 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="n">
+      <c r="A54" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>Anantara Kihavah</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>Baa</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>Minor Hotels</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="F54" s="12" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G54" s="12" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H54" s="12" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>anantara.com</t>
         </is>
       </c>
-      <c r="I54" s="12" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>kihavahmaldives@anantara.com</t>
         </is>
       </c>
-      <c r="J54" s="12" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>+960 660 1020</t>
         </is>
       </c>
-      <c r="K54" s="12" t="inlineStr">
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L54" s="12" t="inlineStr">
+      <c r="L54" s="5" t="inlineStr">
         <is>
           <t>https://www.anantara.com/en/kihavah-maldives/contact</t>
         </is>
       </c>
-      <c r="M54" s="12" t="inlineStr">
+      <c r="M54" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N54" s="12" t="n">
+      <c r="N54" s="5" t="n">
         <v>4</v>
       </c>
       <c r="O54" s="13" t="inlineStr">
@@ -6564,75 +7952,80 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P54" s="12" t="inlineStr">
+      <c r="P54" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
+      <c r="Q54" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="n">
+      <c r="A55" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Angsana Velavaru</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>Dhaalu</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>Banyan Group</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="5" t="n">
         <v>113</v>
       </c>
-      <c r="F55" s="12" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G55" s="12" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H55" s="12" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>angsana.com</t>
         </is>
       </c>
-      <c r="I55" s="12" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>reservations-velavaru@angsana.com</t>
         </is>
       </c>
-      <c r="J55" s="12" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>+960 676 0028</t>
         </is>
       </c>
-      <c r="K55" s="12" t="inlineStr">
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>Arama sonucu</t>
         </is>
       </c>
-      <c r="L55" s="12" t="inlineStr">
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>https://www.angsana.com/maldives/velavaru/travel-information</t>
         </is>
       </c>
-      <c r="M55" s="12" t="inlineStr">
+      <c r="M55" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N55" s="12" t="n">
+      <c r="N55" s="5" t="n">
         <v>4</v>
       </c>
       <c r="O55" s="13" t="inlineStr">
@@ -6640,9 +8033,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P55" s="12" t="inlineStr">
+      <c r="P55" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+        </is>
+      </c>
+      <c r="Q55" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -6725,68 +8123,68 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="n">
+      <c r="A57" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Baros Maldives</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>VERSA Hospitality</t>
         </is>
       </c>
-      <c r="E57" s="12" t="n">
+      <c r="E57" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="F57" s="12" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G57" s="12" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H57" s="12" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <t>baros.com</t>
         </is>
       </c>
-      <c r="I57" s="12" t="inlineStr">
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>reservations@baros.com</t>
         </is>
       </c>
-      <c r="J57" s="12" t="inlineStr">
+      <c r="J57" s="5" t="inlineStr">
         <is>
           <t>+960 664 2672</t>
         </is>
       </c>
-      <c r="K57" s="12" t="inlineStr">
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>Arama sonucu (otel sitesi)</t>
         </is>
       </c>
-      <c r="L57" s="12" t="inlineStr">
+      <c r="L57" s="5" t="inlineStr">
         <is>
           <t>https://barosthn.emarketingeye.net/contact-us</t>
         </is>
       </c>
-      <c r="M57" s="12" t="inlineStr">
+      <c r="M57" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N57" s="12" t="n">
+      <c r="N57" s="5" t="n">
         <v>4</v>
       </c>
       <c r="O57" s="13" t="inlineStr">
@@ -6794,9 +8192,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P57" s="12" t="inlineStr">
+      <c r="P57" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+        </is>
+      </c>
+      <c r="Q57" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -6953,68 +8356,68 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="12" t="n">
+      <c r="A60" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Club Med Finolhu Villas</t>
         </is>
       </c>
-      <c r="C60" s="12" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Club Med</t>
         </is>
       </c>
-      <c r="E60" s="12" t="n">
+      <c r="E60" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="F60" s="12" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>Kani ile aynı lagün</t>
         </is>
       </c>
-      <c r="H60" s="12" t="inlineStr">
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>clubmed.com</t>
         </is>
       </c>
-      <c r="I60" s="12" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>contactus.asia@clubmed.com (bölge merkezi)</t>
         </is>
       </c>
-      <c r="J60" s="12" t="inlineStr">
+      <c r="J60" s="5" t="inlineStr">
         <is>
           <t>+960 664 4040</t>
         </is>
       </c>
-      <c r="K60" s="12" t="inlineStr">
+      <c r="K60" s="5" t="inlineStr">
         <is>
           <t>Club Med sitesi</t>
         </is>
       </c>
-      <c r="L60" s="12" t="inlineStr">
+      <c r="L60" s="5" t="inlineStr">
         <is>
           <t>https://www.clubmed.us/r/the-finolhu-villas/y</t>
         </is>
       </c>
-      <c r="M60" s="12" t="inlineStr">
+      <c r="M60" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N60" s="12" t="n">
+      <c r="N60" s="5" t="n">
         <v>4</v>
       </c>
       <c r="O60" s="13" t="inlineStr">
@@ -7022,9 +8425,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P60" s="12" t="inlineStr">
+      <c r="P60" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+        </is>
+      </c>
+      <c r="Q60" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -7107,68 +8515,68 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="n">
+      <c r="A62" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>Dusit Thani Maldives</t>
         </is>
       </c>
-      <c r="C62" s="12" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Baa</t>
         </is>
       </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Dusit</t>
         </is>
       </c>
-      <c r="E62" s="12" t="n">
+      <c r="E62" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="F62" s="12" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G62" s="12" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H62" s="12" t="inlineStr">
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>dusit.com</t>
         </is>
       </c>
-      <c r="I62" s="12" t="inlineStr">
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>resmaldives@dusit.com</t>
         </is>
       </c>
-      <c r="J62" s="12" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>+960 660 8888</t>
         </is>
       </c>
-      <c r="K62" s="12" t="inlineStr">
+      <c r="K62" s="5" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L62" s="12" t="inlineStr">
+      <c r="L62" s="5" t="inlineStr">
         <is>
           <t>https://www.dusit.com/dusitthani-maldives/contact-us/</t>
         </is>
       </c>
-      <c r="M62" s="12" t="inlineStr">
+      <c r="M62" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N62" s="12" t="n">
+      <c r="N62" s="5" t="n">
         <v>4</v>
       </c>
       <c r="O62" s="13" t="inlineStr">
@@ -7176,9 +8584,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P62" s="12" t="inlineStr">
+      <c r="P62" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+        </is>
+      </c>
+      <c r="Q62" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -7259,68 +8672,68 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="n">
+      <c r="A64" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Embudu Village</t>
         </is>
       </c>
-      <c r="C64" s="12" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Bağımsız</t>
         </is>
       </c>
-      <c r="E64" s="12" t="n">
+      <c r="E64" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="F64" s="12" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G64" s="12" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr">
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>embudu.com</t>
         </is>
       </c>
-      <c r="I64" s="12" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>sales@embuduvillage.com</t>
         </is>
       </c>
-      <c r="J64" s="12" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
         <is>
           <t>+960 664 4776</t>
         </is>
       </c>
-      <c r="K64" s="12" t="inlineStr">
+      <c r="K64" s="5" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L64" s="12" t="inlineStr">
+      <c r="L64" s="5" t="inlineStr">
         <is>
           <t>https://www.embuduvillage.com/contact-us</t>
         </is>
       </c>
-      <c r="M64" s="12" t="inlineStr">
+      <c r="M64" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N64" s="12" t="n">
+      <c r="N64" s="5" t="n">
         <v>4</v>
       </c>
       <c r="O64" s="13" t="inlineStr">
@@ -7328,9 +8741,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P64" s="12" t="inlineStr">
+      <c r="P64" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi</t>
+        </is>
+      </c>
+      <c r="Q64" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -7573,68 +8991,68 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="12" t="n">
+      <c r="A68" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>Gili Lankanfushi</t>
         </is>
       </c>
-      <c r="C68" s="12" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D68" s="12" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>Bağımsız</t>
         </is>
       </c>
-      <c r="E68" s="12" t="n">
+      <c r="E68" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="F68" s="12" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
-      <c r="G68" s="12" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>GES bilgisi var, kapsamı doğrulanmalı</t>
         </is>
       </c>
-      <c r="H68" s="12" t="inlineStr">
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>gili-lankanfushi.com</t>
         </is>
       </c>
-      <c r="I68" s="12" t="inlineStr">
+      <c r="I68" s="5" t="inlineStr">
         <is>
           <t>mr.friday@gili-lankanfushi.com</t>
         </is>
       </c>
-      <c r="J68" s="12" t="inlineStr">
+      <c r="J68" s="5" t="inlineStr">
         <is>
           <t>+960 664 0304</t>
         </is>
       </c>
-      <c r="K68" s="12" t="inlineStr">
+      <c r="K68" s="5" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi (genel misafir hattı)</t>
         </is>
       </c>
-      <c r="L68" s="12" t="inlineStr">
+      <c r="L68" s="5" t="inlineStr">
         <is>
           <t>https://gili-lankanfushi.com/contact-us/</t>
         </is>
       </c>
-      <c r="M68" s="12" t="inlineStr">
+      <c r="M68" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N68" s="12" t="n">
+      <c r="N68" s="5" t="n">
         <v>4</v>
       </c>
       <c r="O68" s="13" t="inlineStr">
@@ -7642,75 +9060,80 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P68" s="12" t="inlineStr">
+      <c r="P68" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi</t>
         </is>
       </c>
+      <c r="Q68" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="12" t="n">
+      <c r="A69" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>Grand Park Kodhipparu</t>
         </is>
       </c>
-      <c r="C69" s="12" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>Park Hotel Group</t>
         </is>
       </c>
-      <c r="E69" s="12" t="n">
+      <c r="E69" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="F69" s="12" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G69" s="12" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H69" s="12" t="inlineStr">
+      <c r="H69" s="5" t="inlineStr">
         <is>
           <t>grandparkkodhipparu.com</t>
         </is>
       </c>
-      <c r="I69" s="12" t="inlineStr">
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>info@grandparkkodhipparu.com; rsvn.gpkd@parkhotelgroup.com</t>
         </is>
       </c>
-      <c r="J69" s="12" t="inlineStr">
+      <c r="J69" s="5" t="inlineStr">
         <is>
           <t>+960 665 1111</t>
         </is>
       </c>
-      <c r="K69" s="12" t="inlineStr">
+      <c r="K69" s="5" t="inlineStr">
         <is>
           <t>Arama sonucu</t>
         </is>
       </c>
-      <c r="L69" s="12" t="inlineStr">
+      <c r="L69" s="5" t="inlineStr">
         <is>
           <t>https://wetu.com/iBrochure/en/Information/141358/grand_park_kodhipparu/Contact</t>
         </is>
       </c>
-      <c r="M69" s="12" t="inlineStr">
+      <c r="M69" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N69" s="12" t="n">
+      <c r="N69" s="5" t="n">
         <v>4</v>
       </c>
       <c r="O69" s="13" t="inlineStr">
@@ -7718,75 +9141,80 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P69" s="12" t="inlineStr">
+      <c r="P69" s="5" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi</t>
         </is>
       </c>
+      <c r="Q69" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="12" t="n">
+      <c r="A70" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>InterContinental Maamunagau</t>
         </is>
       </c>
-      <c r="C70" s="12" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>Raa</t>
         </is>
       </c>
-      <c r="D70" s="12" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>IHG markası</t>
         </is>
       </c>
-      <c r="E70" s="12" t="n">
+      <c r="E70" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="F70" s="12" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G70" s="12" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H70" s="12" t="inlineStr">
+      <c r="H70" s="5" t="inlineStr">
         <is>
           <t>ihg.com</t>
         </is>
       </c>
-      <c r="I70" s="12" t="inlineStr">
+      <c r="I70" s="5" t="inlineStr">
         <is>
           <t>Intercontinental.Maldives@ihg.com</t>
         </is>
       </c>
-      <c r="J70" s="12" t="inlineStr">
+      <c r="J70" s="5" t="inlineStr">
         <is>
           <t>+960 658 0500</t>
         </is>
       </c>
-      <c r="K70" s="12" t="inlineStr">
+      <c r="K70" s="5" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L70" s="12" t="inlineStr">
+      <c r="L70" s="5" t="inlineStr">
         <is>
           <t>https://maldives.intercontinental.com/contact-form/</t>
         </is>
       </c>
-      <c r="M70" s="12" t="inlineStr">
+      <c r="M70" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N70" s="12" t="n">
+      <c r="N70" s="5" t="n">
         <v>4</v>
       </c>
       <c r="O70" s="13" t="inlineStr">
@@ -7794,75 +9222,80 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P70" s="12" t="inlineStr">
+      <c r="P70" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
+      <c r="Q70" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="12" t="n">
+      <c r="A71" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>Kandolhu Maldives</t>
         </is>
       </c>
-      <c r="C71" s="12" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>Alif Alif (Kuzey Ari)</t>
         </is>
       </c>
-      <c r="D71" s="12" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>VERSA Hospitality</t>
         </is>
       </c>
-      <c r="E71" s="12" t="n">
+      <c r="E71" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="F71" s="12" t="inlineStr">
+      <c r="F71" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G71" s="12" t="inlineStr">
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H71" s="12" t="inlineStr">
+      <c r="H71" s="5" t="inlineStr">
         <is>
           <t>kandolhu.com</t>
         </is>
       </c>
-      <c r="I71" s="12" t="inlineStr">
+      <c r="I71" s="5" t="inlineStr">
         <is>
           <t>info@kandolhu.com</t>
         </is>
       </c>
-      <c r="J71" s="12" t="inlineStr">
+      <c r="J71" s="5" t="inlineStr">
         <is>
           <t>+960 668 0790</t>
         </is>
       </c>
-      <c r="K71" s="12" t="inlineStr">
+      <c r="K71" s="5" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L71" s="12" t="inlineStr">
+      <c r="L71" s="5" t="inlineStr">
         <is>
           <t>https://www.kandolhu.com/contact.html</t>
         </is>
       </c>
-      <c r="M71" s="12" t="inlineStr">
+      <c r="M71" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N71" s="12" t="n">
+      <c r="N71" s="5" t="n">
         <v>4</v>
       </c>
       <c r="O71" s="13" t="inlineStr">
@@ -7870,9 +9303,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P71" s="12" t="inlineStr">
+      <c r="P71" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+        </is>
+      </c>
+      <c r="Q71" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -7953,68 +9391,68 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="12" t="n">
+      <c r="A73" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>Milaidhoo Maldives</t>
         </is>
       </c>
-      <c r="C73" s="12" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>Baa</t>
         </is>
       </c>
-      <c r="D73" s="12" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>VERSA Hospitality</t>
         </is>
       </c>
-      <c r="E73" s="12" t="n">
+      <c r="E73" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="F73" s="12" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G73" s="12" t="inlineStr">
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H73" s="12" t="inlineStr">
+      <c r="H73" s="5" t="inlineStr">
         <is>
           <t>milaidhoo.com</t>
         </is>
       </c>
-      <c r="I73" s="12" t="inlineStr">
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>welcome@milaidhoo.com</t>
         </is>
       </c>
-      <c r="J73" s="12" t="inlineStr">
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>+960 660 7788</t>
         </is>
       </c>
-      <c r="K73" s="12" t="inlineStr">
+      <c r="K73" s="5" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi (Universal Enterprises / VERSA)</t>
         </is>
       </c>
-      <c r="L73" s="12" t="inlineStr">
+      <c r="L73" s="5" t="inlineStr">
         <is>
           <t>https://www.milaidhoo.com/contact-us.html</t>
         </is>
       </c>
-      <c r="M73" s="12" t="inlineStr">
+      <c r="M73" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N73" s="12" t="n">
+      <c r="N73" s="5" t="n">
         <v>4</v>
       </c>
       <c r="O73" s="13" t="inlineStr">
@@ -8022,75 +9460,80 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P73" s="12" t="inlineStr">
+      <c r="P73" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
+      <c r="Q73" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="12" t="n">
+      <c r="A74" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>Reethi Beach Resort</t>
         </is>
       </c>
-      <c r="C74" s="12" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>Baa</t>
         </is>
       </c>
-      <c r="D74" s="12" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>NH Collection (Minor Hotels)</t>
         </is>
       </c>
-      <c r="E74" s="12" t="n">
+      <c r="E74" s="5" t="n">
         <v>115</v>
       </c>
-      <c r="F74" s="12" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G74" s="12" t="inlineStr">
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>Yeni adı NH Collection Maldives Reethi</t>
         </is>
       </c>
-      <c r="H74" s="12" t="inlineStr">
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>nh-collection.com</t>
         </is>
       </c>
-      <c r="I74" s="12" t="inlineStr">
+      <c r="I74" s="5" t="inlineStr">
         <is>
           <t>reethi@nhcollection.com</t>
         </is>
       </c>
-      <c r="J74" s="12" t="inlineStr">
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>+960 660 2626</t>
         </is>
       </c>
-      <c r="K74" s="12" t="inlineStr">
+      <c r="K74" s="5" t="inlineStr">
         <is>
           <t>NOT: Yeni adı 'NH Collection Maldives Reethi Resort' (Minor/NH)</t>
         </is>
       </c>
-      <c r="L74" s="12" t="inlineStr">
+      <c r="L74" s="5" t="inlineStr">
         <is>
           <t>https://www.hotelcontact.net/reethi-beach-resort-maldives-baa-en.html</t>
         </is>
       </c>
-      <c r="M74" s="12" t="inlineStr">
+      <c r="M74" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N74" s="12" t="n">
+      <c r="N74" s="5" t="n">
         <v>4</v>
       </c>
       <c r="O74" s="13" t="inlineStr">
@@ -8098,9 +9541,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="P74" s="12" t="inlineStr">
+      <c r="P74" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
+        </is>
+      </c>
+      <c r="Q74" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -8333,68 +9781,68 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="12" t="n">
+      <c r="A78" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>Biyadhoo Island Resort</t>
         </is>
       </c>
-      <c r="C78" s="12" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
-      <c r="D78" s="12" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>Bağımsız</t>
         </is>
       </c>
-      <c r="E78" s="12" t="n">
+      <c r="E78" s="5" t="n">
         <v>96</v>
       </c>
-      <c r="F78" s="12" t="inlineStr">
+      <c r="F78" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G78" s="12" t="inlineStr">
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H78" s="12" t="inlineStr">
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>biyadhoo.com</t>
         </is>
       </c>
-      <c r="I78" s="12" t="inlineStr">
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>biyadhoo@sunland.com.mv</t>
         </is>
       </c>
-      <c r="J78" s="12" t="inlineStr">
+      <c r="J78" s="5" t="inlineStr">
         <is>
           <t>+960 664 7171</t>
         </is>
       </c>
-      <c r="K78" s="12" t="inlineStr">
+      <c r="K78" s="5" t="inlineStr">
         <is>
           <t>Arama sonucu (Sunland grubu)</t>
         </is>
       </c>
-      <c r="L78" s="12" t="inlineStr">
+      <c r="L78" s="5" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com/ShowTopic-g298335-i9918-k6983585-How_to_contact_Biyadhoo_Island_Resort_in_Maldives-South_Male_Atoll.html</t>
         </is>
       </c>
-      <c r="M78" s="12" t="inlineStr">
+      <c r="M78" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N78" s="12" t="n">
+      <c r="N78" s="5" t="n">
         <v>3</v>
       </c>
       <c r="O78" s="14" t="inlineStr">
@@ -8402,75 +9850,80 @@
           <t>C</t>
         </is>
       </c>
-      <c r="P78" s="12" t="inlineStr">
+      <c r="P78" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi</t>
         </is>
       </c>
+      <c r="Q78" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="12" t="n">
+      <c r="A79" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>Malahini Kuda Bandos</t>
         </is>
       </c>
-      <c r="C79" s="12" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D79" s="12" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>Bağımsız</t>
         </is>
       </c>
-      <c r="E79" s="12" t="n">
+      <c r="E79" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="F79" s="12" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G79" s="12" t="inlineStr">
+      <c r="G79" s="5" t="inlineStr">
         <is>
           <t>Akademik GES+ESS fizibilite çalışmasına konu oldu</t>
         </is>
       </c>
-      <c r="H79" s="12" t="inlineStr">
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>malahini.com</t>
         </is>
       </c>
-      <c r="I79" s="12" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>reservations@malahini.mv</t>
         </is>
       </c>
-      <c r="J79" s="12" t="inlineStr">
+      <c r="J79" s="5" t="inlineStr">
         <is>
           <t>+960 664 4556</t>
         </is>
       </c>
-      <c r="K79" s="12" t="inlineStr">
+      <c r="K79" s="5" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi (malahini.mv)</t>
         </is>
       </c>
-      <c r="L79" s="12" t="inlineStr">
+      <c r="L79" s="5" t="inlineStr">
         <is>
           <t>https://malahini.mv/</t>
         </is>
       </c>
-      <c r="M79" s="12" t="inlineStr">
+      <c r="M79" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N79" s="12" t="n">
+      <c r="N79" s="5" t="n">
         <v>3</v>
       </c>
       <c r="O79" s="14" t="inlineStr">
@@ -8478,75 +9931,80 @@
           <t>C</t>
         </is>
       </c>
-      <c r="P79" s="12" t="inlineStr">
+      <c r="P79" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi</t>
         </is>
       </c>
+      <c r="Q79" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="12" t="n">
+      <c r="A80" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>Summer Island Maldives</t>
         </is>
       </c>
-      <c r="C80" s="12" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D80" s="12" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>Bağımsız</t>
         </is>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E80" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="F80" s="12" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G80" s="12" t="inlineStr">
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H80" s="12" t="inlineStr">
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>summerislandmaldives.com</t>
         </is>
       </c>
-      <c r="I80" s="12" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>reservations@summerislandmaldives.com</t>
         </is>
       </c>
-      <c r="J80" s="12" t="inlineStr">
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>+960 664 1949</t>
         </is>
       </c>
-      <c r="K80" s="12" t="inlineStr">
+      <c r="K80" s="5" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L80" s="12" t="inlineStr">
+      <c r="L80" s="5" t="inlineStr">
         <is>
           <t>https://www.summerislandmaldives.com/contact-us</t>
         </is>
       </c>
-      <c r="M80" s="12" t="inlineStr">
+      <c r="M80" s="5" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N80" s="5" t="n">
         <v>3</v>
       </c>
       <c r="O80" s="14" t="inlineStr">
@@ -8554,9 +10012,14 @@
           <t>C</t>
         </is>
       </c>
-      <c r="P80" s="12" t="inlineStr">
+      <c r="P80" s="5" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi</t>
+        </is>
+      </c>
+      <c r="Q80" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -10228,32 +11691,32 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Centara Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Bangkok, Tayland</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>3+</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Machchafushi (eski Centara Grand), Ras Fushi, Mirage Lagoon</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Machchafushi'de çatı GES -&gt; ESS ilavesi</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>centarahotelsresorts.com</t>
         </is>
@@ -10263,24 +11726,29 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K14" s="12" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>

--- a/Maldivler_Potansiyel_Musteri_Listesi.xlsx
+++ b/Maldivler_Potansiyel_Musteri_Listesi.xlsx
@@ -252,8 +252,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Gruplar" displayName="Gruplar" ref="A1:L18" headerRowCount="1">
-  <autoFilter ref="A1:L18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Gruplar" displayName="Gruplar" ref="A1:L21" headerRowCount="1">
+  <autoFilter ref="A1:L21"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Merkez"/>
@@ -10877,7 +10877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -11381,220 +11381,205 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Aitken Spence (Adaaran / Heritance)</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Colombo, Sri Lanka</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Adaaran Hudhuranfushi, Rannalhi, Vadoo, Heritance Aarah</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Kamuya açık GES bilgisi sınırlı</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>aitkenspencehotels.com</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>inquiries.mv@adaaran.com.mv</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>+960 664 0375</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>H. Thuniya 6. kat, Boduthakurufaanu Magu, Malé 20026</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>https://www.aitkenspencehotels.com/contact-us.html</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>Mail gönderildi (2026-10-06)</t>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Gürok Grubu (TÜRK – JOALI sahibi)</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Kütahya, Türkiye</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>JOALI Maldives, JOALI BEING (Raa Atoll)</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Ultra lüks, sürdürülebilirlik odaklı; kamuya açık GES bilgisi yok. Türk sahipli – Türkçe görüşme</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>gurok.com</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>info@gurok.com</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>+90 274 225 06 60</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>İnköy Mah. Eskişehir Karayolu Blv. No:96, Kütahya</t>
+        </is>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>https://gurok.com/iletisim</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Cinnamon Hotels (John Keells)</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Colombo, Sri Lanka</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Dhonveli, Velifushi, Ellaidhoo, Hakuraa</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Kamuya açık GES bilgisi sınırlı</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>cinnamonhotels.com</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>sales.mv@cinnamonhotels.com</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>+960 333 6000</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>H. Maizan Building 2. kat, Sosun Magu, Malé 20252</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>https://www.maldivesyp.com/company/547/Cinnamon_Dhonveli_Maldives</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>Mail gönderildi (2026-10-06)</t>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Astaş Holding (TÜRK – yeni Maldivler projesi)</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>İstanbul, Türkiye</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Proje</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>~120 villalık, 300 M$ resort projesi (Mandarin Oriental Bodrum sahibi)</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Tasarım aşamasında – enerji sistemi baştan hibrit kurgulanabilir. EN SICAK yeni proje adayı</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>astas-holding.com</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>info@astas-holding.com</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>+90 212 215 20 20</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>Büyükdere Cad. No:127 Astoria Kuleleri B Blok K:25, Esentepe, İstanbul</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>https://www.astas-holding.com/tr/iletisim</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Minor Hotels (Anantara, NH Collection)</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Bangkok, Tayland</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Anantara Dhigu/Veli/Naladhu, Kihavah, NH Reethi</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Kamuya açık GES bilgisi sınırlı. Malé adresi VERSA ile aynı – adaların sahibi VERSA olabilir (doğrulanmalı)</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>minorhotels.com</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>reservations.maldives@anantara.com</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>+960 664 4123</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>39 Orchid Magu, Malé (VERSA ile aynı adres – mülk sahipliği bağlantısı doğrulanmalı)</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>https://www.minorhotels.com/en/reservations-offices</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>Mail gönderildi (2026-10-06)</t>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Maxx Royal Resorts (TÜRK – Maxx Royal Maldives)</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Antalya / Bodrum, Türkiye</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Proje</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Maxx Royal Maldives (5 ada, 2027 açılış hedefi)</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Yapım/tasarım aşamasında – enerji sistemi baştan hibrit kurgulanabilir</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>maxxroyal.com</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>contact@maxxroyal.com</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>+90 252 311 01 50</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>Bodrum ofisi</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>https://www.maxxroyal.com/contact</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Pulse Hotels &amp; Resorts (Kandima)</t>
+          <t>Aitken Spence (Adaaran / Heritance)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Malé / Singapur</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Kandima</t>
+          <t>Adaaran Hudhuranfushi, Rannalhi, Vadoo, Heritance Aarah</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Kamuya açık GES bilgisi yok. Mayıs 2026'da Director of Engineering ilanı açtı (yeni kişi göreve başlamış olabilir)</t>
+          <t>Kamuya açık GES bilgisi sınırlı</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>kandima.com</t>
+          <t>aitkenspencehotels.com</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
@@ -11604,22 +11589,22 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>KeepinTouch@pulseresorts.com</t>
+          <t>inquiries.mv@adaaran.com.mv</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>+65 6838 9123 (Singapur)</t>
+          <t>+960 664 0375</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Kaneeru Villa 4. kat, Orchid Magu, Malé 20212</t>
+          <t>H. Thuniya 6. kat, Boduthakurufaanu Magu, Malé 20026</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>https://kandima.com/en/explore/contact</t>
+          <t>https://www.aitkenspencehotels.com/contact-us.html</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -11631,32 +11616,32 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>CROSSROADS / Singha Estate</t>
+          <t>Cinnamon Hotels (John Keells)</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Bangkok, Tayland</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>2 + marina</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Hard Rock, SAii Lagoon</t>
+          <t>Dhonveli, Velifushi, Ellaidhoo, Hakuraa</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Entegre ada kompleksi, tek enerji santrali</t>
+          <t>Kamuya açık GES bilgisi sınırlı</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>crossroadsmaldives.com</t>
+          <t>cinnamonhotels.com</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
@@ -11666,22 +11651,22 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>sales@crossroadsmaldives.com</t>
+          <t>sales.mv@cinnamonhotels.com</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>+960 665 1200</t>
+          <t>+960 333 6000</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>South Malé Atoll, P.O. Box 2097</t>
+          <t>H. Maizan Building 2. kat, Sosun Magu, Malé 20252</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>https://crossroadsmaldives.com/contact-us/</t>
+          <t>https://www.maldivesyp.com/company/547/Cinnamon_Dhonveli_Maldives</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -11693,7 +11678,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Centara Hotels &amp; Resorts</t>
+          <t>Minor Hotels (Anantara, NH Collection)</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -11703,22 +11688,22 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>3+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Machchafushi (eski Centara Grand), Ras Fushi, Mirage Lagoon</t>
+          <t>Anantara Dhigu/Veli/Naladhu, Kihavah, NH Reethi</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Machchafushi'de çatı GES -&gt; ESS ilavesi</t>
+          <t>Kamuya açık GES bilgisi sınırlı. Malé adresi VERSA ile aynı – adaların sahibi VERSA olabilir (doğrulanmalı)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>centarahotelsresorts.com</t>
+          <t>minorhotels.com</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
@@ -11728,22 +11713,22 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>reservations.maldives@anantara.com</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+960 664 4123</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39 Orchid Magu, Malé (VERSA ile aynı adres – mülk sahipliği bağlantısı doğrulanmalı)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.minorhotels.com/en/reservations-offices</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -11755,231 +11740,417 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>Pulse Hotels &amp; Resorts (Kandima)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Malé / Singapur</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Kandima</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Kamuya açık GES bilgisi yok. Mayıs 2026'da Director of Engineering ilanı açtı (yeni kişi göreve başlamış olabilir)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>kandima.com</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>KeepinTouch@pulseresorts.com</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>+65 6838 9123 (Singapur)</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Kaneeru Villa 4. kat, Orchid Magu, Malé 20212</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>https://kandima.com/en/explore/contact</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>CROSSROADS / Singha Estate</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Bangkok, Tayland</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>2 + marina</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Hard Rock, SAii Lagoon</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Entegre ada kompleksi, tek enerji santrali</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>crossroadsmaldives.com</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>sales@crossroadsmaldives.com</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>+960 665 1200</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>South Malé Atoll, P.O. Box 2097</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>https://crossroadsmaldives.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Centara Hotels &amp; Resorts</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Bangkok, Tayland</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>3+</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Machchafushi (eski Centara Grand), Ras Fushi, Mirage Lagoon</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Machchafushi'de çatı GES -&gt; ESS ilavesi</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>centarahotelsresorts.com</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Mail gönderildi (2026-10-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
           <t>Emerald Collection</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Emerald Maldives, Emerald Faarufushi</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Kamuya açık GES bilgisi yok</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>emerald-maldives.com</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>Mail gönderildi (2026-10-06)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Pontiac Land (Fari Islands)</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Singapur</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>3 (Capella 2027)</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Patina, Ritz-Carlton, Capella</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Swimsol ile büyük GES+ESS – rakip tarafından alınmış</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>fari-islands.com</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="J19" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K16" s="12" t="inlineStr">
+      <c r="K19" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Soneva</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Maldivler / Dubai</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Soneva Fushi, Jani, Secret</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Canopy Power + Huawei ESS – rakip tarafından alınmış (referans vaka)</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>soneva.com</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
+      <c r="I20" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J17" s="12" t="inlineStr">
+      <c r="J20" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr">
+      <c r="K20" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Marriott / Hilton / IHG / Four Seasons vb. küresel markalar</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Çeşitli</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>Çok sayıda</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Waldorf, Conrad, Sheraton, Holiday Inn, Four Seasons</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Karar çoğunlukla mülk sahibi (owner) şirkette; marka sadece işletmeci. Owner şirket tespit edilmeli</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="J21" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K18" s="12" t="inlineStr">
+      <c r="K21" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/Maldivler_Potansiyel_Musteri_Listesi.xlsx
+++ b/Maldivler_Potansiyel_Musteri_Listesi.xlsx
@@ -55,7 +55,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -102,6 +102,11 @@
         <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -115,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,6 +136,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -831,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3697,6 +3703,13 @@
       <c r="A66" s="10" t="inlineStr">
         <is>
           <t>İlgilenmiyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>Gönderilemedi – tekrar gönderilecek</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3898,7 @@
       <c r="N2" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="O2" s="11" t="inlineStr">
+      <c r="O2" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3902,76 +3915,76 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="A3" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Sun Island Resort &amp; Spa</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Alif Dhaal (Güney Ari)</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Villa Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="13" t="n">
         <v>350</v>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>Yeni adı Villa Park; 2.400+ güneş paneli var</t>
         </is>
       </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>villaresorts.com</t>
         </is>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>park@villaresorts.com; hello@villaresorts.com (Villa Resorts genel)</t>
         </is>
       </c>
-      <c r="J3" s="12" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>+960 668 0088</t>
         </is>
       </c>
-      <c r="K3" s="12" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi. NOT: Yeni adı 'Villa Park' (eski Sun Island)</t>
         </is>
       </c>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t>https://villaresorts.com/villa-park/contact/</t>
         </is>
       </c>
-      <c r="M3" s="12" t="inlineStr">
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N3" s="12" t="n">
+      <c r="N3" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O3" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="P3" s="12" t="inlineStr">
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t>büyük resort (yüksek dizel tüketimi); GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -4042,7 +4055,7 @@
       <c r="N4" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4059,76 +4072,76 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="A5" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Atmosphere Kanifushi</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Lhaviyani</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Atmosphere Core</t>
         </is>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="13" t="n">
         <v>150</v>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>Grup genelinde ~8.900 panel (çatı GES)</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>atmosphere-kanifushi.com</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>reservations@atmosphere-kanifushi.com</t>
         </is>
       </c>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>+960 662 0066</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr">
+      <c r="K5" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi; genel adres sayfada gizlenmiş</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t>https://atmosphere-kanifushi.com/en/contact-us</t>
         </is>
       </c>
-      <c r="M5" s="12" t="inlineStr">
+      <c r="M5" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N5" s="12" t="n">
+      <c r="N5" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="P5" s="12" t="inlineStr">
+      <c r="P5" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -4199,7 +4212,7 @@
       <c r="N6" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4280,7 +4293,7 @@
       <c r="N7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="O7" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4361,7 +4374,7 @@
       <c r="N8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="O8" s="11" t="inlineStr">
+      <c r="O8" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4442,7 +4455,7 @@
       <c r="N9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O9" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4523,7 +4536,7 @@
       <c r="N10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="O10" s="11" t="inlineStr">
+      <c r="O10" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4540,76 +4553,76 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n">
+      <c r="A11" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Kuredu Island Resort</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Lhaviyani</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Crown &amp; Champa (Kuredu Holdings)</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="13" t="n">
         <v>380</v>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>Ülkenin en büyük resortlarından</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>kuredu.com</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>+960 662 0337</t>
         </is>
       </c>
-      <c r="K11" s="12" t="inlineStr">
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi; e-posta sayfada gizlenmiş. NOT: Crown &amp; Champa sitesinde listeleniyor</t>
         </is>
       </c>
-      <c r="L11" s="12" t="inlineStr">
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t>https://www.kuredu.com/contact-us/</t>
         </is>
       </c>
-      <c r="M11" s="12" t="inlineStr">
+      <c r="M11" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N11" s="12" t="n">
+      <c r="N11" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O11" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="P11" s="12" t="inlineStr">
+      <c r="P11" s="13" t="inlineStr">
         <is>
           <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -4680,7 +4693,7 @@
       <c r="N12" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O12" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4697,228 +4710,228 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="A13" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Mandarin Oriental Bolidhuffaru Reef</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Mandarin Oriental</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="13" t="n">
         <v>120</v>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>~2026 açılış hedefi</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t>mandarinoriental.com</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K13" s="12" t="inlineStr">
+      <c r="K13" s="13" t="inlineStr">
         <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
+      <c r="L13" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M13" s="12" t="inlineStr">
+      <c r="M13" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N13" s="12" t="n">
+      <c r="N13" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="O13" s="11" t="inlineStr">
+      <c r="O13" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="P13" s="12" t="inlineStr">
+      <c r="P13" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>One&amp;Only Reethi Rah</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Kerzner</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="13" t="n">
         <v>128</v>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>Swimsol müşterisi</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t>oneandonlyresorts.com</t>
         </is>
       </c>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="I14" s="13" t="inlineStr">
         <is>
           <t>reservations@oneandonlyreethirah.com (düşük güven)</t>
         </is>
       </c>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t>+960 664 8800</t>
         </is>
       </c>
-      <c r="K14" s="12" t="inlineStr">
+      <c r="K14" s="13" t="inlineStr">
         <is>
           <t>Üçüncü taraf site – doğrulanmalı</t>
         </is>
       </c>
-      <c r="L14" s="12" t="inlineStr">
+      <c r="L14" s="13" t="inlineStr">
         <is>
           <t>https://www.travelweekly.com/Hotels/Male-Maldives/OneOnly-Reethi-Rah-p58629322</t>
         </is>
       </c>
-      <c r="M14" s="12" t="inlineStr">
+      <c r="M14" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N14" s="12" t="n">
+      <c r="N14" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="O14" s="11" t="inlineStr">
+      <c r="O14" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="P14" s="12" t="inlineStr">
+      <c r="P14" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Paradise Island Resort</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Villa Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="13" t="n">
         <v>280</v>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G15" s="12" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>Yeni adı Villa Nautica</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t>villaresorts.com</t>
         </is>
       </c>
-      <c r="I15" s="12" t="inlineStr">
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>nautica@villaresorts.com; hello@villaresorts.com</t>
         </is>
       </c>
-      <c r="J15" s="12" t="inlineStr">
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>+960 664 0011</t>
         </is>
       </c>
-      <c r="K15" s="12" t="inlineStr">
+      <c r="K15" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi. NOT: Yeni adı 'Villa Nautica' (Villa Resorts)</t>
         </is>
       </c>
-      <c r="L15" s="12" t="inlineStr">
+      <c r="L15" s="13" t="inlineStr">
         <is>
           <t>https://villaresorts.com/villa-nautica/contact/</t>
         </is>
       </c>
-      <c r="M15" s="12" t="inlineStr">
+      <c r="M15" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N15" s="12" t="n">
+      <c r="N15" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O15" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="P15" s="12" t="inlineStr">
+      <c r="P15" s="13" t="inlineStr">
         <is>
           <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -4989,7 +5002,7 @@
       <c r="N16" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="O16" s="11" t="inlineStr">
+      <c r="O16" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5006,538 +5019,538 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Adaaran Club Rannalhi</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Aitken Spence (Adaaran)</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="13" t="n">
         <v>130</v>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>adaaran.com</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
+      <c r="I17" s="13" t="inlineStr">
         <is>
           <t>res.acr@adaaran.com.mv</t>
         </is>
       </c>
-      <c r="J17" s="12" t="inlineStr">
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>+960 664 2688</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr">
+      <c r="K17" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi (iletişim sayfası)</t>
         </is>
       </c>
-      <c r="L17" s="12" t="inlineStr">
+      <c r="L17" s="13" t="inlineStr">
         <is>
           <t>https://www.adaaran.com/clubrannalhi/contact-us/</t>
         </is>
       </c>
-      <c r="M17" s="12" t="inlineStr">
+      <c r="M17" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N17" s="12" t="n">
+      <c r="N17" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O17" s="13" t="inlineStr">
+      <c r="O17" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P17" s="12" t="inlineStr">
+      <c r="P17" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n">
+      <c r="A18" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>Adaaran Select Hudhuranfushi</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Aitken Spence (Adaaran)</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="13" t="n">
         <v>210</v>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>adaaran.com</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="I18" s="13" t="inlineStr">
         <is>
           <t>res.hrf@adaaran.com.mv</t>
         </is>
       </c>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>+960 664 0375</t>
         </is>
       </c>
-      <c r="K18" s="12" t="inlineStr">
+      <c r="K18" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi (iletişim sayfası)</t>
         </is>
       </c>
-      <c r="L18" s="12" t="inlineStr">
+      <c r="L18" s="13" t="inlineStr">
         <is>
           <t>https://www.adaaran.com/selecthudhuranfushi/contact-us/</t>
         </is>
       </c>
-      <c r="M18" s="12" t="inlineStr">
+      <c r="M18" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N18" s="12" t="n">
+      <c r="N18" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O18" s="13" t="inlineStr">
+      <c r="O18" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P18" s="12" t="inlineStr">
+      <c r="P18" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n">
+      <c r="A19" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Aman Maldives</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Vaavu</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Aman</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
         </is>
       </c>
-      <c r="G19" s="12" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>2027 hedef, tarih belirsiz</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr">
+      <c r="H19" s="13" t="inlineStr">
         <is>
           <t>aman.com</t>
         </is>
       </c>
-      <c r="I19" s="12" t="inlineStr">
+      <c r="I19" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J19" s="12" t="inlineStr">
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr">
+      <c r="K19" s="13" t="inlineStr">
         <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="L19" s="12" t="inlineStr">
+      <c r="L19" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M19" s="12" t="inlineStr">
+      <c r="M19" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N19" s="12" t="n">
+      <c r="N19" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O19" s="13" t="inlineStr">
+      <c r="O19" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P19" s="12" t="inlineStr">
+      <c r="P19" s="13" t="inlineStr">
         <is>
           <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="n">
+      <c r="A20" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>Amaraa Faru (yeni)</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Atmosphere Core</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>2027 açılış; GES planlandığı açıklandı</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H20" s="13" t="inlineStr">
         <is>
           <t>atmospherecore.com</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr">
+      <c r="I20" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J20" s="12" t="inlineStr">
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K20" s="12" t="inlineStr">
+      <c r="K20" s="13" t="inlineStr">
         <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="L20" s="12" t="inlineStr">
+      <c r="L20" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M20" s="12" t="inlineStr">
+      <c r="M20" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N20" s="12" t="n">
+      <c r="N20" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O20" s="13" t="inlineStr">
+      <c r="O20" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P20" s="12" t="inlineStr">
+      <c r="P20" s="13" t="inlineStr">
         <is>
           <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="n">
+      <c r="A21" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Bandos Maldives</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Bağımsız (Maldivli)</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr">
+      <c r="H21" s="13" t="inlineStr">
         <is>
           <t>bandosmaldives.com</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="I21" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>+960 664 0088</t>
         </is>
       </c>
-      <c r="K21" s="12" t="inlineStr">
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi; e-posta sayfada gizlenmiş</t>
         </is>
       </c>
-      <c r="L21" s="12" t="inlineStr">
+      <c r="L21" s="13" t="inlineStr">
         <is>
           <t>https://bandosmaldives.com/contact-us/</t>
         </is>
       </c>
-      <c r="M21" s="12" t="inlineStr">
+      <c r="M21" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N21" s="12" t="n">
+      <c r="N21" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O21" s="13" t="inlineStr">
+      <c r="O21" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P21" s="12" t="inlineStr">
+      <c r="P21" s="13" t="inlineStr">
         <is>
           <t>büyük resort (yüksek dizel tüketimi); bilinen GES yok -&gt; GES+ESS paketi</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n">
+      <c r="A22" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Bvlgari Resort Ranfushi</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Raa</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Bvlgari (Marriott)</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="13" t="n">
         <v>54</v>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>~2027 açılış</t>
         </is>
       </c>
-      <c r="H22" s="12" t="inlineStr">
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t>bulgarihotels.com</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr">
+      <c r="I22" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K22" s="12" t="inlineStr">
+      <c r="K22" s="13" t="inlineStr">
         <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="L22" s="12" t="inlineStr">
+      <c r="L22" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M22" s="12" t="inlineStr">
+      <c r="M22" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N22" s="12" t="n">
+      <c r="N22" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O22" s="13" t="inlineStr">
+      <c r="O22" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P22" s="12" t="inlineStr">
+      <c r="P22" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Capella Maldives (Fari Islands)</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Pontiac Land</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="G23" s="13" t="inlineStr">
         <is>
           <t>2027 hedef; Fari mikro şebekesine bağlanabilir</t>
         </is>
       </c>
-      <c r="H23" s="12" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr">
         <is>
           <t>capellahotels.com</t>
         </is>
       </c>
-      <c r="I23" s="12" t="inlineStr">
+      <c r="I23" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J23" s="12" t="inlineStr">
+      <c r="J23" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K23" s="12" t="inlineStr">
+      <c r="K23" s="13" t="inlineStr">
         <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="L23" s="12" t="inlineStr">
+      <c r="L23" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M23" s="12" t="inlineStr">
+      <c r="M23" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N23" s="12" t="n">
+      <c r="N23" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O23" s="13" t="inlineStr">
+      <c r="O23" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P23" s="12" t="inlineStr">
+      <c r="P23" s="13" t="inlineStr">
         <is>
           <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -5608,7 +5621,7 @@
       <c r="N24" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="O24" s="13" t="inlineStr">
+      <c r="O24" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5689,7 +5702,7 @@
       <c r="N25" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="O25" s="13" t="inlineStr">
+      <c r="O25" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5706,76 +5719,76 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="n">
+      <c r="A26" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>Cinnamon Dhonveli</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>Cinnamon Hotels (John Keells)</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="13" t="n">
         <v>150</v>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="H26" s="13" t="inlineStr">
         <is>
           <t>cinnamonhotels.com</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr">
+      <c r="I26" s="13" t="inlineStr">
         <is>
           <t>dhonveli@cinnamonhotels.com; sales.mv@cinnamonhotels.com</t>
         </is>
       </c>
-      <c r="J26" s="12" t="inlineStr">
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>+960 664 0055</t>
         </is>
       </c>
-      <c r="K26" s="12" t="inlineStr">
+      <c r="K26" s="13" t="inlineStr">
         <is>
           <t>Otel rehberi / otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="L26" s="13" t="inlineStr">
         <is>
           <t>https://www.maldivesyp.com/company/547/Cinnamon_Dhonveli_Maldives</t>
         </is>
       </c>
-      <c r="M26" s="12" t="inlineStr">
+      <c r="M26" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N26" s="12" t="n">
+      <c r="N26" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O26" s="13" t="inlineStr">
+      <c r="O26" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P26" s="12" t="inlineStr">
+      <c r="P26" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -5846,7 +5859,7 @@
       <c r="N27" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="O27" s="13" t="inlineStr">
+      <c r="O27" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5863,76 +5876,76 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="n">
+      <c r="A28" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>Dhigali Maldives</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>Raa</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>VERSA Hospitality (Niva)</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="13" t="n">
         <v>180</v>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr">
+      <c r="H28" s="13" t="inlineStr">
         <is>
           <t>nivadhigali.com</t>
         </is>
       </c>
-      <c r="I28" s="12" t="inlineStr">
+      <c r="I28" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J28" s="12" t="inlineStr">
+      <c r="J28" s="13" t="inlineStr">
         <is>
           <t>+960 658 6060</t>
         </is>
       </c>
-      <c r="K28" s="12" t="inlineStr">
+      <c r="K28" s="13" t="inlineStr">
         <is>
           <t>NOT: 'Niva Dhigali' adıyla yeni marka/site; e-posta sayfada gizlenmiş</t>
         </is>
       </c>
-      <c r="L28" s="12" t="inlineStr">
+      <c r="L28" s="13" t="inlineStr">
         <is>
           <t>https://www.nivadhigali.com/contact/</t>
         </is>
       </c>
-      <c r="M28" s="12" t="inlineStr">
+      <c r="M28" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N28" s="12" t="n">
+      <c r="N28" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O28" s="13" t="inlineStr">
+      <c r="O28" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P28" s="12" t="inlineStr">
+      <c r="P28" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -6003,7 +6016,7 @@
       <c r="N29" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="O29" s="13" t="inlineStr">
+      <c r="O29" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -6084,7 +6097,7 @@
       <c r="N30" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="O30" s="13" t="inlineStr">
+      <c r="O30" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -6101,380 +6114,380 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n">
+      <c r="A31" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>Hard Rock Hotel Maldives</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>CROSSROADS / Singha Estate</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="13" t="n">
         <v>178</v>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G31" s="13" t="inlineStr">
         <is>
           <t>Entegre ada kompleksi (marina + 2 otel)</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr">
+      <c r="H31" s="13" t="inlineStr">
         <is>
           <t>hardrockhotels.com/maldives</t>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr">
+      <c r="I31" s="13" t="inlineStr">
         <is>
           <t>info@hrhmaldives.com</t>
         </is>
       </c>
-      <c r="J31" s="12" t="inlineStr">
+      <c r="J31" s="13" t="inlineStr">
         <is>
           <t>+960 665 1400</t>
         </is>
       </c>
-      <c r="K31" s="12" t="inlineStr">
+      <c r="K31" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L31" s="12" t="inlineStr">
+      <c r="L31" s="13" t="inlineStr">
         <is>
           <t>https://hotel.hardrock.com/maldives/contact.aspx</t>
         </is>
       </c>
-      <c r="M31" s="12" t="inlineStr">
+      <c r="M31" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N31" s="12" t="n">
+      <c r="N31" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O31" s="13" t="inlineStr">
+      <c r="O31" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P31" s="12" t="inlineStr">
+      <c r="P31" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="n">
+      <c r="A32" s="13" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>Heritance Aarah</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>Raa</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>Aitken Spence (Heritance)</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="13" t="n">
         <v>150</v>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G32" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr">
+      <c r="H32" s="13" t="inlineStr">
         <is>
           <t>heritancehotels.com</t>
         </is>
       </c>
-      <c r="I32" s="12" t="inlineStr">
+      <c r="I32" s="13" t="inlineStr">
         <is>
           <t>res.aarah@heritancehotels.com</t>
         </is>
       </c>
-      <c r="J32" s="12" t="inlineStr">
+      <c r="J32" s="13" t="inlineStr">
         <is>
           <t>+960 664 1908</t>
         </is>
       </c>
-      <c r="K32" s="12" t="inlineStr">
+      <c r="K32" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L32" s="12" t="inlineStr">
+      <c r="L32" s="13" t="inlineStr">
         <is>
           <t>https://www.heritancehotels.com/aarah/contact-us/</t>
         </is>
       </c>
-      <c r="M32" s="12" t="inlineStr">
+      <c r="M32" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N32" s="12" t="n">
+      <c r="N32" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O32" s="13" t="inlineStr">
+      <c r="O32" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P32" s="12" t="inlineStr">
+      <c r="P32" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="n">
+      <c r="A33" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>Holiday Island Resort</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>Alif Dhaal (Güney Ari)</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>Villa Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="13" t="n">
         <v>140</v>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G33" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr">
+      <c r="H33" s="13" t="inlineStr">
         <is>
           <t>villaresorts.com</t>
         </is>
       </c>
-      <c r="I33" s="12" t="inlineStr">
+      <c r="I33" s="13" t="inlineStr">
         <is>
           <t>hello@villaresorts.com (Villa Resorts genel)</t>
         </is>
       </c>
-      <c r="J33" s="12" t="inlineStr">
+      <c r="J33" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K33" s="12" t="inlineStr">
+      <c r="K33" s="13" t="inlineStr">
         <is>
           <t>Otelin kendine ait adresi bulunamadı; Villa Resorts merkezi</t>
         </is>
       </c>
-      <c r="L33" s="12" t="inlineStr">
+      <c r="L33" s="13" t="inlineStr">
         <is>
           <t>https://villaresorts.com/contact/</t>
         </is>
       </c>
-      <c r="M33" s="12" t="inlineStr">
+      <c r="M33" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N33" s="12" t="n">
+      <c r="N33" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O33" s="13" t="inlineStr">
+      <c r="O33" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P33" s="12" t="inlineStr">
+      <c r="P33" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="n">
+      <c r="A34" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>Hurawalhi Island Resort</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>Lhaviyani</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>Crown &amp; Champa Resorts</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G34" s="13" t="inlineStr">
         <is>
           <t>Mimariye entegre GES</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="H34" s="13" t="inlineStr">
         <is>
           <t>hurawalhi.com</t>
         </is>
       </c>
-      <c r="I34" s="12" t="inlineStr">
+      <c r="I34" s="13" t="inlineStr">
         <is>
           <t>reservations@hurawalhi.com</t>
         </is>
       </c>
-      <c r="J34" s="12" t="inlineStr">
+      <c r="J34" s="13" t="inlineStr">
         <is>
           <t>+960 662 2000</t>
         </is>
       </c>
-      <c r="K34" s="12" t="inlineStr">
+      <c r="K34" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L34" s="12" t="inlineStr">
+      <c r="L34" s="13" t="inlineStr">
         <is>
           <t>https://www.hurawalhi.com/contact/</t>
         </is>
       </c>
-      <c r="M34" s="12" t="inlineStr">
+      <c r="M34" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N34" s="12" t="n">
+      <c r="N34" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O34" s="13" t="inlineStr">
+      <c r="O34" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P34" s="12" t="inlineStr">
+      <c r="P34" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="n">
+      <c r="A35" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>Kurumba Maldives</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>VERSA Hospitality (Niva)</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="13" t="n">
         <v>180</v>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="F35" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="G35" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr">
+      <c r="H35" s="13" t="inlineStr">
         <is>
           <t>kurumba.com</t>
         </is>
       </c>
-      <c r="I35" s="12" t="inlineStr">
+      <c r="I35" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J35" s="12" t="inlineStr">
+      <c r="J35" s="13" t="inlineStr">
         <is>
           <t>+960 664 2324</t>
         </is>
       </c>
-      <c r="K35" s="12" t="inlineStr">
+      <c r="K35" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi; e-postalar sayfada gizlenmiş</t>
         </is>
       </c>
-      <c r="L35" s="12" t="inlineStr">
+      <c r="L35" s="13" t="inlineStr">
         <is>
           <t>https://www.kurumba.com/contact</t>
         </is>
       </c>
-      <c r="M35" s="12" t="inlineStr">
+      <c r="M35" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N35" s="12" t="n">
+      <c r="N35" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O35" s="13" t="inlineStr">
+      <c r="O35" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P35" s="12" t="inlineStr">
+      <c r="P35" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -6545,7 +6558,7 @@
       <c r="N36" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="O36" s="13" t="inlineStr">
+      <c r="O36" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -6562,152 +6575,152 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="n">
+      <c r="A37" s="13" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>OZEN LIFE Maadhoo</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>Atmosphere Core</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F37" s="13" t="inlineStr">
         <is>
           <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="G37" s="13" t="inlineStr">
         <is>
           <t>Swimsol SolarSea yüzer GES</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr">
+      <c r="H37" s="13" t="inlineStr">
         <is>
           <t>ozen-life-maadhoo.com</t>
         </is>
       </c>
-      <c r="I37" s="12" t="inlineStr">
+      <c r="I37" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J37" s="12" t="inlineStr">
+      <c r="J37" s="13" t="inlineStr">
         <is>
           <t>+960 400 2222</t>
         </is>
       </c>
-      <c r="K37" s="12" t="inlineStr">
+      <c r="K37" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi; e-posta sayfada gizlenmiş</t>
         </is>
       </c>
-      <c r="L37" s="12" t="inlineStr">
+      <c r="L37" s="13" t="inlineStr">
         <is>
           <t>https://www.theozencollection.com/ozenlife-maadhoo/contact-us/</t>
         </is>
       </c>
-      <c r="M37" s="12" t="inlineStr">
+      <c r="M37" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N37" s="12" t="n">
+      <c r="N37" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O37" s="13" t="inlineStr">
+      <c r="O37" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P37" s="12" t="inlineStr">
+      <c r="P37" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="n">
+      <c r="A38" s="13" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>OZEN Reserve Bolifushi</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>Atmosphere Core</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="F38" s="13" t="inlineStr">
         <is>
           <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="G38" s="13" t="inlineStr">
         <is>
           <t>Grup çatı GES programı</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H38" s="13" t="inlineStr">
         <is>
           <t>ozen-reserve-bolifushi.com</t>
         </is>
       </c>
-      <c r="I38" s="12" t="inlineStr">
+      <c r="I38" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J38" s="12" t="inlineStr">
+      <c r="J38" s="13" t="inlineStr">
         <is>
           <t>+960 664 2020</t>
         </is>
       </c>
-      <c r="K38" s="12" t="inlineStr">
+      <c r="K38" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi; e-posta sayfada gizlenmiş</t>
         </is>
       </c>
-      <c r="L38" s="12" t="inlineStr">
+      <c r="L38" s="13" t="inlineStr">
         <is>
           <t>https://theozencollection.com/bolifushi/en/contact-us</t>
         </is>
       </c>
-      <c r="M38" s="12" t="inlineStr">
+      <c r="M38" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N38" s="12" t="n">
+      <c r="N38" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O38" s="13" t="inlineStr">
+      <c r="O38" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P38" s="12" t="inlineStr">
+      <c r="P38" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -6778,7 +6791,7 @@
       <c r="N39" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="O39" s="13" t="inlineStr">
+      <c r="O39" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -6795,306 +6808,306 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="n">
+      <c r="A40" s="13" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>Rosewood Ranfaru</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>Haa Alifu</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>Rosewood</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="F40" s="13" t="inlineStr">
         <is>
           <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G40" s="13" t="inlineStr">
         <is>
           <t>GES sahası planı açıklandı</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="H40" s="13" t="inlineStr">
         <is>
           <t>rosewoodhotels.com</t>
         </is>
       </c>
-      <c r="I40" s="12" t="inlineStr">
+      <c r="I40" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J40" s="12" t="inlineStr">
+      <c r="J40" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K40" s="12" t="inlineStr">
+      <c r="K40" s="13" t="inlineStr">
         <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="L40" s="12" t="inlineStr">
+      <c r="L40" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M40" s="12" t="inlineStr">
+      <c r="M40" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N40" s="12" t="n">
+      <c r="N40" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O40" s="13" t="inlineStr">
+      <c r="O40" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P40" s="12" t="inlineStr">
+      <c r="P40" s="13" t="inlineStr">
         <is>
           <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="n">
+      <c r="A41" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>Royal Island Resort</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>Baa</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>Villa Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="13" t="n">
         <v>150</v>
       </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="F41" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G41" s="12" t="inlineStr">
+      <c r="G41" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr">
+      <c r="H41" s="13" t="inlineStr">
         <is>
           <t>villaresorts.com</t>
         </is>
       </c>
-      <c r="I41" s="12" t="inlineStr">
+      <c r="I41" s="13" t="inlineStr">
         <is>
           <t>hello@villaresorts.com; sales@villaresorts.com</t>
         </is>
       </c>
-      <c r="J41" s="12" t="inlineStr">
+      <c r="J41" s="13" t="inlineStr">
         <is>
           <t>+960 660 0088</t>
         </is>
       </c>
-      <c r="K41" s="12" t="inlineStr">
+      <c r="K41" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi (Villa Resorts)</t>
         </is>
       </c>
-      <c r="L41" s="12" t="inlineStr">
+      <c r="L41" s="13" t="inlineStr">
         <is>
           <t>https://villaresorts.com/royal-island/contact/</t>
         </is>
       </c>
-      <c r="M41" s="12" t="inlineStr">
+      <c r="M41" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N41" s="12" t="n">
+      <c r="N41" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O41" s="13" t="inlineStr">
+      <c r="O41" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P41" s="12" t="inlineStr">
+      <c r="P41" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="n">
+      <c r="A42" s="13" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>SAii Lagoon Maldives</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>CROSSROADS / Singha Estate</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="13" t="n">
         <v>180</v>
       </c>
-      <c r="F42" s="12" t="inlineStr">
+      <c r="F42" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="G42" s="13" t="inlineStr">
         <is>
           <t>Hard Rock ile aynı ada kompleksi</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr">
+      <c r="H42" s="13" t="inlineStr">
         <is>
           <t>saiihotels.com</t>
         </is>
       </c>
-      <c r="I42" s="12" t="inlineStr">
+      <c r="I42" s="13" t="inlineStr">
         <is>
           <t>rsvn.lagoon@saiihotels.com</t>
         </is>
       </c>
-      <c r="J42" s="12" t="inlineStr">
+      <c r="J42" s="13" t="inlineStr">
         <is>
           <t>+960 665 1300</t>
         </is>
       </c>
-      <c r="K42" s="12" t="inlineStr">
+      <c r="K42" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L42" s="12" t="inlineStr">
+      <c r="L42" s="13" t="inlineStr">
         <is>
           <t>https://www.saiihotels.com/lagoon-maldives/contact-us/</t>
         </is>
       </c>
-      <c r="M42" s="12" t="inlineStr">
+      <c r="M42" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N42" s="12" t="n">
+      <c r="N42" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O42" s="13" t="inlineStr">
+      <c r="O42" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P42" s="12" t="inlineStr">
+      <c r="P42" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="n">
+      <c r="A43" s="13" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>Shangri-La Villingili</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>Addu</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>Shangri-La</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="13" t="n">
         <v>130</v>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F43" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="G43" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr">
+      <c r="H43" s="13" t="inlineStr">
         <is>
           <t>shangri-la.com</t>
         </is>
       </c>
-      <c r="I43" s="12" t="inlineStr">
+      <c r="I43" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J43" s="12" t="inlineStr">
+      <c r="J43" s="13" t="inlineStr">
         <is>
           <t>+960 689 7888</t>
         </is>
       </c>
-      <c r="K43" s="12" t="inlineStr">
+      <c r="K43" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi; e-posta sayfada gizlenmiş</t>
         </is>
       </c>
-      <c r="L43" s="12" t="inlineStr">
+      <c r="L43" s="13" t="inlineStr">
         <is>
           <t>https://www.shangri-la.com/male/villingiliresort/about/local-guide/explore-male/quick-facts/</t>
         </is>
       </c>
-      <c r="M43" s="12" t="inlineStr">
+      <c r="M43" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N43" s="12" t="n">
+      <c r="N43" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O43" s="13" t="inlineStr">
+      <c r="O43" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P43" s="12" t="inlineStr">
+      <c r="P43" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -7165,7 +7178,7 @@
       <c r="N44" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="O44" s="13" t="inlineStr">
+      <c r="O44" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -7246,7 +7259,7 @@
       <c r="N45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="O45" s="13" t="inlineStr">
+      <c r="O45" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -7263,152 +7276,152 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="n">
+      <c r="A46" s="13" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>Sun Siyam Iru Fushi</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>Noonu</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>Sun Siyam Resorts</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="13" t="n">
         <v>220</v>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F46" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G46" s="13" t="inlineStr">
         <is>
           <t>Grup modeli diğer adalara yayacağını açıkladı (2. faz adayı)</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr">
+      <c r="H46" s="13" t="inlineStr">
         <is>
           <t>sunsiyam.com</t>
         </is>
       </c>
-      <c r="I46" s="12" t="inlineStr">
+      <c r="I46" s="13" t="inlineStr">
         <is>
           <t>info.irufushi@sunsiyam.com; book@sunsiyam.com (merkez)</t>
         </is>
       </c>
-      <c r="J46" s="12" t="inlineStr">
+      <c r="J46" s="13" t="inlineStr">
         <is>
           <t>+960 656 0591</t>
         </is>
       </c>
-      <c r="K46" s="12" t="inlineStr">
+      <c r="K46" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L46" s="12" t="inlineStr">
+      <c r="L46" s="13" t="inlineStr">
         <is>
           <t>https://www.sunsiyam.com/sun-siyam-iru-fushi/contact-us/</t>
         </is>
       </c>
-      <c r="M46" s="12" t="inlineStr">
+      <c r="M46" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N46" s="12" t="n">
+      <c r="N46" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O46" s="13" t="inlineStr">
+      <c r="O46" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P46" s="12" t="inlineStr">
+      <c r="P46" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="n">
+      <c r="A47" s="13" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr">
         <is>
           <t>Sun Siyam Iru Veli</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C47" s="13" t="inlineStr">
         <is>
           <t>Dhaalu</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>Sun Siyam Resorts</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="13" t="n">
         <v>125</v>
       </c>
-      <c r="F47" s="12" t="inlineStr">
+      <c r="F47" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G47" s="12" t="inlineStr">
+      <c r="G47" s="13" t="inlineStr">
         <is>
           <t>Grup 2. faz adayı</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr">
+      <c r="H47" s="13" t="inlineStr">
         <is>
           <t>sunsiyam.com</t>
         </is>
       </c>
-      <c r="I47" s="12" t="inlineStr">
+      <c r="I47" s="13" t="inlineStr">
         <is>
           <t>book@sunsiyam.com (merkez)</t>
         </is>
       </c>
-      <c r="J47" s="12" t="inlineStr">
+      <c r="J47" s="13" t="inlineStr">
         <is>
           <t>+960 676 0100</t>
         </is>
       </c>
-      <c r="K47" s="12" t="inlineStr">
+      <c r="K47" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi; otele özel e-posta gizlenmiş</t>
         </is>
       </c>
-      <c r="L47" s="12" t="inlineStr">
+      <c r="L47" s="13" t="inlineStr">
         <is>
           <t>https://www.sunsiyam.com/sun-siyam-iru-veli/contact-us/</t>
         </is>
       </c>
-      <c r="M47" s="12" t="inlineStr">
+      <c r="M47" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N47" s="12" t="n">
+      <c r="N47" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O47" s="13" t="inlineStr">
+      <c r="O47" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P47" s="12" t="inlineStr">
+      <c r="P47" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -7479,7 +7492,7 @@
       <c r="N48" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="O48" s="13" t="inlineStr">
+      <c r="O48" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -7560,7 +7573,7 @@
       <c r="N49" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="O49" s="13" t="inlineStr">
+      <c r="O49" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -7577,306 +7590,306 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="n">
+      <c r="A50" s="13" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>VARU by Atmosphere</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>Atmosphere Core</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="13" t="n">
         <v>110</v>
       </c>
-      <c r="F50" s="12" t="inlineStr">
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>Kısmi GES, ESS yok/bilinmiyor</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
         <is>
           <t>Grup çatı GES programı</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="H50" s="13" t="inlineStr">
         <is>
           <t>varu-by-atmosphere.com</t>
         </is>
       </c>
-      <c r="I50" s="12" t="inlineStr">
+      <c r="I50" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J50" s="12" t="inlineStr">
+      <c r="J50" s="13" t="inlineStr">
         <is>
           <t>+960 400 0800</t>
         </is>
       </c>
-      <c r="K50" s="12" t="inlineStr">
+      <c r="K50" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi; e-posta sayfada gizlenmiş</t>
         </is>
       </c>
-      <c r="L50" s="12" t="inlineStr">
+      <c r="L50" s="13" t="inlineStr">
         <is>
           <t>https://varu-atmosphere.com/en/contact-us</t>
         </is>
       </c>
-      <c r="M50" s="12" t="inlineStr">
+      <c r="M50" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N50" s="12" t="n">
+      <c r="N50" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O50" s="13" t="inlineStr">
+      <c r="O50" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P50" s="12" t="inlineStr">
+      <c r="P50" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; GES var ama ESS yok -&gt; en uygun ESS ilavesi hedefi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="n">
+      <c r="A51" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>Velassaru Maldives</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
         <is>
           <t>VERSA Hospitality (Niva)</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="13" t="n">
         <v>129</v>
       </c>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="F51" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G51" s="12" t="inlineStr">
+      <c r="G51" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr">
+      <c r="H51" s="13" t="inlineStr">
         <is>
           <t>nivavelassaru.com</t>
         </is>
       </c>
-      <c r="I51" s="12" t="inlineStr">
+      <c r="I51" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J51" s="12" t="inlineStr">
+      <c r="J51" s="13" t="inlineStr">
         <is>
           <t>+960 665 6100</t>
         </is>
       </c>
-      <c r="K51" s="12" t="inlineStr">
+      <c r="K51" s="13" t="inlineStr">
         <is>
           <t>NOT: 'Niva Velassaru' adıyla yeni marka/site; e-posta gizlenmiş</t>
         </is>
       </c>
-      <c r="L51" s="12" t="inlineStr">
+      <c r="L51" s="13" t="inlineStr">
         <is>
           <t>https://www.nivavelassaru.com/contact/</t>
         </is>
       </c>
-      <c r="M51" s="12" t="inlineStr">
+      <c r="M51" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N51" s="12" t="n">
+      <c r="N51" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O51" s="13" t="inlineStr">
+      <c r="O51" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P51" s="12" t="inlineStr">
+      <c r="P51" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="n">
+      <c r="A52" s="13" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>Zamani Islands (3 resort + marina)</t>
         </is>
       </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>Zamani</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr">
+      <c r="F52" s="13" t="inlineStr">
         <is>
           <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
         </is>
       </c>
-      <c r="G52" s="12" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t>8 adalı karma proje – büyük enerji ihtiyacı</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr">
+      <c r="H52" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I52" s="12" t="inlineStr">
+      <c r="I52" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J52" s="12" t="inlineStr">
+      <c r="J52" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K52" s="12" t="inlineStr">
+      <c r="K52" s="13" t="inlineStr">
         <is>
           <t>Bulunamadı (yeni proje / doğrulanmalı)</t>
         </is>
       </c>
-      <c r="L52" s="12" t="inlineStr">
+      <c r="L52" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M52" s="12" t="inlineStr">
+      <c r="M52" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N52" s="12" t="n">
+      <c r="N52" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="O52" s="13" t="inlineStr">
+      <c r="O52" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P52" s="12" t="inlineStr">
+      <c r="P52" s="13" t="inlineStr">
         <is>
           <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="n">
+      <c r="A53" s="13" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>Adaaran Prestige Vadoo</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C53" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D53" s="13" t="inlineStr">
         <is>
           <t>Aitken Spence (Adaaran)</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="E53" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="F53" s="12" t="inlineStr">
+      <c r="F53" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G53" s="12" t="inlineStr">
+      <c r="G53" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H53" s="12" t="inlineStr">
+      <c r="H53" s="13" t="inlineStr">
         <is>
           <t>adaaran.com</t>
         </is>
       </c>
-      <c r="I53" s="12" t="inlineStr">
+      <c r="I53" s="13" t="inlineStr">
         <is>
           <t>res.vadoo@adaaran.com.mv</t>
         </is>
       </c>
-      <c r="J53" s="12" t="inlineStr">
+      <c r="J53" s="13" t="inlineStr">
         <is>
           <t>+960 664 3976</t>
         </is>
       </c>
-      <c r="K53" s="12" t="inlineStr">
+      <c r="K53" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L53" s="12" t="inlineStr">
+      <c r="L53" s="13" t="inlineStr">
         <is>
           <t>https://www.adaaran.com/prestigevadoo/contact-us/</t>
         </is>
       </c>
-      <c r="M53" s="12" t="inlineStr">
+      <c r="M53" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N53" s="12" t="n">
+      <c r="N53" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="O53" s="13" t="inlineStr">
+      <c r="O53" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P53" s="12" t="inlineStr">
+      <c r="P53" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -7947,7 +7960,7 @@
       <c r="N54" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O54" s="13" t="inlineStr">
+      <c r="O54" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8028,7 +8041,7 @@
       <c r="N55" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O55" s="13" t="inlineStr">
+      <c r="O55" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8045,78 +8058,78 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="n">
+      <c r="A56" s="13" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>Aura Maldives</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="C56" s="13" t="inlineStr">
         <is>
           <t>Baa</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="E56" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="F56" s="12" t="inlineStr">
+      <c r="F56" s="13" t="inlineStr">
         <is>
           <t>Yeni proje – enerji sistemi tasarım aşamasında</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G56" s="13" t="inlineStr">
         <is>
           <t>2026 sonu açılış bekleniyor</t>
         </is>
       </c>
-      <c r="H56" s="12" t="inlineStr">
+      <c r="H56" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I56" s="12" t="inlineStr">
+      <c r="I56" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J56" s="12" t="inlineStr">
+      <c r="J56" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K56" s="12" t="inlineStr">
+      <c r="K56" s="13" t="inlineStr">
         <is>
           <t>Bulunamadı (yeni proje / doğrulanmalı)</t>
         </is>
       </c>
-      <c r="L56" s="12" t="inlineStr">
+      <c r="L56" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M56" s="12" t="inlineStr">
+      <c r="M56" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N56" s="12" t="n">
+      <c r="N56" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="O56" s="13" t="inlineStr">
+      <c r="O56" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P56" s="12" t="inlineStr">
+      <c r="P56" s="13" t="inlineStr">
         <is>
           <t>oda sayısı doğrulanmalı; yeni proje -&gt; tasarım aşamasında girilebilir</t>
         </is>
@@ -8187,7 +8200,7 @@
       <c r="N57" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O57" s="13" t="inlineStr">
+      <c r="O57" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8204,152 +8217,152 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="n">
+      <c r="A58" s="13" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>Cinnamon Hakuraa Huraa</t>
         </is>
       </c>
-      <c r="C58" s="12" t="inlineStr">
+      <c r="C58" s="13" t="inlineStr">
         <is>
           <t>Meemu</t>
         </is>
       </c>
-      <c r="D58" s="12" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>Cinnamon Hotels (John Keells)</t>
         </is>
       </c>
-      <c r="E58" s="12" t="n">
+      <c r="E58" s="13" t="n">
         <v>80</v>
       </c>
-      <c r="F58" s="12" t="inlineStr">
+      <c r="F58" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G58" s="12" t="inlineStr">
+      <c r="G58" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H58" s="12" t="inlineStr">
+      <c r="H58" s="13" t="inlineStr">
         <is>
           <t>cinnamonhotels.com</t>
         </is>
       </c>
-      <c r="I58" s="12" t="inlineStr">
+      <c r="I58" s="13" t="inlineStr">
         <is>
           <t>info@cinnamonhotels.com (merkez); sales.mv@cinnamonhotels.com</t>
         </is>
       </c>
-      <c r="J58" s="12" t="inlineStr">
+      <c r="J58" s="13" t="inlineStr">
         <is>
           <t>+960 672 6000</t>
         </is>
       </c>
-      <c r="K58" s="12" t="inlineStr">
+      <c r="K58" s="13" t="inlineStr">
         <is>
           <t>Arama sonucu</t>
         </is>
       </c>
-      <c r="L58" s="12" t="inlineStr">
+      <c r="L58" s="13" t="inlineStr">
         <is>
           <t>https://www.cinnamonhotels.com/cinnamon-hakuraa-huraa-maldives</t>
         </is>
       </c>
-      <c r="M58" s="12" t="inlineStr">
+      <c r="M58" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N58" s="12" t="n">
+      <c r="N58" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="O58" s="13" t="inlineStr">
+      <c r="O58" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P58" s="12" t="inlineStr">
+      <c r="P58" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="n">
+      <c r="A59" s="13" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="12" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>Cinnamon Velifushi</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr">
+      <c r="C59" s="13" t="inlineStr">
         <is>
           <t>Vaavu</t>
         </is>
       </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr">
         <is>
           <t>Cinnamon Hotels (John Keells)</t>
         </is>
       </c>
-      <c r="E59" s="12" t="n">
+      <c r="E59" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="F59" s="12" t="inlineStr">
+      <c r="F59" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G59" s="12" t="inlineStr">
+      <c r="G59" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H59" s="12" t="inlineStr">
+      <c r="H59" s="13" t="inlineStr">
         <is>
           <t>cinnamonhotels.com</t>
         </is>
       </c>
-      <c r="I59" s="12" t="inlineStr">
+      <c r="I59" s="13" t="inlineStr">
         <is>
           <t>info@cinnamonhotels.com (merkez); sales.mv@cinnamonhotels.com</t>
         </is>
       </c>
-      <c r="J59" s="12" t="inlineStr">
+      <c r="J59" s="13" t="inlineStr">
         <is>
           <t>+94 112 161 161 (merkez)</t>
         </is>
       </c>
-      <c r="K59" s="12" t="inlineStr">
+      <c r="K59" s="13" t="inlineStr">
         <is>
           <t>Otele özel bilgi bulunamadı</t>
         </is>
       </c>
-      <c r="L59" s="12" t="inlineStr">
+      <c r="L59" s="13" t="inlineStr">
         <is>
           <t>https://www.cinnamonhotels.com/hotel-contact-information</t>
         </is>
       </c>
-      <c r="M59" s="12" t="inlineStr">
+      <c r="M59" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N59" s="12" t="n">
+      <c r="N59" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="O59" s="13" t="inlineStr">
+      <c r="O59" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P59" s="12" t="inlineStr">
+      <c r="P59" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -8420,7 +8433,7 @@
       <c r="N60" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O60" s="13" t="inlineStr">
+      <c r="O60" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8437,78 +8450,78 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="n">
+      <c r="A61" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>Diğer Crown &amp; Champa resortları</t>
         </is>
       </c>
-      <c r="C61" s="12" t="inlineStr">
+      <c r="C61" s="13" t="inlineStr">
         <is>
           <t>Çeşitli</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D61" s="13" t="inlineStr">
         <is>
           <t>Crown &amp; Champa Resorts</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="F61" s="12" t="inlineStr">
+      <c r="F61" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G61" s="12" t="inlineStr">
+      <c r="G61" s="13" t="inlineStr">
         <is>
           <t>Grup düzeyinde tek görüşme ile 7+ ada</t>
         </is>
       </c>
-      <c r="H61" s="12" t="inlineStr">
+      <c r="H61" s="13" t="inlineStr">
         <is>
           <t>crownandchamparesorts.com</t>
         </is>
       </c>
-      <c r="I61" s="12" t="inlineStr">
+      <c r="I61" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J61" s="12" t="inlineStr">
+      <c r="J61" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K61" s="12" t="inlineStr">
+      <c r="K61" s="13" t="inlineStr">
         <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="L61" s="12" t="inlineStr">
+      <c r="L61" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M61" s="12" t="inlineStr">
+      <c r="M61" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N61" s="12" t="n">
+      <c r="N61" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="O61" s="13" t="inlineStr">
+      <c r="O61" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P61" s="12" t="inlineStr">
+      <c r="P61" s="13" t="inlineStr">
         <is>
           <t>oda sayısı doğrulanmalı; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -8579,7 +8592,7 @@
       <c r="N62" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O62" s="13" t="inlineStr">
+      <c r="O62" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8596,76 +8609,76 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="n">
+      <c r="A63" s="13" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>Ellaidhoo Maldives by Cinnamon</t>
         </is>
       </c>
-      <c r="C63" s="12" t="inlineStr">
+      <c r="C63" s="13" t="inlineStr">
         <is>
           <t>Alif Alif (Kuzey Ari)</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
         <is>
           <t>Cinnamon Hotels (John Keells)</t>
         </is>
       </c>
-      <c r="E63" s="12" t="n">
+      <c r="E63" s="13" t="n">
         <v>110</v>
       </c>
-      <c r="F63" s="12" t="inlineStr">
+      <c r="F63" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G63" s="12" t="inlineStr">
+      <c r="G63" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H63" s="12" t="inlineStr">
+      <c r="H63" s="13" t="inlineStr">
         <is>
           <t>cinnamonhotels.com</t>
         </is>
       </c>
-      <c r="I63" s="12" t="inlineStr">
+      <c r="I63" s="13" t="inlineStr">
         <is>
           <t>info@cinnamonhotels.com (merkez); sales.mv@cinnamonhotels.com</t>
         </is>
       </c>
-      <c r="J63" s="12" t="inlineStr">
+      <c r="J63" s="13" t="inlineStr">
         <is>
           <t>+94 112 161 161 (merkez)</t>
         </is>
       </c>
-      <c r="K63" s="12" t="inlineStr">
+      <c r="K63" s="13" t="inlineStr">
         <is>
           <t>Otele özel bilgi bulunamadı</t>
         </is>
       </c>
-      <c r="L63" s="12" t="inlineStr">
+      <c r="L63" s="13" t="inlineStr">
         <is>
           <t>https://www.cinnamonhotels.com/hotel-contact-information</t>
         </is>
       </c>
-      <c r="M63" s="12" t="inlineStr">
+      <c r="M63" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N63" s="12" t="n">
+      <c r="N63" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="O63" s="13" t="inlineStr">
+      <c r="O63" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P63" s="12" t="inlineStr">
+      <c r="P63" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -8736,7 +8749,7 @@
       <c r="N64" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O64" s="13" t="inlineStr">
+      <c r="O64" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8817,7 +8830,7 @@
       <c r="N65" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O65" s="13" t="inlineStr">
+      <c r="O65" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8898,7 +8911,7 @@
       <c r="N66" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O66" s="13" t="inlineStr">
+      <c r="O66" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8915,76 +8928,76 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="n">
+      <c r="A67" s="13" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>Fun Island Resort</t>
         </is>
       </c>
-      <c r="C67" s="12" t="inlineStr">
+      <c r="C67" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D67" s="13" t="inlineStr">
         <is>
           <t>Villa Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="E67" s="12" t="n">
+      <c r="E67" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="F67" s="12" t="inlineStr">
+      <c r="F67" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G67" s="12" t="inlineStr">
+      <c r="G67" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H67" s="12" t="inlineStr">
+      <c r="H67" s="13" t="inlineStr">
         <is>
           <t>villaresorts.com</t>
         </is>
       </c>
-      <c r="I67" s="12" t="inlineStr">
+      <c r="I67" s="13" t="inlineStr">
         <is>
           <t>hello@villaresorts.com (Villa Resorts genel)</t>
         </is>
       </c>
-      <c r="J67" s="12" t="inlineStr">
+      <c r="J67" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K67" s="12" t="inlineStr">
+      <c r="K67" s="13" t="inlineStr">
         <is>
           <t>Otele özel bilgi bulunamadı</t>
         </is>
       </c>
-      <c r="L67" s="12" t="inlineStr">
+      <c r="L67" s="13" t="inlineStr">
         <is>
           <t>https://villaresorts.com/contact/</t>
         </is>
       </c>
-      <c r="M67" s="12" t="inlineStr">
+      <c r="M67" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N67" s="12" t="n">
+      <c r="N67" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="O67" s="13" t="inlineStr">
+      <c r="O67" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P67" s="12" t="inlineStr">
+      <c r="P67" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -9055,7 +9068,7 @@
       <c r="N68" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O68" s="13" t="inlineStr">
+      <c r="O68" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -9136,7 +9149,7 @@
       <c r="N69" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O69" s="13" t="inlineStr">
+      <c r="O69" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -9217,7 +9230,7 @@
       <c r="N70" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O70" s="13" t="inlineStr">
+      <c r="O70" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -9298,7 +9311,7 @@
       <c r="N71" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O71" s="13" t="inlineStr">
+      <c r="O71" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -9315,76 +9328,76 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="12" t="n">
+      <c r="A72" s="13" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>Komandoo Island Resort</t>
         </is>
       </c>
-      <c r="C72" s="12" t="inlineStr">
+      <c r="C72" s="13" t="inlineStr">
         <is>
           <t>Lhaviyani</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr">
+      <c r="D72" s="13" t="inlineStr">
         <is>
           <t>Crown &amp; Champa (Kuredu Holdings)</t>
         </is>
       </c>
-      <c r="E72" s="12" t="n">
+      <c r="E72" s="13" t="n">
         <v>65</v>
       </c>
-      <c r="F72" s="12" t="inlineStr">
+      <c r="F72" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G72" s="12" t="inlineStr">
+      <c r="G72" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H72" s="12" t="inlineStr">
+      <c r="H72" s="13" t="inlineStr">
         <is>
           <t>komandoo.com</t>
         </is>
       </c>
-      <c r="I72" s="12" t="inlineStr">
+      <c r="I72" s="13" t="inlineStr">
         <is>
           <t>reservations@komandoo.com</t>
         </is>
       </c>
-      <c r="J72" s="12" t="inlineStr">
+      <c r="J72" s="13" t="inlineStr">
         <is>
           <t>+960 662 1010</t>
         </is>
       </c>
-      <c r="K72" s="12" t="inlineStr">
+      <c r="K72" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L72" s="12" t="inlineStr">
+      <c r="L72" s="13" t="inlineStr">
         <is>
           <t>https://www.komandoo.com/contact/</t>
         </is>
       </c>
-      <c r="M72" s="12" t="inlineStr">
+      <c r="M72" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N72" s="12" t="n">
+      <c r="N72" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="O72" s="13" t="inlineStr">
+      <c r="O72" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P72" s="12" t="inlineStr">
+      <c r="P72" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
@@ -9455,7 +9468,7 @@
       <c r="N73" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O73" s="13" t="inlineStr">
+      <c r="O73" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -9536,7 +9549,7 @@
       <c r="N74" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O74" s="13" t="inlineStr">
+      <c r="O74" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -9553,228 +9566,228 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="12" t="n">
+      <c r="A75" s="13" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B75" s="13" t="inlineStr">
         <is>
           <t>Siyam World Maldives</t>
         </is>
       </c>
-      <c r="C75" s="12" t="inlineStr">
+      <c r="C75" s="13" t="inlineStr">
         <is>
           <t>Noonu</t>
         </is>
       </c>
-      <c r="D75" s="12" t="inlineStr">
+      <c r="D75" s="13" t="inlineStr">
         <is>
           <t>Sun Siyam Resorts</t>
         </is>
       </c>
-      <c r="E75" s="12" t="n">
+      <c r="E75" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="F75" s="12" t="inlineStr">
+      <c r="F75" s="13" t="inlineStr">
         <is>
           <t>GES + ESS mevcut / sözleşmeli</t>
         </is>
       </c>
-      <c r="G75" s="12" t="inlineStr">
+      <c r="G75" s="13" t="inlineStr">
         <is>
           <t>2025: GES (2,7 MW hedef) + 1.720 kWh ESS – Hayleys Fentons</t>
         </is>
       </c>
-      <c r="H75" s="12" t="inlineStr">
+      <c r="H75" s="13" t="inlineStr">
         <is>
           <t>siyamworld.com</t>
         </is>
       </c>
-      <c r="I75" s="12" t="inlineStr">
+      <c r="I75" s="13" t="inlineStr">
         <is>
           <t>book@sunsiyam.com (merkez)</t>
         </is>
       </c>
-      <c r="J75" s="12" t="inlineStr">
+      <c r="J75" s="13" t="inlineStr">
         <is>
           <t>+960 656 7777</t>
         </is>
       </c>
-      <c r="K75" s="12" t="inlineStr">
+      <c r="K75" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi; otele özel e-posta gizlenmiş</t>
         </is>
       </c>
-      <c r="L75" s="12" t="inlineStr">
+      <c r="L75" s="13" t="inlineStr">
         <is>
           <t>https://www.sunsiyam.com/siyam-world/contact-us/</t>
         </is>
       </c>
-      <c r="M75" s="12" t="inlineStr">
+      <c r="M75" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N75" s="12" t="n">
+      <c r="N75" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="O75" s="13" t="inlineStr">
+      <c r="O75" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P75" s="12" t="inlineStr">
+      <c r="P75" s="13" t="inlineStr">
         <is>
           <t>büyük resort (yüksek dizel tüketimi); rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="12" t="n">
+      <c r="A76" s="13" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>Sun Siyam Vilu Reef</t>
         </is>
       </c>
-      <c r="C76" s="12" t="inlineStr">
+      <c r="C76" s="13" t="inlineStr">
         <is>
           <t>Dhaalu</t>
         </is>
       </c>
-      <c r="D76" s="12" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>Sun Siyam Resorts</t>
         </is>
       </c>
-      <c r="E76" s="12" t="n">
+      <c r="E76" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="F76" s="12" t="inlineStr">
+      <c r="F76" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G76" s="12" t="inlineStr">
+      <c r="G76" s="13" t="inlineStr">
         <is>
           <t>Grup 2. faz adayı</t>
         </is>
       </c>
-      <c r="H76" s="12" t="inlineStr">
+      <c r="H76" s="13" t="inlineStr">
         <is>
           <t>sunsiyam.com</t>
         </is>
       </c>
-      <c r="I76" s="12" t="inlineStr">
+      <c r="I76" s="13" t="inlineStr">
         <is>
           <t>info.vilureef@sunsiyam.com</t>
         </is>
       </c>
-      <c r="J76" s="12" t="inlineStr">
+      <c r="J76" s="13" t="inlineStr">
         <is>
           <t>+960 676 0011</t>
         </is>
       </c>
-      <c r="K76" s="12" t="inlineStr">
+      <c r="K76" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L76" s="12" t="inlineStr">
+      <c r="L76" s="13" t="inlineStr">
         <is>
           <t>https://www.sunsiyam.com/sun-siyam-vilu-reef/contact-us/</t>
         </is>
       </c>
-      <c r="M76" s="12" t="inlineStr">
+      <c r="M76" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N76" s="12" t="n">
+      <c r="N76" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="O76" s="13" t="inlineStr">
+      <c r="O76" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P76" s="12" t="inlineStr">
+      <c r="P76" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; bilinen GES yok -&gt; GES+ESS paketi; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="12" t="n">
+      <c r="A77" s="13" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B77" s="13" t="inlineStr">
         <is>
           <t>Vilamendhoo Island Resort</t>
         </is>
       </c>
-      <c r="C77" s="12" t="inlineStr">
+      <c r="C77" s="13" t="inlineStr">
         <is>
           <t>Alif Dhaal (Güney Ari)</t>
         </is>
       </c>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="D77" s="13" t="inlineStr">
         <is>
           <t>Bağımsız</t>
         </is>
       </c>
-      <c r="E77" s="12" t="n">
+      <c r="E77" s="13" t="n">
         <v>180</v>
       </c>
-      <c r="F77" s="12" t="inlineStr">
+      <c r="F77" s="13" t="inlineStr">
         <is>
           <t>Dizel ağırlıklı (kamuya açık GES bilgisi yok)</t>
         </is>
       </c>
-      <c r="G77" s="12" t="inlineStr">
+      <c r="G77" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H77" s="12" t="inlineStr">
+      <c r="H77" s="13" t="inlineStr">
         <is>
           <t>vilamendhoo.com</t>
         </is>
       </c>
-      <c r="I77" s="12" t="inlineStr">
+      <c r="I77" s="13" t="inlineStr">
         <is>
           <t>reservations@vilamendhoo.com</t>
         </is>
       </c>
-      <c r="J77" s="12" t="inlineStr">
+      <c r="J77" s="13" t="inlineStr">
         <is>
           <t>+960 668 0637</t>
         </is>
       </c>
-      <c r="K77" s="12" t="inlineStr">
+      <c r="K77" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L77" s="12" t="inlineStr">
+      <c r="L77" s="13" t="inlineStr">
         <is>
           <t>https://www.vilamendhoo.com/contact-us.html</t>
         </is>
       </c>
-      <c r="M77" s="12" t="inlineStr">
+      <c r="M77" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N77" s="12" t="n">
+      <c r="N77" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="O77" s="13" t="inlineStr">
+      <c r="O77" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P77" s="12" t="inlineStr">
+      <c r="P77" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; bilinen GES yok -&gt; GES+ESS paketi</t>
         </is>
@@ -9845,7 +9858,7 @@
       <c r="N78" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="O78" s="14" t="inlineStr">
+      <c r="O78" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -9926,7 +9939,7 @@
       <c r="N79" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="O79" s="14" t="inlineStr">
+      <c r="O79" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -10007,7 +10020,7 @@
       <c r="N80" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="O80" s="14" t="inlineStr">
+      <c r="O80" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -10024,840 +10037,840 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="12" t="n">
+      <c r="A81" s="13" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B81" s="13" t="inlineStr">
         <is>
           <t>Sun Siyam Olhuveli</t>
         </is>
       </c>
-      <c r="C81" s="12" t="inlineStr">
+      <c r="C81" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
-      <c r="D81" s="12" t="inlineStr">
+      <c r="D81" s="13" t="inlineStr">
         <is>
           <t>Sun Siyam Resorts</t>
         </is>
       </c>
-      <c r="E81" s="12" t="n">
+      <c r="E81" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="F81" s="12" t="inlineStr">
+      <c r="F81" s="13" t="inlineStr">
         <is>
           <t>GES + ESS mevcut / sözleşmeli</t>
         </is>
       </c>
-      <c r="G81" s="12" t="inlineStr">
+      <c r="G81" s="13" t="inlineStr">
         <is>
           <t>2025: GES + 537,5 kWh ESS – Hayleys Fentons</t>
         </is>
       </c>
-      <c r="H81" s="12" t="inlineStr">
+      <c r="H81" s="13" t="inlineStr">
         <is>
           <t>sunsiyam.com</t>
         </is>
       </c>
-      <c r="I81" s="12" t="inlineStr">
+      <c r="I81" s="13" t="inlineStr">
         <is>
           <t>ecommerce.olhuveli@sunsiyam.com</t>
         </is>
       </c>
-      <c r="J81" s="12" t="inlineStr">
+      <c r="J81" s="13" t="inlineStr">
         <is>
           <t>+960 664 2788</t>
         </is>
       </c>
-      <c r="K81" s="12" t="inlineStr">
+      <c r="K81" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L81" s="12" t="inlineStr">
+      <c r="L81" s="13" t="inlineStr">
         <is>
           <t>https://www.sunsiyam.com/sun-siyam-olhuveli/contact-us/</t>
         </is>
       </c>
-      <c r="M81" s="12" t="inlineStr">
+      <c r="M81" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N81" s="12" t="n">
+      <c r="N81" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="O81" s="14" t="inlineStr">
+      <c r="O81" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="P81" s="12" t="inlineStr">
+      <c r="P81" s="13" t="inlineStr">
         <is>
           <t>orta-büyük resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="12" t="n">
+      <c r="A82" s="13" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B82" s="13" t="inlineStr">
         <is>
           <t>Cheval Blanc Randheli</t>
         </is>
       </c>
-      <c r="C82" s="12" t="inlineStr">
+      <c r="C82" s="13" t="inlineStr">
         <is>
           <t>Noonu</t>
         </is>
       </c>
-      <c r="D82" s="12" t="inlineStr">
+      <c r="D82" s="13" t="inlineStr">
         <is>
           <t>LVMH</t>
         </is>
       </c>
-      <c r="E82" s="12" t="n">
+      <c r="E82" s="13" t="n">
         <v>46</v>
       </c>
-      <c r="F82" s="12" t="inlineStr">
+      <c r="F82" s="13" t="inlineStr">
         <is>
           <t>GES + ESS mevcut / sözleşmeli</t>
         </is>
       </c>
-      <c r="G82" s="12" t="inlineStr">
+      <c r="G82" s="13" t="inlineStr">
         <is>
           <t>Swimsol 2.421 kWp yüzer GES + 1.953 kWh ESS</t>
         </is>
       </c>
-      <c r="H82" s="12" t="inlineStr">
+      <c r="H82" s="13" t="inlineStr">
         <is>
           <t>chevalblanc.com</t>
         </is>
       </c>
-      <c r="I82" s="12" t="inlineStr">
+      <c r="I82" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J82" s="12" t="inlineStr">
+      <c r="J82" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K82" s="12" t="inlineStr">
+      <c r="K82" s="13" t="inlineStr">
         <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="L82" s="12" t="inlineStr">
+      <c r="L82" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M82" s="12" t="inlineStr">
+      <c r="M82" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N82" s="12" t="n">
+      <c r="N82" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="O82" s="14" t="inlineStr">
+      <c r="O82" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="P82" s="12" t="inlineStr">
+      <c r="P82" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="12" t="n">
+      <c r="A83" s="13" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B83" s="13" t="inlineStr">
         <is>
           <t>Kudadoo Maldives Private Island</t>
         </is>
       </c>
-      <c r="C83" s="12" t="inlineStr">
+      <c r="C83" s="13" t="inlineStr">
         <is>
           <t>Lhaviyani</t>
         </is>
       </c>
-      <c r="D83" s="12" t="inlineStr">
+      <c r="D83" s="13" t="inlineStr">
         <is>
           <t>Crown &amp; Champa Resorts</t>
         </is>
       </c>
-      <c r="E83" s="12" t="n">
+      <c r="E83" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="F83" s="12" t="inlineStr">
+      <c r="F83" s="13" t="inlineStr">
         <is>
           <t>GES + ESS mevcut / sözleşmeli</t>
         </is>
       </c>
-      <c r="G83" s="12" t="inlineStr">
+      <c r="G83" s="13" t="inlineStr">
         <is>
           <t>Tamamen güneş enerjili olarak tasarlandı</t>
         </is>
       </c>
-      <c r="H83" s="12" t="inlineStr">
+      <c r="H83" s="13" t="inlineStr">
         <is>
           <t>kudadoo.com</t>
         </is>
       </c>
-      <c r="I83" s="12" t="inlineStr">
+      <c r="I83" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J83" s="12" t="inlineStr">
+      <c r="J83" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K83" s="12" t="inlineStr">
+      <c r="K83" s="13" t="inlineStr">
         <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="L83" s="12" t="inlineStr">
+      <c r="L83" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M83" s="12" t="inlineStr">
+      <c r="M83" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N83" s="12" t="n">
+      <c r="N83" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="O83" s="14" t="inlineStr">
+      <c r="O83" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="P83" s="12" t="inlineStr">
+      <c r="P83" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="12" t="n">
+      <c r="A84" s="13" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B84" s="13" t="inlineStr">
         <is>
           <t>Patina Maldives (Fari Islands)</t>
         </is>
       </c>
-      <c r="C84" s="12" t="inlineStr">
+      <c r="C84" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D84" s="12" t="inlineStr">
+      <c r="D84" s="13" t="inlineStr">
         <is>
           <t>Pontiac Land</t>
         </is>
       </c>
-      <c r="E84" s="12" t="n">
+      <c r="E84" s="13" t="n">
         <v>110</v>
       </c>
-      <c r="F84" s="12" t="inlineStr">
+      <c r="F84" s="13" t="inlineStr">
         <is>
           <t>GES + ESS mevcut / sözleşmeli</t>
         </is>
       </c>
-      <c r="G84" s="12" t="inlineStr">
+      <c r="G84" s="13" t="inlineStr">
         <is>
           <t>~3 MWp GES + 2 MWh ESS; Fari toplam 6,4 MW</t>
         </is>
       </c>
-      <c r="H84" s="12" t="inlineStr">
+      <c r="H84" s="13" t="inlineStr">
         <is>
           <t>patinahotels.com</t>
         </is>
       </c>
-      <c r="I84" s="12" t="inlineStr">
+      <c r="I84" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J84" s="12" t="inlineStr">
+      <c r="J84" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K84" s="12" t="inlineStr">
+      <c r="K84" s="13" t="inlineStr">
         <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="L84" s="12" t="inlineStr">
+      <c r="L84" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M84" s="12" t="inlineStr">
+      <c r="M84" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N84" s="12" t="n">
+      <c r="N84" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="O84" s="14" t="inlineStr">
+      <c r="O84" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="P84" s="12" t="inlineStr">
+      <c r="P84" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="n">
+      <c r="A85" s="13" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B85" s="13" t="inlineStr">
         <is>
           <t>Soneva Fushi</t>
         </is>
       </c>
-      <c r="C85" s="12" t="inlineStr">
+      <c r="C85" s="13" t="inlineStr">
         <is>
           <t>Baa</t>
         </is>
       </c>
-      <c r="D85" s="12" t="inlineStr">
+      <c r="D85" s="13" t="inlineStr">
         <is>
           <t>Soneva</t>
         </is>
       </c>
-      <c r="E85" s="12" t="n">
+      <c r="E85" s="13" t="n">
         <v>70</v>
       </c>
-      <c r="F85" s="12" t="inlineStr">
+      <c r="F85" s="13" t="inlineStr">
         <is>
           <t>GES + ESS mevcut / sözleşmeli</t>
         </is>
       </c>
-      <c r="G85" s="12" t="inlineStr">
+      <c r="G85" s="13" t="inlineStr">
         <is>
           <t>Canopy Power GES + ESS (~%60 yenilenebilir)</t>
         </is>
       </c>
-      <c r="H85" s="12" t="inlineStr">
+      <c r="H85" s="13" t="inlineStr">
         <is>
           <t>soneva.com</t>
         </is>
       </c>
-      <c r="I85" s="12" t="inlineStr">
+      <c r="I85" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J85" s="12" t="inlineStr">
+      <c r="J85" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K85" s="12" t="inlineStr">
+      <c r="K85" s="13" t="inlineStr">
         <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="L85" s="12" t="inlineStr">
+      <c r="L85" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M85" s="12" t="inlineStr">
+      <c r="M85" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N85" s="12" t="n">
+      <c r="N85" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="O85" s="14" t="inlineStr">
+      <c r="O85" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="P85" s="12" t="inlineStr">
+      <c r="P85" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="12" t="n">
+      <c r="A86" s="13" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>Soneva Jani</t>
         </is>
       </c>
-      <c r="C86" s="12" t="inlineStr">
+      <c r="C86" s="13" t="inlineStr">
         <is>
           <t>Noonu</t>
         </is>
       </c>
-      <c r="D86" s="12" t="inlineStr">
+      <c r="D86" s="13" t="inlineStr">
         <is>
           <t>Soneva</t>
         </is>
       </c>
-      <c r="E86" s="12" t="n">
+      <c r="E86" s="13" t="n">
         <v>51</v>
       </c>
-      <c r="F86" s="12" t="inlineStr">
+      <c r="F86" s="13" t="inlineStr">
         <is>
           <t>GES + ESS mevcut / sözleşmeli</t>
         </is>
       </c>
-      <c r="G86" s="12" t="inlineStr">
+      <c r="G86" s="13" t="inlineStr">
         <is>
           <t>Canopy Power GES + ESS</t>
         </is>
       </c>
-      <c r="H86" s="12" t="inlineStr">
+      <c r="H86" s="13" t="inlineStr">
         <is>
           <t>soneva.com</t>
         </is>
       </c>
-      <c r="I86" s="12" t="inlineStr">
+      <c r="I86" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J86" s="12" t="inlineStr">
+      <c r="J86" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K86" s="12" t="inlineStr">
+      <c r="K86" s="13" t="inlineStr">
         <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="L86" s="12" t="inlineStr">
+      <c r="L86" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M86" s="12" t="inlineStr">
+      <c r="M86" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N86" s="12" t="n">
+      <c r="N86" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="O86" s="14" t="inlineStr">
+      <c r="O86" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="P86" s="12" t="inlineStr">
+      <c r="P86" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="12" t="n">
+      <c r="A87" s="13" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="B87" s="13" t="inlineStr">
         <is>
           <t>Soneva Secret</t>
         </is>
       </c>
-      <c r="C87" s="12" t="inlineStr">
+      <c r="C87" s="13" t="inlineStr">
         <is>
           <t>Haa Dhaalu</t>
         </is>
       </c>
-      <c r="D87" s="12" t="inlineStr">
+      <c r="D87" s="13" t="inlineStr">
         <is>
           <t>Soneva</t>
         </is>
       </c>
-      <c r="E87" s="12" t="n">
+      <c r="E87" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="F87" s="12" t="inlineStr">
+      <c r="F87" s="13" t="inlineStr">
         <is>
           <t>GES + ESS mevcut / sözleşmeli</t>
         </is>
       </c>
-      <c r="G87" s="12" t="inlineStr">
+      <c r="G87" s="13" t="inlineStr">
         <is>
           <t>Canopy Power 2 MWp yüzer GES + 3 MWh Huawei ESS</t>
         </is>
       </c>
-      <c r="H87" s="12" t="inlineStr">
+      <c r="H87" s="13" t="inlineStr">
         <is>
           <t>soneva.com</t>
         </is>
       </c>
-      <c r="I87" s="12" t="inlineStr">
+      <c r="I87" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J87" s="12" t="inlineStr">
+      <c r="J87" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K87" s="12" t="inlineStr">
+      <c r="K87" s="13" t="inlineStr">
         <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="L87" s="12" t="inlineStr">
+      <c r="L87" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M87" s="12" t="inlineStr">
+      <c r="M87" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N87" s="12" t="n">
+      <c r="N87" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="O87" s="14" t="inlineStr">
+      <c r="O87" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="P87" s="12" t="inlineStr">
+      <c r="P87" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="12" t="n">
+      <c r="A88" s="13" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B88" s="13" t="inlineStr">
         <is>
           <t>The Ritz-Carlton Maldives (Fari Islands)</t>
         </is>
       </c>
-      <c r="C88" s="12" t="inlineStr">
+      <c r="C88" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Kuzey Malé)</t>
         </is>
       </c>
-      <c r="D88" s="12" t="inlineStr">
+      <c r="D88" s="13" t="inlineStr">
         <is>
           <t>Pontiac Land / Marriott</t>
         </is>
       </c>
-      <c r="E88" s="12" t="n">
+      <c r="E88" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="F88" s="12" t="inlineStr">
+      <c r="F88" s="13" t="inlineStr">
         <is>
           <t>GES + ESS mevcut / sözleşmeli</t>
         </is>
       </c>
-      <c r="G88" s="12" t="inlineStr">
+      <c r="G88" s="13" t="inlineStr">
         <is>
           <t>983 kW çatı GES; Fari ortak mikro şebeke</t>
         </is>
       </c>
-      <c r="H88" s="12" t="inlineStr">
+      <c r="H88" s="13" t="inlineStr">
         <is>
           <t>ritzcarlton.com</t>
         </is>
       </c>
-      <c r="I88" s="12" t="inlineStr">
+      <c r="I88" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J88" s="12" t="inlineStr">
+      <c r="J88" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K88" s="12" t="inlineStr">
+      <c r="K88" s="13" t="inlineStr">
         <is>
           <t>Web sitesindeki 'Contact' sayfası (genel e-posta/telefon buradan teyit edilmeli)</t>
         </is>
       </c>
-      <c r="L88" s="12" t="inlineStr">
+      <c r="L88" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M88" s="12" t="inlineStr">
+      <c r="M88" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N88" s="12" t="n">
+      <c r="N88" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="O88" s="14" t="inlineStr">
+      <c r="O88" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="P88" s="12" t="inlineStr">
+      <c r="P88" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="12" t="n">
+      <c r="A89" s="13" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="B89" s="13" t="inlineStr">
         <is>
           <t>Veligandu Maldives</t>
         </is>
       </c>
-      <c r="C89" s="12" t="inlineStr">
+      <c r="C89" s="13" t="inlineStr">
         <is>
           <t>Alif Alif (Rasdhoo)</t>
         </is>
       </c>
-      <c r="D89" s="12" t="inlineStr">
+      <c r="D89" s="13" t="inlineStr">
         <is>
           <t>Crown &amp; Champa Resorts</t>
         </is>
       </c>
-      <c r="E89" s="12" t="n">
+      <c r="E89" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="F89" s="12" t="inlineStr">
+      <c r="F89" s="13" t="inlineStr">
         <is>
           <t>GES + ESS mevcut / sözleşmeli</t>
         </is>
       </c>
-      <c r="G89" s="12" t="inlineStr">
+      <c r="G89" s="13" t="inlineStr">
         <is>
           <t>1.441 kW GES + 1.668 kWh ESS (Eyl. 2025)</t>
         </is>
       </c>
-      <c r="H89" s="12" t="inlineStr">
+      <c r="H89" s="13" t="inlineStr">
         <is>
           <t>veligandu.com</t>
         </is>
       </c>
-      <c r="I89" s="12" t="inlineStr">
+      <c r="I89" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J89" s="12" t="inlineStr">
+      <c r="J89" s="13" t="inlineStr">
         <is>
           <t>+960 666 0519</t>
         </is>
       </c>
-      <c r="K89" s="12" t="inlineStr">
+      <c r="K89" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi; e-posta gizlenmiş</t>
         </is>
       </c>
-      <c r="L89" s="12" t="inlineStr">
+      <c r="L89" s="13" t="inlineStr">
         <is>
           <t>https://veligandu.com/contact/</t>
         </is>
       </c>
-      <c r="M89" s="12" t="inlineStr">
+      <c r="M89" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N89" s="12" t="n">
+      <c r="N89" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="O89" s="14" t="inlineStr">
+      <c r="O89" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="P89" s="12" t="inlineStr">
+      <c r="P89" s="13" t="inlineStr">
         <is>
           <t>küçük/butik resort; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis; çok-resortlu grup (tek kararla birden fazla ada)</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="12" t="n">
+      <c r="A90" s="13" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="12" t="inlineStr">
+      <c r="B90" s="13" t="inlineStr">
         <is>
           <t>RAH GILI MALDIVES</t>
         </is>
       </c>
-      <c r="C90" s="12" t="inlineStr">
+      <c r="C90" s="13" t="inlineStr">
         <is>
           <t>Kaafu (Güney Malé)</t>
         </is>
       </c>
-      <c r="D90" s="12" t="inlineStr">
+      <c r="D90" s="13" t="inlineStr">
         <is>
           <t>Bağımsız</t>
         </is>
       </c>
-      <c r="E90" s="12" t="inlineStr">
+      <c r="E90" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="F90" s="12" t="inlineStr">
+      <c r="F90" s="13" t="inlineStr">
         <is>
           <t>GES + ESS mevcut / sözleşmeli</t>
         </is>
       </c>
-      <c r="G90" s="12" t="inlineStr">
+      <c r="G90" s="13" t="inlineStr">
         <is>
           <t>2 MW GES + 2.500 kWh ESS; günlük ~17.000 kWh tüketim</t>
         </is>
       </c>
-      <c r="H90" s="12" t="inlineStr">
+      <c r="H90" s="13" t="inlineStr">
         <is>
           <t>rahgili.com</t>
         </is>
       </c>
-      <c r="I90" s="12" t="inlineStr">
+      <c r="I90" s="13" t="inlineStr">
         <is>
           <t>reservations@rahgili.com</t>
         </is>
       </c>
-      <c r="J90" s="12" t="inlineStr">
+      <c r="J90" s="13" t="inlineStr">
         <is>
           <t>+960 401 4001</t>
         </is>
       </c>
-      <c r="K90" s="12" t="inlineStr">
+      <c r="K90" s="13" t="inlineStr">
         <is>
           <t>Otelin kendi sitesi</t>
         </is>
       </c>
-      <c r="L90" s="12" t="inlineStr">
+      <c r="L90" s="13" t="inlineStr">
         <is>
           <t>https://rahgili.com/contact-us</t>
         </is>
       </c>
-      <c r="M90" s="12" t="inlineStr">
+      <c r="M90" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N90" s="12" t="n">
+      <c r="N90" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="O90" s="14" t="inlineStr">
+      <c r="O90" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="P90" s="12" t="inlineStr">
+      <c r="P90" s="13" t="inlineStr">
         <is>
           <t>oda sayısı doğrulanmalı; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="12" t="n">
+      <c r="A91" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="12" t="inlineStr">
+      <c r="B91" s="13" t="inlineStr">
         <is>
           <t>Royal Rosewood Resort Island</t>
         </is>
       </c>
-      <c r="C91" s="12" t="inlineStr">
+      <c r="C91" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="D91" s="12" t="inlineStr">
+      <c r="D91" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="E91" s="12" t="inlineStr">
+      <c r="E91" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="F91" s="12" t="inlineStr">
+      <c r="F91" s="13" t="inlineStr">
         <is>
           <t>GES + ESS mevcut / sözleşmeli</t>
         </is>
       </c>
-      <c r="G91" s="12" t="inlineStr">
+      <c r="G91" s="13" t="inlineStr">
         <is>
           <t>Solmacher: 16 MWp GES + 40 MWh Huawei ESS (2026 sözleşme)</t>
         </is>
       </c>
-      <c r="H91" s="12" t="inlineStr">
+      <c r="H91" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I91" s="12" t="inlineStr">
+      <c r="I91" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J91" s="12" t="inlineStr">
+      <c r="J91" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K91" s="12" t="inlineStr">
+      <c r="K91" s="13" t="inlineStr">
         <is>
           <t>Bulunamadı (yeni proje / doğrulanmalı)</t>
         </is>
       </c>
-      <c r="L91" s="12" t="inlineStr">
+      <c r="L91" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M91" s="12" t="inlineStr">
+      <c r="M91" s="13" t="inlineStr">
         <is>
           <t>Resort: Director of Engineering / Chief Engineer, General Manager; Grup: Technical Services / Sustainability Director</t>
         </is>
       </c>
-      <c r="N91" s="12" t="n">
+      <c r="N91" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="O91" s="14" t="inlineStr">
+      <c r="O91" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="P91" s="12" t="inlineStr">
+      <c r="P91" s="13" t="inlineStr">
         <is>
           <t>oda sayısı doğrulanmalı; rakip GES+ESS kurmuş -&gt; sadece genişleme/servis</t>
         </is>
@@ -10957,57 +10970,57 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>VERSA Hospitality (eski Universal Resorts)</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Malé (Maldivli)</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>Niva Kuramathi, Niva Kurumba, Niva Velassaru, Niva Dhigali, Baros, Milaidhoo, Kandolhu</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>Ekim 2025'te VERSA adını aldı, Niva markasını kurdu. Kuramathi'de kısmi GES; diğerlerinde kamuya açık GES bilgisi yok</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>versahospitality.com</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H2" s="12" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>— (web sitesindeki form)</t>
         </is>
       </c>
-      <c r="I2" s="12" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J2" s="12" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>39 Orchid Magu, Malé</t>
         </is>
       </c>
-      <c r="K2" s="12" t="inlineStr">
+      <c r="K2" s="13" t="inlineStr">
         <is>
           <t>https://www.versahospitality.com/</t>
         </is>
@@ -11044,7 +11057,7 @@
           <t>villaresorts.com</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -11106,7 +11119,7 @@
           <t>sunsiyam.com</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -11168,7 +11181,7 @@
           <t>crownandchamparesorts.com</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -11200,57 +11213,57 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Kuredu Holdings (Crown &amp; Champa ortağı)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Malé (Maldivli)</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>2+</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Kuredu, Komandoo</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Kuredu ve Komandoo'nun sahibi; yeni resortlar geliştiriyor</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>— (Crown &amp; Champa üzerinden)</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>M. Champa Building 4. kat, Kandi Dhon Manik Goalhi, Malé 20187</t>
         </is>
       </c>
-      <c r="K6" s="12" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>https://business.egov.mv/BusinessRegistry/ViewDetails/39070?key=-577025120</t>
         </is>
@@ -11287,7 +11300,7 @@
           <t>atmospherecore.com</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -11349,7 +11362,7 @@
           <t>aydeniz.com</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -11381,171 +11394,171 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Gürok Grubu (TÜRK – JOALI sahibi)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Kütahya, Türkiye</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>JOALI Maldives, JOALI BEING (Raa Atoll)</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Ultra lüks, sürdürülebilirlik odaklı; kamuya açık GES bilgisi yok. Türk sahipli – Türkçe görüşme</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>gurok.com</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>info@gurok.com</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t>+90 274 225 06 60</t>
         </is>
       </c>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>İnköy Mah. Eskişehir Karayolu Blv. No:96, Kütahya</t>
         </is>
       </c>
-      <c r="K9" s="12" t="inlineStr">
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>https://gurok.com/iletisim</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Astaş Holding (TÜRK – yeni Maldivler projesi)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>İstanbul, Türkiye</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Proje</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>~120 villalık, 300 M$ resort projesi (Mandarin Oriental Bodrum sahibi)</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Tasarım aşamasında – enerji sistemi baştan hibrit kurgulanabilir. EN SICAK yeni proje adayı</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>astas-holding.com</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t>info@astas-holding.com</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>+90 212 215 20 20</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>Büyükdere Cad. No:127 Astoria Kuleleri B Blok K:25, Esentepe, İstanbul</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr">
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>https://www.astas-holding.com/tr/iletisim</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Maxx Royal Resorts (TÜRK – Maxx Royal Maldives)</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Antalya / Bodrum, Türkiye</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Proje</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Maxx Royal Maldives (5 ada, 2027 açılış hedefi)</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Yapım/tasarım aşamasında – enerji sistemi baştan hibrit kurgulanabilir</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>maxxroyal.com</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>contact@maxxroyal.com</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>+90 252 311 01 50</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>Bodrum ofisi</t>
         </is>
       </c>
-      <c r="K11" s="12" t="inlineStr">
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t>https://www.maxxroyal.com/contact</t>
         </is>
@@ -11582,7 +11595,7 @@
           <t>aitkenspencehotels.com</t>
         </is>
       </c>
-      <c r="G12" s="13" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -11644,7 +11657,7 @@
           <t>cinnamonhotels.com</t>
         </is>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -11706,7 +11719,7 @@
           <t>minorhotels.com</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -11768,7 +11781,7 @@
           <t>kandima.com</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -11830,7 +11843,7 @@
           <t>crossroadsmaldives.com</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -11892,7 +11905,7 @@
           <t>centarahotelsresorts.com</t>
         </is>
       </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -11954,7 +11967,7 @@
           <t>emerald-maldives.com</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -11986,171 +11999,171 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Pontiac Land (Fari Islands)</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Singapur</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>3 (Capella 2027)</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Patina, Ritz-Carlton, Capella</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Swimsol ile büyük GES+ESS – rakip tarafından alınmış</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>fari-islands.com</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr">
+      <c r="H19" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I19" s="12" t="inlineStr">
+      <c r="I19" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J19" s="12" t="inlineStr">
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr">
+      <c r="K19" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Soneva</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>Maldivler / Dubai</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Soneva Fushi, Jani, Secret</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Canopy Power + Huawei ESS – rakip tarafından alınmış (referans vaka)</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>soneva.com</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G20" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H20" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr">
+      <c r="I20" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J20" s="12" t="inlineStr">
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K20" s="12" t="inlineStr">
+      <c r="K20" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Marriott / Hilton / IHG / Four Seasons vb. küresel markalar</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Çeşitli</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Çok sayıda</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Waldorf, Conrad, Sheraton, Holiday Inn, Four Seasons</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Karar çoğunlukla mülk sahibi (owner) şirkette; marka sadece işletmeci. Owner şirket tespit edilmeli</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr">
+      <c r="H21" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="I21" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K21" s="12" t="inlineStr">
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12214,384 +12227,384 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Swimsol</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Avusturya (Maldivler'de yerleşik)</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>GES geliştirici / EPC, PPA ve satış</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>50+ resort adası; 2024'te 13+ MWp; Cheval Blanc 2,4 MWp, Taj Exotica, Taj Coral Reef, LUX* South Ari, OZEN LIFE Maadhoo, Fari Islands 1 MWp yüzer, Ritz-Carlton 983 kW, Four Seasons, Kuramathi</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>SolarSea yüzer GES (kendi patenti), çatı GES; toplam ~50 MWp GES + ~25 MWh batarya</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>Pazar lideri. ESS'yi dışarıdan tedarik ediyor -&gt; ESS tedarikçisi olarak ORTAK adayı da olabilir</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Canopy Power</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Singapur</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Mikro şebeke EPC / PPA</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Soneva Fushi, Soneva Jani (5,2 MWp + 4,7 MWh), Soneva Secret (2 MWp yüzer + 3 MWh)</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Huawei ESS, Ocean Sun yüzer GES</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>Huawei ile çalışıyor; geri dönüş 4-5 yıl beyanı</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Solmacher Solar Energy</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>EPC / mikro şebeke</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Royal Rosewood Resort Island: 16 MWp GES + 40 MWh ESS (Ağu. 2026 sözleşme)</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Huawei Digital Power ESS + C&amp;I/utility inverter</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>Maldivler'in en büyük resort mikro şebekesi; Huawei'nin bölgedeki ana kanalı</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Hayleys Fentons</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>EPC</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Sun Siyam: Siyam World + Olhuveli (4.110 kWp + 2.257 kWh ESS)</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Sri Lanka merkezli büyük grup – ortaklık veya rakip</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Ecogreen Maldives</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Maldivler</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Yerel kurulumcu</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Resort, misafirhane, konut</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>Yerel ortak adayı</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Renewable Energy Maldives (REM)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Maldivler</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Yerel kurulumcu (2012)</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>Yerel ortak adayı</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Ensys</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Tayland</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Geliştirici / PPA</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Maldivler'de GES PPA (ASPIRE)</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>Kamu ihaleleri tarafı</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Avi Technologies</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Kurulumcu – GES + batarya</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Batarya entegrasyonu odaklı – ortak adayı</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>MYENERGY Solutions</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>ESS distribütörü (EAST Group)</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Sri Lanka &amp; Maldivler'e ESS dağıtımı</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>EAST Group ESS</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>Doğrudan ürün rakibi (Çin menşeli ESS)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Huawei Digital Power</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Çin</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Üretici</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Soneva Secret (3 MWh), Royal Rosewood (40 MWh)</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>LUNA2000 C&amp;I/Utility ESS, FusionSolar</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Bölgede referansı VAR. Karea'nın Türkiye distribütörlüğü Maldivler'i kapsamıyor olabilir -&gt; Huawei bölge ofisiyle kanal netleştirilmeli</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>HYXI</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Çin</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Üretici</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Maldivler'de kamuya açık proje bulunamadı</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>C&amp;I ESS, inverter</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>Boş alan: Karea ilk referansı yapabilir; HYXI ile Maldivler için yetki/destek görüşülmeli</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Sungrow, BYD, Tesla vb.</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Çeşitli</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Üretici</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Kamu ihaleleri (ASSURE 40 MWh BESS) ve resortlarda olası</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Fiyat rekabeti beklenmeli</t>
         </is>
@@ -12809,32 +12822,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Renewable Energy Maldives (REM)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Yerel kurulumcu (2006)</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Sri Lanka kolu (REM Lanka) SolaX kullanıyor</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>~25 ada ve resortlarla çalışmış eski oyuncu</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>LinkedIn: REM Solar</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>Yerel ortak adayı</t>
         </is>
@@ -12952,32 +12965,32 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Solmacher Solar Energy</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>EPC</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>HUAWEI (Royal Rosewood 40 MWh ESS + inverter, Ağu. 2026)</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Huawei'nin Maldivler'deki en büyük projesi bu firmada</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Doğrulanmalı</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>Huawei kullanıcısı</t>
         </is>
@@ -13058,96 +13071,96 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Resort jeneratör bakım/servis firmaları</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>O&amp;M</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Cummins, MTU, Caterpillar yerel bayileri</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Her resortun enerji santraline zaten erişimleri var; hibrit kontrol entegrasyonu için kritik</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Saha ziyaretinde tespit edilecek</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Teknik ortak</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>DEIF</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Hibrit kontrol sistemi (Danimarka)</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Maldivler'de bir lüks resortta dizel+GES+batarya kontrolünü yaptı; ESS entegrasyonunda teknik ortak</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>deif.com</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>Teknik ortak</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Elemental Water Makers</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Güneş enerjili su arıtma</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Resortlarda tuzdan arındırma en büyük elektrik yüklerinden biri</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>elementalwatermakers.com</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Tamamlayıcı ortak</t>
         </is>
@@ -13199,308 +13212,308 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Ministry of Climate Change, Environment and Energy</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Enerji politikası (Nisan 2026'da yeniden ayrı bakanlık oldu)</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>Yenilenebilir hedefler (%33 @2028), politika ve izinler</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>environment.gov.mv</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Utility Regulatory Authority (URA)</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Düzenleyici kurum (Kanun 26/2020)</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Elektrik üretim/servis lisansları, şebeke bağlantı ve net metering kuralları</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>ura.gov.mv</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>STELCO</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Devlet elektrik şirketi (Malé bölgesi)</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Resortlar şebekeye bağlı değil; ama kamu ESS ihalelerinin alıcısı</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>stelco.com.mv</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>FENAKA Corporation</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Devlet hizmet şirketi (dış adalar)</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Dış adalardaki ESS/GES ihaleleri</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>fenaka.mv</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Ministry of Tourism</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Resort lisansları</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Resort listeleri, yeni ada kiralamaları, istatistik. Sitedeki 'Registered Facilities' listesi tüm resortların resmi telefon/e-posta bilgilerini içerir (PDF/CSV indirilebilir). Bakanlık: info@tourism.gov.mv, +960 332 3224</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>tourism.gov.mv</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Maldives Association of Tourism Industry (MATI)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Resort sahipleri derneği</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Sektöre toplu erişim, etkinlikler, sunum fırsatı</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>mati.mv</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Invest Maldives</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Yatırım ajansı</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Şirket kurma / yabancı yatırım süreçleri</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>investmaldives.gov.mv</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Maldives Customs Service</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Gümrük</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Yenilenebilir enerji ürünlerinde ithalat vergisi muafiyetinin teyidi</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>customs.gov.mv</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>State Trading Organization (STO)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Akaryakıt tedarikçisi</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Dizel fiyatlarının kaynağı</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>sto.mv</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Bank of Maldives</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Yerel banka</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Resort projelerine yerel finansman / yeşil kredi</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>bankofmaldives.com.mv</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Dünya Bankası – ASPIRE / ARISE</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Finansman programları</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>ASPIRE: özel GES PPA ihaleleri (tarifeler 21¢ -&gt; 10,9¢/kWh). ARISE: 100 M$, batarya + şebeke entegrasyonu</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>worldbank.org</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Asya Kalkınma Bankası (ADB) – POISED / ASSURE</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Finansman programları</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>POISED: dış adalarda hibrit sistemler (%25 yakıt tasarrufu). ASSURE: 18 adada 40 MWh BESS ihalesi (41,5 M$ hibe)</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>adb.org</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>AIIB</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Finansman</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>Solar Power Development and Energy Storage Solution projesi</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>aiib.org</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>T.C. Malé Büyükelçiliği / Ticaret Müşavirliği</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Ticari diplomasi</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Kurum tanıtımı, randevu desteği (temsilcilik yapısı doğrulanmalı)</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>mfa.gov.tr</t>
         </is>
@@ -13656,7 +13669,7 @@
           <t>Yıllık bakım (O&amp;M) maliyeti (% yatırım)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="16" t="n">
         <v>0.015</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -13693,7 +13706,7 @@
           <t>Yıllık GES üretimi (kWh)</t>
         </is>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="17">
         <f>B2*B3</f>
         <v/>
       </c>
@@ -13709,7 +13722,7 @@
           <t>Toplam yatırım ($)</t>
         </is>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="17">
         <f>B2*B5+B4*B6</f>
         <v/>
       </c>
@@ -13721,7 +13734,7 @@
           <t>Yıllık dizel tasarrufu ($)</t>
         </is>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="17">
         <f>B13*B7+B8</f>
         <v/>
       </c>
@@ -13737,7 +13750,7 @@
           <t>Yıllık O&amp;M ($)</t>
         </is>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="17">
         <f>B14*B9</f>
         <v/>
       </c>
@@ -13749,7 +13762,7 @@
           <t>Net yıllık tasarruf ($)</t>
         </is>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="17">
         <f>B15-B16</f>
         <v/>
       </c>
@@ -13761,7 +13774,7 @@
           <t>Basit geri dönüş süresi (yıl)</t>
         </is>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="18">
         <f>B14/B17</f>
         <v/>
       </c>
@@ -13777,7 +13790,7 @@
           <t>Yenilenebilir payı (%)</t>
         </is>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="19">
         <f>B13/B10</f>
         <v/>
       </c>
@@ -13793,7 +13806,7 @@
           <t>Yıllık dizel tasarrufu (litre, ~3,5 kWh/L)</t>
         </is>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="17">
         <f>B13/3.5</f>
         <v/>
       </c>
@@ -13819,37 +13832,37 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="n">
+      <c r="A24" s="20" t="n">
         <v>0.2</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="21">
         <f>B14/(B13*A24+B8-B16)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="n">
+      <c r="A25" s="20" t="n">
         <v>0.25</v>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="21">
         <f>B14/(B13*A25+B8-B16)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="n">
+      <c r="A26" s="20" t="n">
         <v>0.3</v>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="21">
         <f>B14/(B13*A26+B8-B16)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="n">
+      <c r="A27" s="20" t="n">
         <v>0.35</v>
       </c>
-      <c r="B27" s="20">
+      <c r="B27" s="21">
         <f>B14/(B13*A27+B8-B16)</f>
         <v/>
       </c>
@@ -13892,276 +13905,276 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Dizel üretim maliyeti 0,23–0,33 $/kWh; küçük adalarda 0,70 $/kWh'e kadar; resortlarda ~144 MW dizel</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>https://www.cif.org/sites/cif_enc/files/knowledge-documents/66436_191219_maldives_case_study_v7s.pdf</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>ADB Maldivler Yenilenebilir Yol Haritası</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>https://www.adb.org/sites/default/files/publication/654021/renewables-roadmap-energy-sector-maldives.pdf</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Enerji Yol Haritası 2024–2033</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>https://www.environment.gov.mv/v2/wp-content/files/publications/20241107-pub-energy-roadmap-maldives-2024-2033-.pdf</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>%33 yenilenebilir @2028 hedefi</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>https://en.mmtv.mv/246</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Yenilenebilir kapasite 53 MW -&gt; 126 MW; Raa/Baa 6,5 MW GES + 10 MW batarya</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>https://edition.mv/news/54359</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Dizel fiyatı 17,54 MVR/L (~1,14 $/L), Mart 2026 artışı</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>https://www.globalpetrolprices.com/Maldives/diesel_prices/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>2026 petrol şoku – dizel fiyatları</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>https://maldivesindependent.com/economy/half-a-gas-cylinder-double-the-diesel-price-the-oil-shock-hits-maldives-d022</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>179 resort, 44.807 resort yatağı (2026)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>https://en.maaldif.com/11791/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Swimsol: 50+ resort, Cheval Blanc 2,4 MWp, yılda 1,5 M$ tasarruf</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>https://www.businesswire.com/news/home/20260422437338/en/Swimsols-SolarSea-Maldives-Largest-Floating-Solar-Array-at-Sea-Saves-One-Island-USD-1.5-Million-Per-Year</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Fari Islands GES genişlemesi</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>https://www.pv-magazine.com/2025/07/11/fari-islands-set-to-triple-use-of-solar-energy/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Solmacher + Huawei 40 MWh BESS, Royal Rosewood</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/solmacher-signs-huawei-deal-for-40-mwh-bess-in-maldives/96106</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Huawei – Soneva Secret vaka çalışması (geri dönüş 4–5 yıl)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>https://digitalpower.huawei.com/en/cases/fusionsolar/floating-solar-maldives</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Canopy Power – Soneva</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>https://www.canopypower.com/resources/floating-solar-in-maldives</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Sun Siyam GES + ESS (Hayleys Fentons)</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>https://www.ttgasia.com/2025/12/16/sun-siyam-launches-major-solar-energy-project-in-maldives-resorts/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Veligandu GES + 1.668 kWh ESS</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>https://veligandu.com/sustainability/veligandu-solar-power/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Centara GES sonuçları</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>https://www.hospitalitynet.org/news/4130648/centara-leads-the-fight-against-climate-change-in-the-maldives</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>RAH GILI tüketim verisi</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>https://hoteliermaldives.com/solar-at-scale-how-rah-gili-maldives-is-reducing-diesel-dependence-and-embracing-sustainability/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>ASSURE 40 MWh BESS ihalesi</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>https://www.energy-storage.news/maldives-launches-tender-seeking-40mwh-bess-and-ems-across-18-islands/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Pontiac Land ilk yeşil kredi (180 M$)</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>https://hotelsmag.com/news/pontiac-land-secures-green-loan-in-the-maldives/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>URA ve lisans gereklilikleri</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>https://www.ctlstrategies.com/latest/maldives-energy-act/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>ENF Solar – Maldivler kurulumcu dizini</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>https://www.enfsolar.com/directory/installer/Maldives</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Yeni resort projeleri 2026–2027</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>https://resortlife.travel/maldives-new-resorts</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Atmosphere Core GES / Amaraa Faru</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>https://www.hotelierindia.com/development/atmosphere-core-signs-its-10th-resort-in-maldives</t>
         </is>
